--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 14:39</t>
+          <t>2026-05-08 16:05</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="V5" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W5" s="7" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>1</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W6" s="10" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="V7" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W7" s="7" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W8" s="10" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>1</v>
       </c>
       <c r="V9" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W9" s="7" t="n">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="V10" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W10" s="10" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>1</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W11" s="7" t="n">
         <v>0</v>
@@ -1389,7 +1389,7 @@
         <v>1</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W12" s="10" t="n">
         <v>0</v>
@@ -1477,10 +1477,10 @@
         <v>1</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>3750</v>
+        <v>3638</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>1</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W14" s="10" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>1</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W15" s="7" t="n">
         <v>0</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="V16" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W16" s="10" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W17" s="7" t="n">
         <v>0</v>
@@ -1917,10 +1917,10 @@
         <v>1</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W18" s="10" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="X18" s="10" t="n">
         <v>0</v>
@@ -2005,10 +2005,10 @@
         <v>1</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>8000</v>
+        <v>6825</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X19" s="7" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W20" s="10" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
         <v>1</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>8000</v>
+        <v>6825</v>
       </c>
       <c r="W21" s="7" t="n">
         <v>0</v>
@@ -2269,10 +2269,10 @@
         <v>1</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>8000</v>
+        <v>6825</v>
       </c>
       <c r="W22" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>0</v>
@@ -2357,10 +2357,10 @@
         <v>1</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>8000</v>
+        <v>6825</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X23" s="7" t="n">
         <v>0</v>
@@ -2445,10 +2445,10 @@
         <v>1</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W24" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>1</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W26" s="10" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W27" s="7" t="n">
         <v>0</v>
@@ -2797,7 +2797,7 @@
         <v>1</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W28" s="10" t="n">
         <v>0</v>
@@ -2885,10 +2885,10 @@
         <v>1</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>0</v>
@@ -2973,10 +2973,10 @@
         <v>1</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>1</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W31" s="7" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>1</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W32" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="V33" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W33" s="7" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>1</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W34" s="10" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>1</v>
       </c>
       <c r="V35" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W35" s="7" t="n">
         <v>0</v>
@@ -3505,10 +3505,10 @@
         <v>1</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W36" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>1</v>
       </c>
       <c r="V37" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W37" s="7" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
         <v>1</v>
       </c>
       <c r="V38" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W38" s="10" t="n">
         <v>0</v>
@@ -3769,7 +3769,7 @@
         <v>1</v>
       </c>
       <c r="V39" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W39" s="7" t="n">
         <v>0</v>
@@ -3857,7 +3857,7 @@
         <v>1</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W40" s="10" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W41" s="7" t="n">
         <v>0</v>
@@ -4033,10 +4033,10 @@
         <v>1</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W42" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         <v>1</v>
       </c>
       <c r="V43" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W43" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X43" s="7" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W44" s="10" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         <v>1</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W45" s="7" t="n">
         <v>0</v>
@@ -4385,10 +4385,10 @@
         <v>1</v>
       </c>
       <c r="V46" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W46" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="V47" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W47" s="7" t="n">
         <v>0</v>
@@ -4561,7 +4561,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W48" s="10" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="V49" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W49" s="7" t="n">
         <v>0</v>
@@ -4737,10 +4737,10 @@
         <v>1</v>
       </c>
       <c r="V50" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W50" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>1</v>
       </c>
       <c r="V51" s="7" t="n">
-        <v>7500</v>
+        <v>7280</v>
       </c>
       <c r="W51" s="7" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
         <v>1</v>
       </c>
       <c r="V52" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W52" s="10" t="n">
         <v>0</v>
@@ -5005,10 +5005,10 @@
         <v>1</v>
       </c>
       <c r="V53" s="7" t="n">
-        <v>7500</v>
+        <v>7280</v>
       </c>
       <c r="W53" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="X53" s="7" t="n">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W54" s="10" t="n">
         <v>0</v>
@@ -5181,10 +5181,10 @@
         <v>1</v>
       </c>
       <c r="V55" s="7" t="n">
-        <v>7500</v>
+        <v>7280</v>
       </c>
       <c r="W55" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>0</v>
@@ -5269,7 +5269,7 @@
         <v>1</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W56" s="10" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="V57" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W57" s="7" t="n">
         <v>0</v>
@@ -5445,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="V58" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W58" s="10" t="n">
         <v>0</v>
@@ -5533,7 +5533,7 @@
         <v>1</v>
       </c>
       <c r="V59" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W59" s="7" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W60" s="10" t="n">
         <v>0</v>
@@ -5709,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="V61" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W61" s="7" t="n">
         <v>0</v>
@@ -5797,10 +5797,10 @@
         <v>1</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>0</v>
@@ -5885,7 +5885,7 @@
         <v>1</v>
       </c>
       <c r="V63" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W63" s="7" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         <v>1</v>
       </c>
       <c r="V64" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W64" s="10" t="n">
         <v>0</v>
@@ -6065,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="V65" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W65" s="7" t="n">
         <v>0</v>
@@ -6153,7 +6153,7 @@
         <v>1</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W66" s="10" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>1</v>
       </c>
       <c r="V67" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W67" s="7" t="n">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="V68" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W68" s="10" t="n">
         <v>0</v>
@@ -6417,7 +6417,7 @@
         <v>1</v>
       </c>
       <c r="V69" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W69" s="7" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="V70" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W70" s="10" t="n">
         <v>0</v>
@@ -6597,7 +6597,7 @@
         <v>1</v>
       </c>
       <c r="V71" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W71" s="7" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
         <v>1</v>
       </c>
       <c r="V72" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W72" s="10" t="n">
         <v>0</v>
@@ -6773,7 +6773,7 @@
         <v>1</v>
       </c>
       <c r="V73" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W73" s="7" t="n">
         <v>0</v>
@@ -6861,10 +6861,10 @@
         <v>1</v>
       </c>
       <c r="V74" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W74" s="10" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="V75" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W75" s="7" t="n">
         <v>0</v>
@@ -7037,7 +7037,7 @@
         <v>1</v>
       </c>
       <c r="V76" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W76" s="10" t="n">
         <v>0</v>
@@ -7125,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="V77" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W77" s="7" t="n">
         <v>0</v>
@@ -7217,7 +7217,7 @@
         <v>1</v>
       </c>
       <c r="V78" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W78" s="10" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="V79" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W79" s="7" t="n">
         <v>0</v>
@@ -7393,7 +7393,7 @@
         <v>1</v>
       </c>
       <c r="V80" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W80" s="10" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="V81" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W81" s="7" t="n">
         <v>0</v>
@@ -7573,7 +7573,7 @@
         <v>1</v>
       </c>
       <c r="V82" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W82" s="10" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="V83" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W83" s="7" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>1</v>
       </c>
       <c r="V84" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W84" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X84" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="Y84" s="10" t="n">
         <v>0</v>
@@ -7841,13 +7841,13 @@
         <v>1</v>
       </c>
       <c r="V85" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X85" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="Y85" s="7" t="n">
         <v>0</v>
@@ -7929,13 +7929,13 @@
         <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X86" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="Y86" s="10" t="n">
         <v>0</v>
@@ -8017,10 +8017,10 @@
         <v>1</v>
       </c>
       <c r="V87" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W87" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>0</v>
@@ -8105,10 +8105,10 @@
         <v>1</v>
       </c>
       <c r="V88" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W88" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>0</v>
@@ -8193,7 +8193,7 @@
         <v>1</v>
       </c>
       <c r="V89" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W89" s="7" t="n">
         <v>0</v>
@@ -8281,10 +8281,10 @@
         <v>1</v>
       </c>
       <c r="V90" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W90" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>0</v>
@@ -8369,10 +8369,10 @@
         <v>1</v>
       </c>
       <c r="V91" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W91" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>0</v>
@@ -8457,10 +8457,10 @@
         <v>1</v>
       </c>
       <c r="V92" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W92" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>0</v>
@@ -8469,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="Z92" s="10" t="n">
-        <v>7500</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="93">
@@ -8545,10 +8545,10 @@
         <v>1</v>
       </c>
       <c r="V93" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W93" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X93" s="7" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
         <v>1</v>
       </c>
       <c r="V94" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W94" s="10" t="n">
         <v>0</v>
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="Y94" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z94" s="10" t="n">
         <v>0</v>
@@ -8721,16 +8721,16 @@
         <v>1</v>
       </c>
       <c r="V95" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W95" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y95" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z95" s="7" t="n">
         <v>0</v>
@@ -8809,16 +8809,16 @@
         <v>1</v>
       </c>
       <c r="V96" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W96" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y96" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z96" s="10" t="n">
         <v>0</v>
@@ -8897,7 +8897,7 @@
         <v>1</v>
       </c>
       <c r="V97" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W97" s="7" t="n">
         <v>0</v>
@@ -8985,7 +8985,7 @@
         <v>1</v>
       </c>
       <c r="V98" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W98" s="10" t="n">
         <v>0</v>
@@ -9073,7 +9073,7 @@
         <v>1</v>
       </c>
       <c r="V99" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W99" s="7" t="n">
         <v>0</v>
@@ -9161,7 +9161,7 @@
         <v>1</v>
       </c>
       <c r="V100" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W100" s="10" t="n">
         <v>0</v>
@@ -9249,7 +9249,7 @@
         <v>1</v>
       </c>
       <c r="V101" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W101" s="7" t="n">
         <v>0</v>
@@ -9341,16 +9341,16 @@
         <v>1</v>
       </c>
       <c r="V102" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W102" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y102" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z102" s="10" t="n">
         <v>0</v>
@@ -9429,10 +9429,10 @@
         <v>1</v>
       </c>
       <c r="V103" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W103" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X103" s="7" t="n">
         <v>0</v>
@@ -9517,16 +9517,16 @@
         <v>1</v>
       </c>
       <c r="V104" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W104" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y104" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z104" s="10" t="n">
         <v>0</v>
@@ -9605,16 +9605,16 @@
         <v>1</v>
       </c>
       <c r="V105" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W105" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y105" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z105" s="7" t="n">
         <v>0</v>
@@ -9693,16 +9693,16 @@
         <v>1</v>
       </c>
       <c r="V106" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W106" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y106" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z106" s="10" t="n">
         <v>0</v>
@@ -9781,16 +9781,16 @@
         <v>1</v>
       </c>
       <c r="V107" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W107" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y107" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z107" s="7" t="n">
         <v>0</v>
@@ -9869,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="V108" s="10" t="n">
-        <v>7500</v>
+        <v>7378</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>3750</v>
+        <v>3689</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>0</v>
@@ -9957,10 +9957,10 @@
         <v>1</v>
       </c>
       <c r="V109" s="7" t="n">
-        <v>7500</v>
+        <v>7378</v>
       </c>
       <c r="W109" s="7" t="n">
-        <v>3750</v>
+        <v>3689</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>0</v>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:05</t>
+          <t>2026-05-08 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -109,7 +109,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,7 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="V5" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W5" s="7" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>1</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W6" s="10" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="V7" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W7" s="7" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W8" s="10" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>1</v>
       </c>
       <c r="V9" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W9" s="7" t="n">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="V10" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W10" s="10" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>1</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W11" s="7" t="n">
         <v>0</v>
@@ -1389,7 +1389,7 @@
         <v>1</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W12" s="10" t="n">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>1</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W13" s="7" t="n">
         <v>3638</v>
@@ -1565,10 +1565,10 @@
         <v>1</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W14" s="10" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>1</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W15" s="7" t="n">
         <v>0</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="V16" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W16" s="10" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W17" s="7" t="n">
         <v>0</v>
@@ -1917,10 +1917,10 @@
         <v>1</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W18" s="10" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="X18" s="10" t="n">
         <v>0</v>
@@ -2005,10 +2005,10 @@
         <v>1</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X19" s="7" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W20" s="10" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
         <v>1</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W21" s="7" t="n">
         <v>0</v>
@@ -2269,10 +2269,10 @@
         <v>1</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W22" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>0</v>
@@ -2357,10 +2357,10 @@
         <v>1</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X23" s="7" t="n">
         <v>0</v>
@@ -2445,10 +2445,10 @@
         <v>1</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W24" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>1</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W26" s="10" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W27" s="7" t="n">
         <v>0</v>
@@ -2797,7 +2797,7 @@
         <v>1</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W28" s="10" t="n">
         <v>0</v>
@@ -2885,10 +2885,10 @@
         <v>1</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>0</v>
@@ -2973,10 +2973,10 @@
         <v>1</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>1</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W31" s="7" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>1</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W32" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="V33" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W33" s="7" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>1</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W34" s="10" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>1</v>
       </c>
       <c r="V35" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W35" s="7" t="n">
         <v>0</v>
@@ -3505,10 +3505,10 @@
         <v>1</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W36" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>1</v>
       </c>
       <c r="V37" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W37" s="7" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
         <v>1</v>
       </c>
       <c r="V38" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W38" s="10" t="n">
         <v>0</v>
@@ -3769,7 +3769,7 @@
         <v>1</v>
       </c>
       <c r="V39" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W39" s="7" t="n">
         <v>0</v>
@@ -3857,7 +3857,7 @@
         <v>1</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W40" s="10" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W41" s="7" t="n">
         <v>0</v>
@@ -4033,10 +4033,10 @@
         <v>1</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W42" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         <v>1</v>
       </c>
       <c r="V43" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W43" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X43" s="7" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W44" s="10" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         <v>1</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W45" s="7" t="n">
         <v>0</v>
@@ -4385,10 +4385,10 @@
         <v>1</v>
       </c>
       <c r="V46" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W46" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="V47" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W47" s="7" t="n">
         <v>0</v>
@@ -4561,7 +4561,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W48" s="10" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="V49" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W49" s="7" t="n">
         <v>0</v>
@@ -4737,10 +4737,10 @@
         <v>1</v>
       </c>
       <c r="V50" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W50" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>1</v>
       </c>
       <c r="V51" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W51" s="7" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
         <v>1</v>
       </c>
       <c r="V52" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W52" s="10" t="n">
         <v>0</v>
@@ -5005,10 +5005,10 @@
         <v>1</v>
       </c>
       <c r="V53" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W53" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="X53" s="7" t="n">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W54" s="10" t="n">
         <v>0</v>
@@ -5181,10 +5181,10 @@
         <v>1</v>
       </c>
       <c r="V55" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W55" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>0</v>
@@ -5269,7 +5269,7 @@
         <v>1</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W56" s="10" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="V57" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W57" s="7" t="n">
         <v>0</v>
@@ -5445,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="V58" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W58" s="10" t="n">
         <v>0</v>
@@ -5533,7 +5533,7 @@
         <v>1</v>
       </c>
       <c r="V59" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W59" s="7" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W60" s="10" t="n">
         <v>0</v>
@@ -5709,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="V61" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W61" s="7" t="n">
         <v>0</v>
@@ -5797,10 +5797,10 @@
         <v>1</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>0</v>
@@ -5885,7 +5885,7 @@
         <v>1</v>
       </c>
       <c r="V63" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W63" s="7" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         <v>1</v>
       </c>
       <c r="V64" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W64" s="10" t="n">
         <v>0</v>
@@ -6065,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="V65" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W65" s="7" t="n">
         <v>0</v>
@@ -6153,7 +6153,7 @@
         <v>1</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W66" s="10" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>1</v>
       </c>
       <c r="V67" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W67" s="7" t="n">
         <v>0</v>
@@ -6329,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="V68" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W68" s="10" t="n">
         <v>0</v>
@@ -6417,7 +6417,7 @@
         <v>1</v>
       </c>
       <c r="V69" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W69" s="7" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="V70" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W70" s="10" t="n">
         <v>0</v>
@@ -6597,7 +6597,7 @@
         <v>1</v>
       </c>
       <c r="V71" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W71" s="7" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
         <v>1</v>
       </c>
       <c r="V72" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W72" s="10" t="n">
         <v>0</v>
@@ -6773,7 +6773,7 @@
         <v>1</v>
       </c>
       <c r="V73" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W73" s="7" t="n">
         <v>0</v>
@@ -6861,10 +6861,10 @@
         <v>1</v>
       </c>
       <c r="V74" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W74" s="10" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="V75" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W75" s="7" t="n">
         <v>0</v>
@@ -7037,7 +7037,7 @@
         <v>1</v>
       </c>
       <c r="V76" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W76" s="10" t="n">
         <v>0</v>
@@ -7125,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="V77" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W77" s="7" t="n">
         <v>0</v>
@@ -7217,7 +7217,7 @@
         <v>1</v>
       </c>
       <c r="V78" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W78" s="10" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="V79" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W79" s="7" t="n">
         <v>0</v>
@@ -7393,7 +7393,7 @@
         <v>1</v>
       </c>
       <c r="V80" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W80" s="10" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="V81" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W81" s="7" t="n">
         <v>0</v>
@@ -7573,7 +7573,7 @@
         <v>1</v>
       </c>
       <c r="V82" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W82" s="10" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="V83" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W83" s="7" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>1</v>
       </c>
       <c r="V84" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W84" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X84" s="10" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="Y84" s="10" t="n">
         <v>0</v>
@@ -7841,13 +7841,13 @@
         <v>1</v>
       </c>
       <c r="V85" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X85" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="Y85" s="7" t="n">
         <v>0</v>
@@ -7929,13 +7929,13 @@
         <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="X86" s="10" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="Y86" s="10" t="n">
         <v>0</v>
@@ -8017,10 +8017,10 @@
         <v>1</v>
       </c>
       <c r="V87" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W87" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>0</v>
@@ -8105,10 +8105,10 @@
         <v>1</v>
       </c>
       <c r="V88" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W88" s="10" t="n">
-        <v>6500</v>
+        <v>6546</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>0</v>
@@ -8193,7 +8193,7 @@
         <v>1</v>
       </c>
       <c r="V89" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W89" s="7" t="n">
         <v>0</v>
@@ -8281,10 +8281,10 @@
         <v>1</v>
       </c>
       <c r="V90" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W90" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>0</v>
@@ -8369,10 +8369,10 @@
         <v>1</v>
       </c>
       <c r="V91" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W91" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>0</v>
@@ -8457,10 +8457,10 @@
         <v>1</v>
       </c>
       <c r="V92" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W92" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>0</v>
@@ -8469,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="Z92" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="93">
@@ -8545,10 +8545,10 @@
         <v>1</v>
       </c>
       <c r="V93" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W93" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="X93" s="7" t="n">
         <v>0</v>
@@ -9869,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="V108" s="10" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>0</v>
@@ -9957,10 +9957,10 @@
         <v>1</v>
       </c>
       <c r="V109" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="W109" s="7" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>0</v>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:26</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trip_Detail" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trip_Detail'!$A$4:$Z$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trip_Detail'!$A$4:$Z$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z109"/>
+  <dimension ref="A1:Z107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:26</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>
@@ -9796,184 +9796,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B108" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C108" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>BigC</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
-        </is>
-      </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>13.8</t>
-        </is>
-      </c>
-      <c r="H108" s="9" t="inlineStr">
-        <is>
-          <t>14.9</t>
-        </is>
-      </c>
-      <c r="I108" s="8" t="n">
-        <v>46143.26266203704</v>
-      </c>
-      <c r="J108" s="8" t="n">
-        <v>46143.48762731482</v>
-      </c>
-      <c r="K108" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L108" s="8" t="n">
-        <v>46143.56759259259</v>
-      </c>
-      <c r="M108" s="8" t="n">
-        <v>46143.6196875</v>
-      </c>
-      <c r="N108" s="9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O108" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P108" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" s="9" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="S108" s="9" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="T108" s="9" t="n"/>
-      <c r="U108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V108" s="10" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="W108" s="10" t="n">
-        <v>3716</v>
-      </c>
-      <c r="X108" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y108" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z108" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B109" s="5" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C109" s="5" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>7.14</t>
-        </is>
-      </c>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>7.14</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="n">
-        <v>46143.82527777777</v>
-      </c>
-      <c r="J109" s="5" t="n">
-        <v>46143.89219907407</v>
-      </c>
-      <c r="K109" s="6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="L109" s="5" t="n">
-        <v>46143.96318287037</v>
-      </c>
-      <c r="M109" s="5" t="n">
-        <v>46143.97673611111</v>
-      </c>
-      <c r="N109" s="6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O109" s="6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P109" s="6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Q109" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" s="6" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="S109" s="6" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="T109" s="6" t="n"/>
-      <c r="U109" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V109" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="W109" s="7" t="n">
-        <v>3716</v>
-      </c>
-      <c r="X109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z109" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:Z109"/>
+  <autoFilter ref="A4:Z107"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:09</t>
+          <t>2026-05-26 13:16</t>
         </is>
       </c>
     </row>
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="V5" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X5" s="7" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>1</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>0</v>
@@ -945,16 +945,16 @@
         <v>1</v>
       </c>
       <c r="V7" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="Z7" s="7" t="n">
         <v>0</v>
@@ -1033,16 +1033,16 @@
         <v>1</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="10" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="Z8" s="10" t="n">
         <v>0</v>
@@ -1121,16 +1121,16 @@
         <v>1</v>
       </c>
       <c r="V9" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="Z9" s="7" t="n">
         <v>0</v>
@@ -1209,10 +1209,10 @@
         <v>1</v>
       </c>
       <c r="V10" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>0</v>
@@ -1297,10 +1297,10 @@
         <v>1</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>7432</v>
+        <v>6598</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W12" s="10" t="n">
         <v>0</v>
@@ -1473,16 +1473,16 @@
         <v>1</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y13" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="Z13" s="7" t="n">
         <v>0</v>
@@ -1561,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W14" s="10" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>1</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>0</v>
@@ -1737,10 +1737,10 @@
         <v>1</v>
       </c>
       <c r="V16" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W16" s="10" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>0</v>
@@ -1825,10 +1825,10 @@
         <v>1</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X17" s="7" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W18" s="10" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>1</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X19" s="7" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W20" s="10" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>1</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X21" s="7" t="n">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         <v>1</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W22" s="10" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W23" s="7" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W24" s="10" t="n">
         <v>0</v>
@@ -2529,10 +2529,10 @@
         <v>1</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>3716</v>
+        <v>3299</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>0</v>
@@ -2617,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W26" s="10" t="n">
         <v>0</v>
@@ -2705,10 +2705,10 @@
         <v>1</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>3661</v>
+        <v>3250</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>7432.03</v>
+        <v>6597.5</v>
       </c>
       <c r="W28" s="10" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         <v>1</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W29" s="7" t="n">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W30" s="10" t="n">
         <v>0</v>
@@ -3057,10 +3057,10 @@
         <v>1</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>3661</v>
+        <v>3250</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>0</v>
@@ -3145,10 +3145,10 @@
         <v>1</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W32" s="10" t="n">
-        <v>3661</v>
+        <v>3250</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="V33" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W33" s="7" t="n">
         <v>0</v>
@@ -3321,10 +3321,10 @@
         <v>1</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W34" s="10" t="n">
-        <v>3661</v>
+        <v>3250</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="V35" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W35" s="7" t="n">
         <v>0</v>
@@ -3497,10 +3497,10 @@
         <v>1</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W36" s="10" t="n">
-        <v>7322</v>
+        <v>6500</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="V37" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W37" s="7" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="V38" s="10" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W38" s="10" t="n">
         <v>0</v>
@@ -3761,10 +3761,10 @@
         <v>1</v>
       </c>
       <c r="V39" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W39" s="7" t="n">
-        <v>7322</v>
+        <v>6500</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W40" s="10" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W41" s="7" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>1</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W42" s="10" t="n">
         <v>0</v>
@@ -4113,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="V43" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W43" s="7" t="n">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="10" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W44" s="10" t="n">
         <v>0</v>
@@ -4289,10 +4289,10 @@
         <v>1</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W45" s="7" t="n">
-        <v>3661</v>
+        <v>3250</v>
       </c>
       <c r="X45" s="7" t="n">
         <v>0</v>
@@ -4377,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="V46" s="10" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W46" s="10" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="V47" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W47" s="7" t="n">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="10" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W48" s="10" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="V49" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W49" s="7" t="n">
         <v>0</v>
@@ -4729,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="V50" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W50" s="10" t="n">
         <v>0</v>
@@ -4817,10 +4817,10 @@
         <v>1</v>
       </c>
       <c r="V51" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W51" s="7" t="n">
-        <v>3661</v>
+        <v>3299</v>
       </c>
       <c r="X51" s="7" t="n">
         <v>0</v>
@@ -4905,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="V52" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W52" s="10" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="V53" s="7" t="n">
-        <v>7322.2</v>
+        <v>6500</v>
       </c>
       <c r="W53" s="7" t="n">
         <v>0</v>
@@ -5081,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W54" s="10" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
         <v>1</v>
       </c>
       <c r="V55" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W55" s="7" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W56" s="10" t="n">
         <v>0</v>
@@ -5349,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="V57" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W57" s="7" t="n">
         <v>0</v>
@@ -5437,10 +5437,10 @@
         <v>1</v>
       </c>
       <c r="V58" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W58" s="10" t="n">
-        <v>3661</v>
+        <v>3299</v>
       </c>
       <c r="X58" s="10" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         <v>1</v>
       </c>
       <c r="V59" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W59" s="7" t="n">
         <v>0</v>
@@ -5613,10 +5613,10 @@
         <v>1</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W60" s="10" t="n">
-        <v>3661</v>
+        <v>3299</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         <v>1</v>
       </c>
       <c r="V61" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W61" s="7" t="n">
         <v>0</v>
@@ -5789,10 +5789,10 @@
         <v>1</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>3661</v>
+        <v>3299</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>0</v>
@@ -5877,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="V63" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W63" s="7" t="n">
         <v>0</v>
@@ -5965,7 +5965,7 @@
         <v>1</v>
       </c>
       <c r="V64" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W64" s="10" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1</v>
       </c>
       <c r="V65" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W65" s="7" t="n">
         <v>0</v>
@@ -6141,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W66" s="10" t="n">
         <v>0</v>
@@ -6229,10 +6229,10 @@
         <v>1</v>
       </c>
       <c r="V67" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W67" s="7" t="n">
-        <v>3661</v>
+        <v>3299</v>
       </c>
       <c r="X67" s="7" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>1</v>
       </c>
       <c r="V68" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W68" s="10" t="n">
         <v>0</v>
@@ -6405,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="V69" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W69" s="7" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="V70" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W70" s="10" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
         <v>1</v>
       </c>
       <c r="V71" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W71" s="7" t="n">
         <v>0</v>
@@ -6669,7 +6669,7 @@
         <v>1</v>
       </c>
       <c r="V72" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W72" s="10" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>1</v>
       </c>
       <c r="V73" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W73" s="7" t="n">
         <v>0</v>
@@ -6845,7 +6845,7 @@
         <v>1</v>
       </c>
       <c r="V74" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W74" s="10" t="n">
         <v>0</v>
@@ -6933,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="V75" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W75" s="7" t="n">
         <v>0</v>
@@ -7021,10 +7021,10 @@
         <v>1</v>
       </c>
       <c r="V76" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W76" s="10" t="n">
-        <v>3661</v>
+        <v>3299</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>1</v>
       </c>
       <c r="V77" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W77" s="7" t="n">
         <v>0</v>
@@ -7197,10 +7197,10 @@
         <v>1</v>
       </c>
       <c r="V78" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W78" s="10" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X78" s="10" t="n">
         <v>0</v>
@@ -7285,10 +7285,10 @@
         <v>1</v>
       </c>
       <c r="V79" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W79" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X79" s="7" t="n">
         <v>0</v>
@@ -7373,7 +7373,7 @@
         <v>1</v>
       </c>
       <c r="V80" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W80" s="10" t="n">
         <v>0</v>
@@ -7461,10 +7461,10 @@
         <v>1</v>
       </c>
       <c r="V81" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W81" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>0</v>
@@ -7549,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="V82" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W82" s="10" t="n">
         <v>0</v>
@@ -7637,10 +7637,10 @@
         <v>1</v>
       </c>
       <c r="V83" s="7" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W83" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X83" s="7" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>1</v>
       </c>
       <c r="V84" s="10" t="n">
-        <v>7322.2</v>
+        <v>6597.5</v>
       </c>
       <c r="W84" s="10" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>0</v>
@@ -7813,7 +7813,7 @@
         <v>1</v>
       </c>
       <c r="V85" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W85" s="7" t="n">
         <v>0</v>
@@ -7901,10 +7901,10 @@
         <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W86" s="10" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="V87" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W87" s="7" t="n">
         <v>0</v>
@@ -8077,7 +8077,7 @@
         <v>1</v>
       </c>
       <c r="V88" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W88" s="10" t="n">
         <v>0</v>
@@ -8165,10 +8165,10 @@
         <v>1</v>
       </c>
       <c r="V89" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W89" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>1</v>
       </c>
       <c r="V90" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W90" s="10" t="n">
         <v>0</v>
@@ -8341,10 +8341,10 @@
         <v>1</v>
       </c>
       <c r="V91" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W91" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>1</v>
       </c>
       <c r="V92" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W92" s="10" t="n">
         <v>0</v>
@@ -8517,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="V93" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W93" s="7" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>1</v>
       </c>
       <c r="V94" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W94" s="10" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
         <v>1</v>
       </c>
       <c r="V95" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W95" s="7" t="n">
         <v>0</v>
@@ -8781,10 +8781,10 @@
         <v>1</v>
       </c>
       <c r="V96" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W96" s="10" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>0</v>
@@ -8869,10 +8869,10 @@
         <v>1</v>
       </c>
       <c r="V97" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W97" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X97" s="7" t="n">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         <v>1</v>
       </c>
       <c r="V98" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W98" s="10" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         <v>1</v>
       </c>
       <c r="V99" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W99" s="7" t="n">
         <v>0</v>
@@ -9133,10 +9133,10 @@
         <v>1</v>
       </c>
       <c r="V100" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W100" s="10" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>0</v>
@@ -9221,10 +9221,10 @@
         <v>1</v>
       </c>
       <c r="V101" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W101" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>0</v>
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="V102" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W102" s="10" t="n">
-        <v>7322</v>
+        <v>6696</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>0</v>
@@ -9397,7 +9397,7 @@
         <v>1</v>
       </c>
       <c r="V103" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W103" s="7" t="n">
         <v>0</v>
@@ -9485,7 +9485,7 @@
         <v>1</v>
       </c>
       <c r="V104" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W104" s="10" t="n">
         <v>0</v>
@@ -9573,10 +9573,10 @@
         <v>1</v>
       </c>
       <c r="V105" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W105" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>0</v>
@@ -9661,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="V106" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W106" s="10" t="n">
         <v>0</v>
@@ -9749,10 +9749,10 @@
         <v>1</v>
       </c>
       <c r="V107" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W107" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>0</v>
@@ -9837,7 +9837,7 @@
         <v>1</v>
       </c>
       <c r="V108" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W108" s="10" t="n">
         <v>0</v>
@@ -9925,10 +9925,10 @@
         <v>1</v>
       </c>
       <c r="V109" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W109" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>0</v>
@@ -10013,7 +10013,7 @@
         <v>1</v>
       </c>
       <c r="V110" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W110" s="10" t="n">
         <v>0</v>
@@ -10101,10 +10101,10 @@
         <v>1</v>
       </c>
       <c r="V111" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W111" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>0</v>
@@ -10189,7 +10189,7 @@
         <v>1</v>
       </c>
       <c r="V112" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W112" s="10" t="n">
         <v>0</v>
@@ -10277,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="V113" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W113" s="7" t="n">
         <v>0</v>
@@ -10365,10 +10365,10 @@
         <v>1</v>
       </c>
       <c r="V114" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W114" s="10" t="n">
-        <v>7322</v>
+        <v>6696</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>0</v>
@@ -10453,7 +10453,7 @@
         <v>1</v>
       </c>
       <c r="V115" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W115" s="7" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
         <v>1</v>
       </c>
       <c r="V116" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W116" s="10" t="n">
         <v>0</v>
@@ -10629,7 +10629,7 @@
         <v>1</v>
       </c>
       <c r="V117" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W117" s="7" t="n">
         <v>0</v>
@@ -10717,7 +10717,7 @@
         <v>1</v>
       </c>
       <c r="V118" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W118" s="10" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
         <v>1</v>
       </c>
       <c r="V119" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W119" s="7" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>1</v>
       </c>
       <c r="V120" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W120" s="10" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>0</v>
@@ -10981,7 +10981,7 @@
         <v>1</v>
       </c>
       <c r="V121" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W121" s="7" t="n">
         <v>0</v>
@@ -11073,7 +11073,7 @@
         <v>1</v>
       </c>
       <c r="V122" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W122" s="10" t="n">
         <v>0</v>
@@ -11161,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="V123" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W123" s="7" t="n">
         <v>0</v>
@@ -11249,10 +11249,10 @@
         <v>1</v>
       </c>
       <c r="V124" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W124" s="10" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>0</v>
@@ -11337,10 +11337,10 @@
         <v>1</v>
       </c>
       <c r="V125" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W125" s="7" t="n">
-        <v>3661</v>
+        <v>3348</v>
       </c>
       <c r="X125" s="7" t="n">
         <v>0</v>
@@ -11425,10 +11425,10 @@
         <v>1</v>
       </c>
       <c r="V126" s="10" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W126" s="10" t="n">
-        <v>7322</v>
+        <v>6696</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>0</v>
@@ -11513,7 +11513,7 @@
         <v>1</v>
       </c>
       <c r="V127" s="7" t="n">
-        <v>7322.2</v>
+        <v>6696.46</v>
       </c>
       <c r="W127" s="7" t="n">
         <v>0</v>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:16</t>
+          <t>2026-05-26 13:20</t>
         </is>
       </c>
     </row>
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="V5" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X5" s="7" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>1</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>0</v>
@@ -945,16 +945,16 @@
         <v>1</v>
       </c>
       <c r="V7" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="Z7" s="7" t="n">
         <v>0</v>
@@ -1033,16 +1033,16 @@
         <v>1</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="10" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="Z8" s="10" t="n">
         <v>0</v>
@@ -1121,16 +1121,16 @@
         <v>1</v>
       </c>
       <c r="V9" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="Z9" s="7" t="n">
         <v>0</v>
@@ -1209,10 +1209,10 @@
         <v>1</v>
       </c>
       <c r="V10" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>0</v>
@@ -1297,10 +1297,10 @@
         <v>1</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>6598</v>
+        <v>7432</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W12" s="10" t="n">
         <v>0</v>
@@ -1473,16 +1473,16 @@
         <v>1</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y13" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="Z13" s="7" t="n">
         <v>0</v>
@@ -1561,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W14" s="10" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>1</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>0</v>
@@ -1737,10 +1737,10 @@
         <v>1</v>
       </c>
       <c r="V16" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W16" s="10" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>0</v>
@@ -1825,10 +1825,10 @@
         <v>1</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X17" s="7" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W18" s="10" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>1</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X19" s="7" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W20" s="10" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>1</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X21" s="7" t="n">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         <v>1</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W22" s="10" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W23" s="7" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W24" s="10" t="n">
         <v>0</v>
@@ -2529,10 +2529,10 @@
         <v>1</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>0</v>
@@ -2617,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W26" s="10" t="n">
         <v>0</v>
@@ -2705,10 +2705,10 @@
         <v>1</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>3250</v>
+        <v>3661</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W28" s="10" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         <v>1</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W29" s="7" t="n">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W30" s="10" t="n">
         <v>0</v>
@@ -3057,10 +3057,10 @@
         <v>1</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>3250</v>
+        <v>3661</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>0</v>
@@ -3145,10 +3145,10 @@
         <v>1</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W32" s="10" t="n">
-        <v>3250</v>
+        <v>3661</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="V33" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W33" s="7" t="n">
         <v>0</v>
@@ -3321,10 +3321,10 @@
         <v>1</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W34" s="10" t="n">
-        <v>3250</v>
+        <v>3661</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="V35" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W35" s="7" t="n">
         <v>0</v>
@@ -3497,10 +3497,10 @@
         <v>1</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W36" s="10" t="n">
-        <v>6500</v>
+        <v>7322</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="V37" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W37" s="7" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="V38" s="10" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W38" s="10" t="n">
         <v>0</v>
@@ -3761,10 +3761,10 @@
         <v>1</v>
       </c>
       <c r="V39" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W39" s="7" t="n">
-        <v>6500</v>
+        <v>7322</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W40" s="10" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W41" s="7" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>1</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W42" s="10" t="n">
         <v>0</v>
@@ -4113,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="V43" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W43" s="7" t="n">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="10" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W44" s="10" t="n">
         <v>0</v>
@@ -4289,10 +4289,10 @@
         <v>1</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W45" s="7" t="n">
-        <v>3250</v>
+        <v>3661</v>
       </c>
       <c r="X45" s="7" t="n">
         <v>0</v>
@@ -4377,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="V46" s="10" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W46" s="10" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="V47" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W47" s="7" t="n">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="10" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W48" s="10" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="V49" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W49" s="7" t="n">
         <v>0</v>
@@ -4729,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="V50" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W50" s="10" t="n">
         <v>0</v>
@@ -4817,10 +4817,10 @@
         <v>1</v>
       </c>
       <c r="V51" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W51" s="7" t="n">
-        <v>3299</v>
+        <v>3716</v>
       </c>
       <c r="X51" s="7" t="n">
         <v>0</v>
@@ -4905,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="V52" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W52" s="10" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="V53" s="7" t="n">
-        <v>6500</v>
+        <v>7322.2</v>
       </c>
       <c r="W53" s="7" t="n">
         <v>0</v>
@@ -5081,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W54" s="10" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
         <v>1</v>
       </c>
       <c r="V55" s="7" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W55" s="7" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W56" s="10" t="n">
         <v>0</v>
@@ -5349,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="V57" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W57" s="7" t="n">
         <v>0</v>
@@ -5437,10 +5437,10 @@
         <v>1</v>
       </c>
       <c r="V58" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W58" s="10" t="n">
-        <v>3299</v>
+        <v>3772</v>
       </c>
       <c r="X58" s="10" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         <v>1</v>
       </c>
       <c r="V59" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W59" s="7" t="n">
         <v>0</v>
@@ -5613,10 +5613,10 @@
         <v>1</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>6597.5</v>
+        <v>7432.03</v>
       </c>
       <c r="W60" s="10" t="n">
-        <v>3299</v>
+        <v>3772</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         <v>1</v>
       </c>
       <c r="V61" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W61" s="7" t="n">
         <v>0</v>
@@ -5789,10 +5789,10 @@
         <v>1</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>3299</v>
+        <v>3772</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>0</v>
@@ -5877,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="V63" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W63" s="7" t="n">
         <v>0</v>
@@ -5965,7 +5965,7 @@
         <v>1</v>
       </c>
       <c r="V64" s="10" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W64" s="10" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1</v>
       </c>
       <c r="V65" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W65" s="7" t="n">
         <v>0</v>
@@ -6141,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W66" s="10" t="n">
         <v>0</v>
@@ -6229,10 +6229,10 @@
         <v>1</v>
       </c>
       <c r="V67" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W67" s="7" t="n">
-        <v>3299</v>
+        <v>3772</v>
       </c>
       <c r="X67" s="7" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>1</v>
       </c>
       <c r="V68" s="10" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W68" s="10" t="n">
         <v>0</v>
@@ -6405,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="V69" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W69" s="7" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="V70" s="10" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W70" s="10" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
         <v>1</v>
       </c>
       <c r="V71" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W71" s="7" t="n">
         <v>0</v>
@@ -6669,7 +6669,7 @@
         <v>1</v>
       </c>
       <c r="V72" s="10" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W72" s="10" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>1</v>
       </c>
       <c r="V73" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W73" s="7" t="n">
         <v>0</v>
@@ -6845,7 +6845,7 @@
         <v>1</v>
       </c>
       <c r="V74" s="10" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W74" s="10" t="n">
         <v>0</v>
@@ -6933,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="V75" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W75" s="7" t="n">
         <v>0</v>
@@ -7021,10 +7021,10 @@
         <v>1</v>
       </c>
       <c r="V76" s="10" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W76" s="10" t="n">
-        <v>3299</v>
+        <v>3772</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>1</v>
       </c>
       <c r="V77" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W77" s="7" t="n">
         <v>0</v>
@@ -7197,10 +7197,10 @@
         <v>1</v>
       </c>
       <c r="V78" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W78" s="10" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X78" s="10" t="n">
         <v>0</v>
@@ -7285,10 +7285,10 @@
         <v>1</v>
       </c>
       <c r="V79" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W79" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X79" s="7" t="n">
         <v>0</v>
@@ -7373,7 +7373,7 @@
         <v>1</v>
       </c>
       <c r="V80" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W80" s="10" t="n">
         <v>0</v>
@@ -7461,10 +7461,10 @@
         <v>1</v>
       </c>
       <c r="V81" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W81" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>0</v>
@@ -7549,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="V82" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W82" s="10" t="n">
         <v>0</v>
@@ -7637,10 +7637,10 @@
         <v>1</v>
       </c>
       <c r="V83" s="7" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W83" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X83" s="7" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>1</v>
       </c>
       <c r="V84" s="10" t="n">
-        <v>6597.5</v>
+        <v>7543.52</v>
       </c>
       <c r="W84" s="10" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>0</v>
@@ -7813,7 +7813,7 @@
         <v>1</v>
       </c>
       <c r="V85" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W85" s="7" t="n">
         <v>0</v>
@@ -7901,10 +7901,10 @@
         <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W86" s="10" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="V87" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W87" s="7" t="n">
         <v>0</v>
@@ -8077,7 +8077,7 @@
         <v>1</v>
       </c>
       <c r="V88" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W88" s="10" t="n">
         <v>0</v>
@@ -8165,10 +8165,10 @@
         <v>1</v>
       </c>
       <c r="V89" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W89" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>1</v>
       </c>
       <c r="V90" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W90" s="10" t="n">
         <v>0</v>
@@ -8341,10 +8341,10 @@
         <v>1</v>
       </c>
       <c r="V91" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W91" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>1</v>
       </c>
       <c r="V92" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W92" s="10" t="n">
         <v>0</v>
@@ -8517,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="V93" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W93" s="7" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>1</v>
       </c>
       <c r="V94" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W94" s="10" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
         <v>1</v>
       </c>
       <c r="V95" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W95" s="7" t="n">
         <v>0</v>
@@ -8781,10 +8781,10 @@
         <v>1</v>
       </c>
       <c r="V96" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W96" s="10" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>0</v>
@@ -8869,10 +8869,10 @@
         <v>1</v>
       </c>
       <c r="V97" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W97" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X97" s="7" t="n">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         <v>1</v>
       </c>
       <c r="V98" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W98" s="10" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         <v>1</v>
       </c>
       <c r="V99" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W99" s="7" t="n">
         <v>0</v>
@@ -9133,10 +9133,10 @@
         <v>1</v>
       </c>
       <c r="V100" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W100" s="10" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>0</v>
@@ -9221,10 +9221,10 @@
         <v>1</v>
       </c>
       <c r="V101" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W101" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>0</v>
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="V102" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W102" s="10" t="n">
-        <v>6696</v>
+        <v>7656</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>0</v>
@@ -9397,7 +9397,7 @@
         <v>1</v>
       </c>
       <c r="V103" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W103" s="7" t="n">
         <v>0</v>
@@ -9485,7 +9485,7 @@
         <v>1</v>
       </c>
       <c r="V104" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W104" s="10" t="n">
         <v>0</v>
@@ -9573,10 +9573,10 @@
         <v>1</v>
       </c>
       <c r="V105" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W105" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>0</v>
@@ -9661,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="V106" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W106" s="10" t="n">
         <v>0</v>
@@ -9749,10 +9749,10 @@
         <v>1</v>
       </c>
       <c r="V107" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W107" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>0</v>
@@ -9837,7 +9837,7 @@
         <v>1</v>
       </c>
       <c r="V108" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W108" s="10" t="n">
         <v>0</v>
@@ -9925,10 +9925,10 @@
         <v>1</v>
       </c>
       <c r="V109" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W109" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>0</v>
@@ -10013,7 +10013,7 @@
         <v>1</v>
       </c>
       <c r="V110" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W110" s="10" t="n">
         <v>0</v>
@@ -10101,10 +10101,10 @@
         <v>1</v>
       </c>
       <c r="V111" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W111" s="7" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>0</v>
@@ -10189,7 +10189,7 @@
         <v>1</v>
       </c>
       <c r="V112" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W112" s="10" t="n">
         <v>0</v>
@@ -10277,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="V113" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W113" s="7" t="n">
         <v>0</v>
@@ -10365,10 +10365,10 @@
         <v>1</v>
       </c>
       <c r="V114" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W114" s="10" t="n">
-        <v>6696</v>
+        <v>7656</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>0</v>
@@ -10453,7 +10453,7 @@
         <v>1</v>
       </c>
       <c r="V115" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W115" s="7" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
         <v>1</v>
       </c>
       <c r="V116" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W116" s="10" t="n">
         <v>0</v>
@@ -10629,7 +10629,7 @@
         <v>1</v>
       </c>
       <c r="V117" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W117" s="7" t="n">
         <v>0</v>
@@ -10717,7 +10717,7 @@
         <v>1</v>
       </c>
       <c r="V118" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W118" s="10" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
         <v>1</v>
       </c>
       <c r="V119" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W119" s="7" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>1</v>
       </c>
       <c r="V120" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W120" s="10" t="n">
-        <v>3348</v>
+        <v>3828</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>0</v>
@@ -10981,7 +10981,7 @@
         <v>1</v>
       </c>
       <c r="V121" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W121" s="7" t="n">
         <v>0</v>
@@ -11073,7 +11073,7 @@
         <v>1</v>
       </c>
       <c r="V122" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W122" s="10" t="n">
         <v>0</v>
@@ -11161,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="V123" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W123" s="7" t="n">
         <v>0</v>
@@ -11249,10 +11249,10 @@
         <v>1</v>
       </c>
       <c r="V124" s="10" t="n">
-        <v>6696.46</v>
+        <v>7543.52</v>
       </c>
       <c r="W124" s="10" t="n">
-        <v>3348</v>
+        <v>3772</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>0</v>
@@ -11337,10 +11337,10 @@
         <v>1</v>
       </c>
       <c r="V125" s="7" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W125" s="7" t="n">
-        <v>3348</v>
+        <v>3772</v>
       </c>
       <c r="X125" s="7" t="n">
         <v>0</v>
@@ -11425,10 +11425,10 @@
         <v>1</v>
       </c>
       <c r="V126" s="10" t="n">
-        <v>6696.46</v>
+        <v>7656.67</v>
       </c>
       <c r="W126" s="10" t="n">
-        <v>6696</v>
+        <v>7544</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>0</v>
@@ -11513,7 +11513,7 @@
         <v>1</v>
       </c>
       <c r="V127" s="7" t="n">
-        <v>6696.46</v>
+        <v>7543.52</v>
       </c>
       <c r="W127" s="7" t="n">
         <v>0</v>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Trip_Detail" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trip_Detail'!$A$4:$Z$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trip_Detail'!$A$4:$Z$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z127"/>
+  <dimension ref="A1:Z158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:20</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="V5" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X5" s="7" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         <v>1</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>0</v>
@@ -945,16 +945,16 @@
         <v>1</v>
       </c>
       <c r="V7" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="7" t="n">
-        <v>3716</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="7" t="n">
         <v>0</v>
@@ -1033,16 +1033,16 @@
         <v>1</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="10" t="n">
-        <v>3716</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="10" t="n">
         <v>0</v>
@@ -1121,16 +1121,16 @@
         <v>1</v>
       </c>
       <c r="V9" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="7" t="n">
-        <v>3716</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="7" t="n">
         <v>0</v>
@@ -1209,10 +1209,10 @@
         <v>1</v>
       </c>
       <c r="V10" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>0</v>
@@ -1297,10 +1297,10 @@
         <v>1</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>7432</v>
+        <v>7264</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W12" s="10" t="n">
         <v>0</v>
@@ -1473,16 +1473,16 @@
         <v>1</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y13" s="7" t="n">
-        <v>3716</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="7" t="n">
         <v>0</v>
@@ -1561,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W14" s="10" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>1</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>0</v>
@@ -1737,10 +1737,10 @@
         <v>1</v>
       </c>
       <c r="V16" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W16" s="10" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>0</v>
@@ -1825,10 +1825,10 @@
         <v>1</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X17" s="7" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W18" s="10" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>1</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X19" s="7" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W20" s="10" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>1</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X21" s="7" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -2265,10 +2265,10 @@
         <v>1</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W22" s="10" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W23" s="7" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W24" s="10" t="n">
         <v>0</v>
@@ -2529,10 +2529,10 @@
         <v>1</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>0</v>
@@ -2617,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W26" s="10" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -2705,10 +2705,10 @@
         <v>1</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>3661</v>
+        <v>3584</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W28" s="10" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         <v>1</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W29" s="7" t="n">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W30" s="10" t="n">
         <v>0</v>
@@ -3057,10 +3057,10 @@
         <v>1</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>3661</v>
+        <v>3584</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -3145,10 +3145,10 @@
         <v>1</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W32" s="10" t="n">
-        <v>3661</v>
+        <v>3584</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="V33" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W33" s="7" t="n">
         <v>0</v>
@@ -3321,10 +3321,10 @@
         <v>1</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W34" s="10" t="n">
-        <v>3661</v>
+        <v>3584</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="V35" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W35" s="7" t="n">
         <v>0</v>
@@ -3497,10 +3497,10 @@
         <v>1</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W36" s="10" t="n">
-        <v>7322</v>
+        <v>7168</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="V37" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W37" s="7" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -3673,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="V38" s="10" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W38" s="10" t="n">
         <v>0</v>
@@ -3761,10 +3761,10 @@
         <v>1</v>
       </c>
       <c r="V39" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W39" s="7" t="n">
-        <v>7322</v>
+        <v>7168</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W40" s="10" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W41" s="7" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -4025,7 +4025,7 @@
         <v>1</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W42" s="10" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -4113,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="V43" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W43" s="7" t="n">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="10" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W44" s="10" t="n">
         <v>0</v>
@@ -4289,10 +4289,10 @@
         <v>1</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W45" s="7" t="n">
-        <v>3661</v>
+        <v>3584</v>
       </c>
       <c r="X45" s="7" t="n">
         <v>0</v>
@@ -4377,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="V46" s="10" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W46" s="10" t="n">
         <v>0</v>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -4465,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="V47" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W47" s="7" t="n">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="10" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W48" s="10" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="V49" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W49" s="7" t="n">
         <v>0</v>
@@ -4729,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="V50" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W50" s="10" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -4817,10 +4817,10 @@
         <v>1</v>
       </c>
       <c r="V51" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W51" s="7" t="n">
-        <v>3716</v>
+        <v>3632</v>
       </c>
       <c r="X51" s="7" t="n">
         <v>0</v>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -4905,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="V52" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W52" s="10" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="V53" s="7" t="n">
-        <v>7322.2</v>
+        <v>7168</v>
       </c>
       <c r="W53" s="7" t="n">
         <v>0</v>
@@ -5081,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W54" s="10" t="n">
         <v>0</v>
@@ -5173,7 +5173,7 @@
         <v>1</v>
       </c>
       <c r="V55" s="7" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W55" s="7" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W56" s="10" t="n">
         <v>0</v>
@@ -5349,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="V57" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W57" s="7" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -5437,10 +5437,10 @@
         <v>1</v>
       </c>
       <c r="V58" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W58" s="10" t="n">
-        <v>3772</v>
+        <v>3680</v>
       </c>
       <c r="X58" s="10" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
@@ -5525,7 +5525,7 @@
         <v>1</v>
       </c>
       <c r="V59" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W59" s="7" t="n">
         <v>0</v>
@@ -5613,10 +5613,10 @@
         <v>1</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>7432.03</v>
+        <v>7264</v>
       </c>
       <c r="W60" s="10" t="n">
-        <v>3772</v>
+        <v>3680</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         <v>1</v>
       </c>
       <c r="V61" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W61" s="7" t="n">
         <v>0</v>
@@ -5789,10 +5789,10 @@
         <v>1</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>3772</v>
+        <v>3680</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>0</v>
@@ -5877,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="V63" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W63" s="7" t="n">
         <v>0</v>
@@ -5965,7 +5965,7 @@
         <v>1</v>
       </c>
       <c r="V64" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W64" s="10" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1</v>
       </c>
       <c r="V65" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W65" s="7" t="n">
         <v>0</v>
@@ -6141,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W66" s="10" t="n">
         <v>0</v>
@@ -6229,10 +6229,10 @@
         <v>1</v>
       </c>
       <c r="V67" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W67" s="7" t="n">
-        <v>3772</v>
+        <v>3680</v>
       </c>
       <c r="X67" s="7" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>1</v>
       </c>
       <c r="V68" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W68" s="10" t="n">
         <v>0</v>
@@ -6405,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="V69" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W69" s="7" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="V70" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W70" s="10" t="n">
         <v>0</v>
@@ -6581,7 +6581,7 @@
         <v>1</v>
       </c>
       <c r="V71" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W71" s="7" t="n">
         <v>0</v>
@@ -6669,7 +6669,7 @@
         <v>1</v>
       </c>
       <c r="V72" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W72" s="10" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>1</v>
       </c>
       <c r="V73" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W73" s="7" t="n">
         <v>0</v>
@@ -6845,7 +6845,7 @@
         <v>1</v>
       </c>
       <c r="V74" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W74" s="10" t="n">
         <v>0</v>
@@ -6933,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="V75" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W75" s="7" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
@@ -7021,10 +7021,10 @@
         <v>1</v>
       </c>
       <c r="V76" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W76" s="10" t="n">
-        <v>3772</v>
+        <v>3680</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>1</v>
       </c>
       <c r="V77" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W77" s="7" t="n">
         <v>0</v>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>71-8001 ธนวัฒน์ หัวลาก10W</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
@@ -7197,10 +7197,10 @@
         <v>1</v>
       </c>
       <c r="V78" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W78" s="10" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X78" s="10" t="n">
         <v>0</v>
@@ -7285,10 +7285,10 @@
         <v>1</v>
       </c>
       <c r="V79" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W79" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X79" s="7" t="n">
         <v>0</v>
@@ -7373,7 +7373,7 @@
         <v>1</v>
       </c>
       <c r="V80" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W80" s="10" t="n">
         <v>0</v>
@@ -7461,10 +7461,10 @@
         <v>1</v>
       </c>
       <c r="V81" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W81" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>0</v>
@@ -7549,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="V82" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W82" s="10" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -7637,10 +7637,10 @@
         <v>1</v>
       </c>
       <c r="V83" s="7" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W83" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X83" s="7" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>1</v>
       </c>
       <c r="V84" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W84" s="10" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>0</v>
@@ -7813,7 +7813,7 @@
         <v>1</v>
       </c>
       <c r="V85" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W85" s="7" t="n">
         <v>0</v>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>71-8001 ธนวัฒน์ หัวลาก10W</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr">
@@ -7901,10 +7901,10 @@
         <v>1</v>
       </c>
       <c r="V86" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W86" s="10" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="V87" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W87" s="7" t="n">
         <v>0</v>
@@ -8077,7 +8077,7 @@
         <v>1</v>
       </c>
       <c r="V88" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W88" s="10" t="n">
         <v>0</v>
@@ -8165,10 +8165,10 @@
         <v>1</v>
       </c>
       <c r="V89" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W89" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>1</v>
       </c>
       <c r="V90" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W90" s="10" t="n">
         <v>0</v>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
@@ -8341,10 +8341,10 @@
         <v>1</v>
       </c>
       <c r="V91" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W91" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>1</v>
       </c>
       <c r="V92" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W92" s="10" t="n">
         <v>0</v>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>71-8001 ธนวัฒน์ หัวลาก10W</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -8517,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="V93" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W93" s="7" t="n">
         <v>0</v>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>71-8001 ธนวัฒน์ หัวลาก10W</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
@@ -8605,7 +8605,7 @@
         <v>1</v>
       </c>
       <c r="V94" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W94" s="10" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
         <v>1</v>
       </c>
       <c r="V95" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W95" s="7" t="n">
         <v>0</v>
@@ -8781,10 +8781,10 @@
         <v>1</v>
       </c>
       <c r="V96" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W96" s="10" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>0</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
@@ -8869,10 +8869,10 @@
         <v>1</v>
       </c>
       <c r="V97" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W97" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X97" s="7" t="n">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         <v>1</v>
       </c>
       <c r="V98" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W98" s="10" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>0</v>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>71-8001 ธนวัฒน์ หัวลาก10W</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
@@ -9045,7 +9045,7 @@
         <v>1</v>
       </c>
       <c r="V99" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W99" s="7" t="n">
         <v>0</v>
@@ -9133,10 +9133,10 @@
         <v>1</v>
       </c>
       <c r="V100" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W100" s="10" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>0</v>
@@ -9221,10 +9221,10 @@
         <v>1</v>
       </c>
       <c r="V101" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W101" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>0</v>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G102" s="9" t="inlineStr">
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="V102" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W102" s="10" t="n">
-        <v>7656</v>
+        <v>7456</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>0</v>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
@@ -9397,7 +9397,7 @@
         <v>1</v>
       </c>
       <c r="V103" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W103" s="7" t="n">
         <v>0</v>
@@ -9485,7 +9485,7 @@
         <v>1</v>
       </c>
       <c r="V104" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W104" s="10" t="n">
         <v>0</v>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>71-8001 ธนวัฒน์ หัวลาก10W</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
@@ -9573,10 +9573,10 @@
         <v>1</v>
       </c>
       <c r="V105" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W105" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>0</v>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>71-8001 ธนวัฒน์ หัวลาก10W</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G106" s="9" t="inlineStr">
@@ -9661,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="V106" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W106" s="10" t="n">
         <v>0</v>
@@ -9749,10 +9749,10 @@
         <v>1</v>
       </c>
       <c r="V107" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W107" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G108" s="9" t="inlineStr">
@@ -9837,7 +9837,7 @@
         <v>1</v>
       </c>
       <c r="V108" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W108" s="10" t="n">
         <v>0</v>
@@ -9925,10 +9925,10 @@
         <v>1</v>
       </c>
       <c r="V109" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W109" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>0</v>
@@ -10013,7 +10013,7 @@
         <v>1</v>
       </c>
       <c r="V110" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W110" s="10" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>71-8001 ธนวัฒน์ หัวลาก10W</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
@@ -10101,10 +10101,10 @@
         <v>1</v>
       </c>
       <c r="V111" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W111" s="7" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>0</v>
@@ -10189,7 +10189,7 @@
         <v>1</v>
       </c>
       <c r="V112" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W112" s="10" t="n">
         <v>0</v>
@@ -10277,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="V113" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W113" s="7" t="n">
         <v>0</v>
@@ -10365,10 +10365,10 @@
         <v>1</v>
       </c>
       <c r="V114" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W114" s="10" t="n">
-        <v>7656</v>
+        <v>7456</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>0</v>
@@ -10453,7 +10453,7 @@
         <v>1</v>
       </c>
       <c r="V115" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W115" s="7" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G116" s="9" t="inlineStr">
@@ -10541,7 +10541,7 @@
         <v>1</v>
       </c>
       <c r="V116" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W116" s="10" t="n">
         <v>0</v>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
@@ -10629,7 +10629,7 @@
         <v>1</v>
       </c>
       <c r="V117" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W117" s="7" t="n">
         <v>0</v>
@@ -10717,7 +10717,7 @@
         <v>1</v>
       </c>
       <c r="V118" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W118" s="10" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
         <v>1</v>
       </c>
       <c r="V119" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W119" s="7" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>1</v>
       </c>
       <c r="V120" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W120" s="10" t="n">
-        <v>3828</v>
+        <v>3728</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>0</v>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
@@ -10981,7 +10981,7 @@
         <v>1</v>
       </c>
       <c r="V121" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W121" s="7" t="n">
         <v>0</v>
@@ -11073,7 +11073,7 @@
         <v>1</v>
       </c>
       <c r="V122" s="10" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W122" s="10" t="n">
         <v>0</v>
@@ -11136,32 +11136,32 @@
         <v>46168.27104166667</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>46168.45107638889</v>
+        <v>46168.69186342593</v>
       </c>
       <c r="N123" s="6" t="n">
         <v>1.8</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>4.32</v>
+        <v>10.1</v>
       </c>
       <c r="P123" s="6" t="n">
-        <v>4.32</v>
+        <v>10.1</v>
       </c>
       <c r="Q123" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R123" s="6" t="n">
-        <v>17.43</v>
+        <v>23.21</v>
       </c>
       <c r="S123" s="6" t="n">
-        <v>17.43</v>
+        <v>23.21</v>
       </c>
       <c r="T123" s="6" t="n"/>
       <c r="U123" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V123" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W123" s="7" t="n">
         <v>0</v>
@@ -11224,35 +11224,35 @@
         <v>46168.41813657407</v>
       </c>
       <c r="M124" s="8" t="n">
-        <v>46168.4377662037</v>
+        <v>46168.79332175926</v>
       </c>
       <c r="N124" s="9" t="n">
         <v>1.87</v>
       </c>
       <c r="O124" s="9" t="n">
-        <v>0.47</v>
+        <v>9</v>
       </c>
       <c r="P124" s="9" t="n">
-        <v>0.47</v>
+        <v>9</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R124" s="9" t="n">
-        <v>4.9</v>
+        <v>13.43</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>4.9</v>
+        <v>13.43</v>
       </c>
       <c r="T124" s="9" t="n"/>
       <c r="U124" s="9" t="n">
         <v>1</v>
       </c>
       <c r="V124" s="10" t="n">
-        <v>7543.52</v>
+        <v>7360</v>
       </c>
       <c r="W124" s="10" t="n">
-        <v>3772</v>
+        <v>3680</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>0</v>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ว่าง หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
@@ -11337,10 +11337,10 @@
         <v>1</v>
       </c>
       <c r="V125" s="7" t="n">
-        <v>7656.67</v>
+        <v>7456</v>
       </c>
       <c r="W125" s="7" t="n">
-        <v>3772</v>
+        <v>7360</v>
       </c>
       <c r="X125" s="7" t="n">
         <v>0</v>
@@ -11354,81 +11354,81 @@
     </row>
     <row r="126">
       <c r="A126" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B126" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="C126" s="8" t="n">
         <v>46168</v>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="I126" s="8" t="n">
-        <v>46167.88145833334</v>
+        <v>46168.39633101852</v>
       </c>
       <c r="J126" s="8" t="n">
-        <v>46167.93736111111</v>
+        <v>46168.57978009259</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>1.34</v>
+        <v>4.4</v>
       </c>
       <c r="L126" s="8" t="n">
-        <v>46168.00524305556</v>
+        <v>46168.65016203704</v>
       </c>
       <c r="M126" s="8" t="n">
-        <v>46168.24994212963</v>
+        <v>46169.98444444445</v>
       </c>
       <c r="N126" s="9" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="O126" s="9" t="n">
-        <v>5.87</v>
+        <v>32.02</v>
       </c>
       <c r="P126" s="9" t="n">
-        <v>5.87</v>
+        <v>32.02</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R126" s="9" t="n">
-        <v>8.84</v>
+        <v>38.11</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>8.84</v>
+        <v>38.11</v>
       </c>
       <c r="T126" s="9" t="n"/>
       <c r="U126" s="9" t="n">
         <v>1</v>
       </c>
       <c r="V126" s="10" t="n">
-        <v>7656.67</v>
+        <v>7360</v>
       </c>
       <c r="W126" s="10" t="n">
-        <v>7544</v>
+        <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>0</v>
@@ -11442,10 +11442,10 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="C127" s="5" t="n">
         <v>46168</v>
@@ -11467,56 +11467,56 @@
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I127" s="5" t="n">
-        <v>46168.34814814815</v>
+        <v>46167.88145833334</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>46168.47204861111</v>
+        <v>46167.93736111111</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>2.97</v>
+        <v>1.34</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>46168.54461805556</v>
+        <v>46168.00524305556</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>46168.54577546296</v>
+        <v>46168.24994212963</v>
       </c>
       <c r="N127" s="6" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>0.03</v>
+        <v>5.87</v>
       </c>
       <c r="P127" s="6" t="n">
-        <v>0.03</v>
+        <v>5.87</v>
       </c>
       <c r="Q127" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R127" s="6" t="n">
-        <v>4.74</v>
+        <v>8.84</v>
       </c>
       <c r="S127" s="6" t="n">
-        <v>4.74</v>
+        <v>8.84</v>
       </c>
       <c r="T127" s="6" t="n"/>
       <c r="U127" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V127" s="7" t="n">
-        <v>7543.52</v>
+        <v>7456</v>
       </c>
       <c r="W127" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="X127" s="7" t="n">
         <v>0</v>
@@ -11528,8 +11528,2744 @@
         <v>0</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B128" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="C128" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="I128" s="8" t="n">
+        <v>46168.34814814815</v>
+      </c>
+      <c r="J128" s="8" t="n">
+        <v>46168.47204861111</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L128" s="8" t="n">
+        <v>46168.54461805556</v>
+      </c>
+      <c r="M128" s="8" t="n">
+        <v>46169.68572916667</v>
+      </c>
+      <c r="N128" s="9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O128" s="9" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="P128" s="9" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="Q128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" s="9" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="S128" s="9" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="T128" s="9" t="n"/>
+      <c r="U128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V128" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>7.21</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>8.24</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>46168.79240740741</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>46169.13828703704</v>
+      </c>
+      <c r="K129" s="6" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>46169.20743055556</v>
+      </c>
+      <c r="M129" s="5" t="n">
+        <v>46169.67351851852</v>
+      </c>
+      <c r="N129" s="6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O129" s="6" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="P129" s="6" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="Q129" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" s="6" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="S129" s="6" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="T129" s="6" t="n"/>
+      <c r="U129" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V129" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W129" s="7" t="n">
+        <v>3680</v>
+      </c>
+      <c r="X129" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B130" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="C130" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="I130" s="8" t="n">
+        <v>46168.95151620371</v>
+      </c>
+      <c r="J130" s="8" t="n">
+        <v>46169.36881944445</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="L130" s="8" t="n">
+        <v>46169.45774305556</v>
+      </c>
+      <c r="M130" s="8" t="n">
+        <v>46169.6916550926</v>
+      </c>
+      <c r="N130" s="9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O130" s="9" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="P130" s="9" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="Q130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" s="9" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="S130" s="9" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="T130" s="9" t="n"/>
+      <c r="U130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V130" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W130" s="10" t="n">
+        <v>3680</v>
+      </c>
+      <c r="X130" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>46169.77158564814</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>46169.9080787037</v>
+      </c>
+      <c r="K131" s="6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>46169.97532407408</v>
+      </c>
+      <c r="M131" s="5" t="n">
+        <v>46170.45916666667</v>
+      </c>
+      <c r="N131" s="6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O131" s="6" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="P131" s="6" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="Q131" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S131" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="T131" s="6" t="n"/>
+      <c r="U131" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V131" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W131" s="7" t="n">
+        <v>3680</v>
+      </c>
+      <c r="X131" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B132" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C132" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>71-8001 มานพ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>9.10</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>10.13</t>
+        </is>
+      </c>
+      <c r="I132" s="8" t="n">
+        <v>46169.71230324074</v>
+      </c>
+      <c r="J132" s="8" t="n">
+        <v>46170.50636574074</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="L132" s="8" t="n">
+        <v>46170.58515046296</v>
+      </c>
+      <c r="M132" s="8" t="n">
+        <v>46171.03496527778</v>
+      </c>
+      <c r="N132" s="9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O132" s="9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P132" s="9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Q132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" s="9" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="S132" s="9" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="T132" s="9" t="n"/>
+      <c r="U132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V132" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W132" s="10" t="n">
+        <v>3680</v>
+      </c>
+      <c r="X132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>7.22</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>46169.76866898148</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>46169.92724537037</v>
+      </c>
+      <c r="K133" s="6" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>46170.0078587963</v>
+      </c>
+      <c r="M133" s="5" t="n">
+        <v>46170.40075231482</v>
+      </c>
+      <c r="N133" s="6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O133" s="6" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="P133" s="6" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="Q133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" s="6" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="S133" s="6" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="T133" s="6" t="n"/>
+      <c r="U133" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V133" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W133" s="7" t="n">
+        <v>3680</v>
+      </c>
+      <c r="X133" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B134" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C134" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>7.23</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="I134" s="8" t="n">
+        <v>46170.58152777778</v>
+      </c>
+      <c r="J134" s="8" t="n">
+        <v>46170.66003472222</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L134" s="8" t="n">
+        <v>46170.72534722222</v>
+      </c>
+      <c r="M134" s="8" t="n">
+        <v>46170.76195601852</v>
+      </c>
+      <c r="N134" s="9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O134" s="9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P134" s="9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" s="9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S134" s="9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T134" s="9" t="n"/>
+      <c r="U134" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V134" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>7.24</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>8.27</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>46170.87883101852</v>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>46170.92953703704</v>
+      </c>
+      <c r="K135" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>46170.99549768519</v>
+      </c>
+      <c r="M135" s="5" t="n">
+        <v>46171.26299768518</v>
+      </c>
+      <c r="N135" s="6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O135" s="6" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="P135" s="6" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="Q135" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" s="6" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="S135" s="6" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="T135" s="6" t="n"/>
+      <c r="U135" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V135" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W135" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B136" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C136" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="n">
+        <v>46169.78903935185</v>
+      </c>
+      <c r="J136" s="8" t="n">
+        <v>46169.98337962963</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="L136" s="8" t="n">
+        <v>46170.07542824074</v>
+      </c>
+      <c r="M136" s="8" t="n">
+        <v>46170.40826388889</v>
+      </c>
+      <c r="N136" s="9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O136" s="9" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="P136" s="9" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="Q136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" s="9" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="S136" s="9" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="T136" s="9" t="n"/>
+      <c r="U136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V136" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W136" s="10" t="n">
+        <v>3680</v>
+      </c>
+      <c r="X136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>46170.5037037037</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>46170.62738425926</v>
+      </c>
+      <c r="K137" s="6" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>46170.72587962963</v>
+      </c>
+      <c r="M137" s="5" t="n">
+        <v>46170.7800462963</v>
+      </c>
+      <c r="N137" s="6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O137" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P137" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q137" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" s="6" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="S137" s="6" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="T137" s="6" t="n"/>
+      <c r="U137" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V137" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B138" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C138" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="n">
+        <v>46170.11607638889</v>
+      </c>
+      <c r="J138" s="8" t="n">
+        <v>46170.26921296296</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="L138" s="8" t="n">
+        <v>46170.83622685185</v>
+      </c>
+      <c r="M138" s="8" t="n">
+        <v>46170.9013425926</v>
+      </c>
+      <c r="N138" s="9" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="O138" s="9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P138" s="9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" s="9" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="S138" s="9" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="T138" s="9" t="inlineStr">
+        <is>
+          <t>ABNORMAL</t>
+        </is>
+      </c>
+      <c r="U138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V138" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W138" s="10" t="n">
+        <v>3680</v>
+      </c>
+      <c r="X138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>46170.58722222222</v>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>46170.89265046296</v>
+      </c>
+      <c r="K139" s="6" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>46170.96063657408</v>
+      </c>
+      <c r="M139" s="5" t="n">
+        <v>46171.30994212963</v>
+      </c>
+      <c r="N139" s="6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O139" s="6" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="P139" s="6" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="Q139" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" s="6" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="S139" s="6" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="T139" s="6" t="n"/>
+      <c r="U139" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V139" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W139" s="7" t="n">
+        <v>3680</v>
+      </c>
+      <c r="X139" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B140" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C140" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="n">
+        <v>46171.16535879629</v>
+      </c>
+      <c r="J140" s="8" t="n">
+        <v>46171.27927083334</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L140" s="8" t="n">
+        <v>46171.37247685185</v>
+      </c>
+      <c r="M140" s="8" t="n">
+        <v>46171.61934027778</v>
+      </c>
+      <c r="N140" s="9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O140" s="9" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="P140" s="9" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="Q140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="S140" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="T140" s="9" t="n"/>
+      <c r="U140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V140" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W140" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>46171.78201388889</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>46171.89481481481</v>
+      </c>
+      <c r="K141" s="6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>46171.96677083334</v>
+      </c>
+      <c r="M141" s="5" t="n">
+        <v>46172.09275462963</v>
+      </c>
+      <c r="N141" s="6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O141" s="6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P141" s="6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Q141" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" s="6" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="S141" s="6" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="T141" s="6" t="n"/>
+      <c r="U141" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V141" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W141" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B142" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C142" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>8.28</t>
+        </is>
+      </c>
+      <c r="I142" s="8" t="n">
+        <v>46171.33181712963</v>
+      </c>
+      <c r="J142" s="8" t="n">
+        <v>46171.60032407408</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="L142" s="8" t="n">
+        <v>46171.67759259259</v>
+      </c>
+      <c r="M142" s="8" t="n">
+        <v>46171.70689814815</v>
+      </c>
+      <c r="N142" s="9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O142" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P142" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q142" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="S142" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T142" s="9" t="n"/>
+      <c r="U142" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W142" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>46170.99238425926</v>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>46171.28165509259</v>
+      </c>
+      <c r="K143" s="6" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>46171.3696875</v>
+      </c>
+      <c r="M143" s="5" t="n">
+        <v>46171.59075231481</v>
+      </c>
+      <c r="N143" s="6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O143" s="6" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="P143" s="6" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="Q143" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" s="6" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="S143" s="6" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="T143" s="6" t="n"/>
+      <c r="U143" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V143" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W143" s="7" t="n">
+        <v>3680</v>
+      </c>
+      <c r="X143" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y143" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B144" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C144" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="I144" s="8" t="n">
+        <v>46171.66229166667</v>
+      </c>
+      <c r="J144" s="8" t="n">
+        <v>46171.72710648148</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L144" s="8" t="n">
+        <v>46171.82959490741</v>
+      </c>
+      <c r="M144" s="8" t="n">
+        <v>46171.94225694444</v>
+      </c>
+      <c r="N144" s="9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O144" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P144" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" s="9" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="S144" s="9" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="T144" s="9" t="n"/>
+      <c r="U144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V144" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W144" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B145" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>46171.00243055556</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>46171.46831018518</v>
+      </c>
+      <c r="K145" s="6" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>46171.54582175926</v>
+      </c>
+      <c r="M145" s="5" t="n">
+        <v>46171.60834490741</v>
+      </c>
+      <c r="N145" s="6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O145" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P145" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q145" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" s="6" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="S145" s="6" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="T145" s="6" t="n"/>
+      <c r="U145" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V145" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W145" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y145" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B146" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C146" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="I146" s="8" t="n">
+        <v>46171.67638888889</v>
+      </c>
+      <c r="J146" s="8" t="n">
+        <v>46171.7416087963</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L146" s="8" t="n">
+        <v>46171.82641203704</v>
+      </c>
+      <c r="M146" s="8" t="n">
+        <v>46171.875625</v>
+      </c>
+      <c r="N146" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O146" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P146" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Q146" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" s="9" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="S146" s="9" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="T146" s="9" t="n"/>
+      <c r="U146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V146" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y146" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B147" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>46171.72065972222</v>
+      </c>
+      <c r="J147" s="5" t="n">
+        <v>46171.87474537037</v>
+      </c>
+      <c r="K147" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>46171.94614583333</v>
+      </c>
+      <c r="M147" s="5" t="n">
+        <v>46172.63309027778</v>
+      </c>
+      <c r="N147" s="6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O147" s="6" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="P147" s="6" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="Q147" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" s="6" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="S147" s="6" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="T147" s="6" t="n"/>
+      <c r="U147" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V147" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W147" s="7" t="n">
+        <v>3680</v>
+      </c>
+      <c r="X147" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B148" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="C148" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="I148" s="8" t="n">
+        <v>46172.32059027778</v>
+      </c>
+      <c r="J148" s="8" t="n">
+        <v>46172.47302083333</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="L148" s="8" t="n">
+        <v>46172.56171296296</v>
+      </c>
+      <c r="M148" s="8" t="n">
+        <v>46172.81743055556</v>
+      </c>
+      <c r="N148" s="9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O148" s="9" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="P148" s="9" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="Q148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" s="9" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="S148" s="9" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="T148" s="9" t="n"/>
+      <c r="U148" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V148" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="W148" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X148" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y148" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B149" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>7.26</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>8.29</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>46171.82071759259</v>
+      </c>
+      <c r="J149" s="5" t="n">
+        <v>46171.92391203704</v>
+      </c>
+      <c r="K149" s="6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>46172.29966435185</v>
+      </c>
+      <c r="M149" s="5" t="n">
+        <v>46172.37111111111</v>
+      </c>
+      <c r="N149" s="6" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="O149" s="6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="P149" s="6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q149" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" s="6" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="S149" s="6" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="T149" s="6" t="inlineStr">
+        <is>
+          <t>ABNORMAL</t>
+        </is>
+      </c>
+      <c r="U149" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V149" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W149" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y149" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B150" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="C150" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>7.27</t>
+        </is>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>8.30</t>
+        </is>
+      </c>
+      <c r="I150" s="8" t="n">
+        <v>46172.43083333333</v>
+      </c>
+      <c r="J150" s="8" t="n">
+        <v>46172.52552083333</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L150" s="8" t="n">
+        <v>46172.61280092593</v>
+      </c>
+      <c r="M150" s="8" t="n">
+        <v>46172.86035879629</v>
+      </c>
+      <c r="N150" s="9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O150" s="9" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="P150" s="9" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="Q150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" s="9" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="S150" s="9" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="T150" s="9" t="n"/>
+      <c r="U150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V150" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="W150" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B151" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>46172.03034722222</v>
+      </c>
+      <c r="J151" s="5" t="n">
+        <v>46172.28571759259</v>
+      </c>
+      <c r="K151" s="6" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>46172.36446759259</v>
+      </c>
+      <c r="M151" s="5" t="n">
+        <v>46172.49165509259</v>
+      </c>
+      <c r="N151" s="6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O151" s="6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P151" s="6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q151" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" s="6" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="S151" s="6" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="T151" s="6" t="n"/>
+      <c r="U151" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V151" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="W151" s="7" t="n">
+        <v>3632</v>
+      </c>
+      <c r="X151" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B152" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C152" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="I152" s="8" t="n">
+        <v>46171.99543981482</v>
+      </c>
+      <c r="J152" s="8" t="n">
+        <v>46172.2858449074</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="L152" s="8" t="n">
+        <v>46172.40947916666</v>
+      </c>
+      <c r="M152" s="8" t="n">
+        <v>46172.62247685185</v>
+      </c>
+      <c r="N152" s="9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="O152" s="9" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="P152" s="9" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="Q152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" s="9" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="S152" s="9" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="T152" s="9" t="n"/>
+      <c r="U152" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V152" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="W152" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y152" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B153" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>46172.945</v>
+      </c>
+      <c r="J153" s="5" t="n">
+        <v>46173.25171296296</v>
+      </c>
+      <c r="K153" s="6" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>46173.33864583333</v>
+      </c>
+      <c r="M153" s="5" t="n">
+        <v>46173.38333333333</v>
+      </c>
+      <c r="N153" s="6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O153" s="6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P153" s="6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q153" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" s="6" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="S153" s="6" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="T153" s="6" t="n"/>
+      <c r="U153" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V153" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="W153" s="7" t="n">
+        <v>3632</v>
+      </c>
+      <c r="X153" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y153" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B154" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C154" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="I154" s="8" t="n">
+        <v>46173.50255787037</v>
+      </c>
+      <c r="J154" s="8" t="n">
+        <v>46173.72892361111</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="L154" s="8" t="n">
+        <v>46173.81170138889</v>
+      </c>
+      <c r="M154" s="8" t="n">
+        <v>46173.91047453704</v>
+      </c>
+      <c r="N154" s="9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O154" s="9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P154" s="9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" s="9" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="S154" s="9" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="T154" s="9" t="n"/>
+      <c r="U154" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V154" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="W154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y154" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>8.31</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>46172.96576388889</v>
+      </c>
+      <c r="J155" s="5" t="n">
+        <v>46173.20033564815</v>
+      </c>
+      <c r="K155" s="6" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>46173.26480324074</v>
+      </c>
+      <c r="M155" s="5" t="n">
+        <v>46173.38116898148</v>
+      </c>
+      <c r="N155" s="6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O155" s="6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P155" s="6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Q155" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" s="6" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="S155" s="6" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="T155" s="6" t="n"/>
+      <c r="U155" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V155" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="W155" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y155" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B156" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="C156" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="G156" s="9" t="inlineStr">
+        <is>
+          <t>5.28</t>
+        </is>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>5.28</t>
+        </is>
+      </c>
+      <c r="I156" s="8" t="n">
+        <v>46172.97828703704</v>
+      </c>
+      <c r="J156" s="8" t="n">
+        <v>46173.5018287037</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="L156" s="8" t="n">
+        <v>46173.57653935185</v>
+      </c>
+      <c r="M156" s="8" t="n">
+        <v>46173.62144675926</v>
+      </c>
+      <c r="N156" s="9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O156" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P156" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" s="9" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="S156" s="9" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="T156" s="9" t="n"/>
+      <c r="U156" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V156" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="W156" s="10" t="n">
+        <v>3632</v>
+      </c>
+      <c r="X156" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B157" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>46172.75962962963</v>
+      </c>
+      <c r="J157" s="5" t="n">
+        <v>46173.02157407408</v>
+      </c>
+      <c r="K157" s="6" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>46173.09358796296</v>
+      </c>
+      <c r="M157" s="5" t="n">
+        <v>46173.18756944445</v>
+      </c>
+      <c r="N157" s="6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O157" s="6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P157" s="6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q157" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" s="6" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="S157" s="6" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="T157" s="6" t="n"/>
+      <c r="U157" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V157" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="W157" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="X157" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B158" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C158" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="I158" s="8" t="n">
+        <v>46173.25349537037</v>
+      </c>
+      <c r="J158" s="8" t="n">
+        <v>46173.31078703704</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L158" s="8" t="n">
+        <v>46173.385625</v>
+      </c>
+      <c r="M158" s="8" t="n">
+        <v>46173.41065972222</v>
+      </c>
+      <c r="N158" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O158" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P158" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" s="9" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="S158" s="9" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="T158" s="9" t="n"/>
+      <c r="U158" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V158" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="W158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Z127"/>
+  <autoFilter ref="A4:Z158"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>46143</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>46144</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>46144</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>46144</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>46145</v>
@@ -1300,7 +1300,7 @@
         <v>7264</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>46146</v>
@@ -1388,7 +1388,7 @@
         <v>7264</v>
       </c>
       <c r="W12" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X12" s="10" t="n">
         <v>0</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>46144</v>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>46145</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>46146</v>
@@ -1652,7 +1652,7 @@
         <v>7264</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>0</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>46146</v>
@@ -1740,7 +1740,7 @@
         <v>7264</v>
       </c>
       <c r="W16" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>7264</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X17" s="7" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>7264</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X19" s="7" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>46149</v>
@@ -2177,10 +2177,10 @@
         <v>1</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>3632</v>
+        <v>3584</v>
       </c>
       <c r="X21" s="7" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>7264</v>
       </c>
       <c r="W24" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>7264</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
         <v>7264</v>
       </c>
       <c r="W26" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>46149</v>
@@ -2793,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="W28" s="10" t="n">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>7168</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>0</v>
@@ -2986,7 +2986,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>46150</v>
@@ -3060,7 +3060,7 @@
         <v>7168</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>46150</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B34" s="8" t="n">
         <v>46150</v>
@@ -3324,7 +3324,7 @@
         <v>7168</v>
       </c>
       <c r="W34" s="10" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>0</v>
@@ -3500,7 +3500,7 @@
         <v>7168</v>
       </c>
       <c r="W36" s="10" t="n">
-        <v>7168</v>
+        <v>0</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>7168</v>
       </c>
       <c r="W37" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="X37" s="7" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
         <v>7168</v>
       </c>
       <c r="W38" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>0</v>
@@ -3764,7 +3764,7 @@
         <v>7168</v>
       </c>
       <c r="W39" s="7" t="n">
-        <v>7168</v>
+        <v>0</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>0</v>
@@ -3852,7 +3852,7 @@
         <v>7168</v>
       </c>
       <c r="W40" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
         <v>7168</v>
       </c>
       <c r="W41" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="X41" s="7" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B42" s="8" t="n">
         <v>46152</v>
@@ -4204,7 +4204,7 @@
         <v>7168</v>
       </c>
       <c r="W44" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>46153</v>
@@ -4292,7 +4292,7 @@
         <v>7168</v>
       </c>
       <c r="W45" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="X45" s="7" t="n">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>46153</v>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B48" s="8" t="n">
         <v>46153</v>
@@ -4732,7 +4732,7 @@
         <v>7264</v>
       </c>
       <c r="W50" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>0</v>
@@ -4820,7 +4820,7 @@
         <v>7168</v>
       </c>
       <c r="W51" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X51" s="7" t="n">
         <v>0</v>
@@ -4908,7 +4908,7 @@
         <v>7264</v>
       </c>
       <c r="W52" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B53" s="5" t="n">
         <v>46154</v>
@@ -4993,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="V53" s="7" t="n">
-        <v>7168</v>
+        <v>7264</v>
       </c>
       <c r="W53" s="7" t="n">
         <v>0</v>
@@ -5098,7 +5098,7 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>46155</v>
@@ -5173,10 +5173,10 @@
         <v>1</v>
       </c>
       <c r="V55" s="7" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="W55" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>0</v>
@@ -5366,7 +5366,7 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B58" s="8" t="n">
         <v>46155</v>
@@ -5437,7 +5437,7 @@
         <v>1</v>
       </c>
       <c r="V58" s="10" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="W58" s="10" t="n">
         <v>3680</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B59" s="5" t="n">
         <v>46156</v>
@@ -5528,7 +5528,7 @@
         <v>7360</v>
       </c>
       <c r="W59" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X59" s="7" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B60" s="8" t="n">
         <v>46155</v>
@@ -5613,10 +5613,10 @@
         <v>1</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="W60" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>0</v>
@@ -5718,7 +5718,7 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B62" s="8" t="n">
         <v>46156</v>
@@ -6056,7 +6056,7 @@
         <v>7360</v>
       </c>
       <c r="W65" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X65" s="7" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>46157</v>
@@ -6232,7 +6232,7 @@
         <v>7360</v>
       </c>
       <c r="W67" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X67" s="7" t="n">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>7360</v>
       </c>
       <c r="W72" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>0</v>
@@ -6760,7 +6760,7 @@
         <v>7360</v>
       </c>
       <c r="W73" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X73" s="7" t="n">
         <v>0</v>
@@ -6848,7 +6848,7 @@
         <v>7360</v>
       </c>
       <c r="W74" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B75" s="5" t="n">
         <v>46159</v>
@@ -6950,7 +6950,7 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B76" s="8" t="n">
         <v>46159</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B77" s="5" t="n">
         <v>46159</v>
@@ -7112,7 +7112,7 @@
         <v>7360</v>
       </c>
       <c r="W77" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X77" s="7" t="n">
         <v>0</v>
@@ -7214,7 +7214,7 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B79" s="5" t="n">
         <v>46160</v>
@@ -7285,10 +7285,10 @@
         <v>1</v>
       </c>
       <c r="V79" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="W79" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X79" s="7" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
         <v>7360</v>
       </c>
       <c r="W81" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>0</v>
@@ -7552,7 +7552,7 @@
         <v>7456</v>
       </c>
       <c r="W82" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>0</v>
@@ -7566,7 +7566,7 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B83" s="5" t="n">
         <v>46160</v>
@@ -7637,7 +7637,7 @@
         <v>1</v>
       </c>
       <c r="V83" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="W83" s="7" t="n">
         <v>3728</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B84" s="8" t="n">
         <v>46160</v>
@@ -7725,10 +7725,10 @@
         <v>1</v>
       </c>
       <c r="V84" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="W84" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>0</v>
@@ -8094,7 +8094,7 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B89" s="5" t="n">
         <v>46161</v>
@@ -8168,7 +8168,7 @@
         <v>7456</v>
       </c>
       <c r="W89" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>0</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>46161</v>
@@ -8358,7 +8358,7 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B92" s="8" t="n">
         <v>46161</v>
@@ -8432,7 +8432,7 @@
         <v>7456</v>
       </c>
       <c r="W92" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>0</v>
@@ -8622,7 +8622,7 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>46162</v>
@@ -8696,7 +8696,7 @@
         <v>7456</v>
       </c>
       <c r="W95" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X95" s="7" t="n">
         <v>0</v>
@@ -8798,7 +8798,7 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B97" s="5" t="n">
         <v>46162</v>
@@ -8886,7 +8886,7 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B98" s="8" t="n">
         <v>46162</v>
@@ -9048,7 +9048,7 @@
         <v>7456</v>
       </c>
       <c r="W99" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X99" s="7" t="n">
         <v>0</v>
@@ -9238,7 +9238,7 @@
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B102" s="8" t="n">
         <v>46163</v>
@@ -9312,7 +9312,7 @@
         <v>7456</v>
       </c>
       <c r="W102" s="10" t="n">
-        <v>7456</v>
+        <v>0</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>0</v>
@@ -9488,7 +9488,7 @@
         <v>7456</v>
       </c>
       <c r="W104" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B105" s="5" t="n">
         <v>46164</v>
@@ -9576,7 +9576,7 @@
         <v>7456</v>
       </c>
       <c r="W105" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>0</v>
@@ -9840,7 +9840,7 @@
         <v>7456</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>0</v>
@@ -9854,7 +9854,7 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B109" s="5" t="n">
         <v>46164</v>
@@ -9942,7 +9942,7 @@
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B110" s="8" t="n">
         <v>46165</v>
@@ -10368,7 +10368,7 @@
         <v>7456</v>
       </c>
       <c r="W114" s="10" t="n">
-        <v>7456</v>
+        <v>3728</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
         <v>7456</v>
       </c>
       <c r="W115" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X115" s="7" t="n">
         <v>0</v>
@@ -10470,7 +10470,7 @@
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B116" s="8" t="n">
         <v>46165</v>
@@ -10808,7 +10808,7 @@
         <v>7456</v>
       </c>
       <c r="W119" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X119" s="7" t="n">
         <v>0</v>
@@ -10910,7 +10910,7 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B121" s="5" t="n">
         <v>46166</v>
@@ -10984,7 +10984,7 @@
         <v>7456</v>
       </c>
       <c r="W121" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X121" s="7" t="n">
         <v>0</v>
@@ -10998,7 +10998,7 @@
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B122" s="8" t="n">
         <v>46166</v>
@@ -11090,7 +11090,7 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B123" s="5" t="n">
         <v>46167</v>
@@ -11161,10 +11161,10 @@
         <v>1</v>
       </c>
       <c r="V123" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="W123" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X123" s="7" t="n">
         <v>0</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B125" s="5" t="n">
         <v>46167</v>
@@ -11337,10 +11337,10 @@
         <v>1</v>
       </c>
       <c r="V125" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="W125" s="7" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="X125" s="7" t="n">
         <v>0</v>
@@ -11354,7 +11354,7 @@
     </row>
     <row r="126">
       <c r="A126" s="8" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B126" s="8" t="n">
         <v>46168</v>
@@ -11428,7 +11428,7 @@
         <v>7360</v>
       </c>
       <c r="W126" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>0</v>
@@ -11516,7 +11516,7 @@
         <v>7456</v>
       </c>
       <c r="W127" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="X127" s="7" t="n">
         <v>0</v>
@@ -11530,7 +11530,7 @@
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B128" s="8" t="n">
         <v>46168</v>
@@ -11604,7 +11604,7 @@
         <v>7360</v>
       </c>
       <c r="W128" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B129" s="5" t="n">
         <v>46168</v>
@@ -11706,7 +11706,7 @@
     </row>
     <row r="130">
       <c r="A130" s="8" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B130" s="8" t="n">
         <v>46168</v>
@@ -11794,7 +11794,7 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B131" s="5" t="n">
         <v>46169</v>
@@ -11882,7 +11882,7 @@
     </row>
     <row r="132">
       <c r="A132" s="8" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B132" s="8" t="n">
         <v>46169</v>
@@ -11970,7 +11970,7 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B133" s="5" t="n">
         <v>46169</v>
@@ -12044,7 +12044,7 @@
         <v>7360</v>
       </c>
       <c r="W133" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X133" s="7" t="n">
         <v>0</v>
@@ -12146,7 +12146,7 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B135" s="5" t="n">
         <v>46170</v>
@@ -12234,7 +12234,7 @@
     </row>
     <row r="136">
       <c r="A136" s="8" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B136" s="8" t="n">
         <v>46169</v>
@@ -12308,7 +12308,7 @@
         <v>7360</v>
       </c>
       <c r="W136" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>0</v>
@@ -12502,7 +12502,7 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B139" s="5" t="n">
         <v>46170</v>
@@ -12854,7 +12854,7 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B143" s="5" t="n">
         <v>46170</v>
@@ -12928,7 +12928,7 @@
         <v>7360</v>
       </c>
       <c r="W143" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X143" s="7" t="n">
         <v>0</v>
@@ -13206,7 +13206,7 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B147" s="5" t="n">
         <v>46171</v>
@@ -13277,10 +13277,10 @@
         <v>1</v>
       </c>
       <c r="V147" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="W147" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X147" s="7" t="n">
         <v>0</v>
@@ -13368,7 +13368,7 @@
         <v>7264</v>
       </c>
       <c r="W148" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X148" s="10" t="n">
         <v>0</v>
@@ -13382,7 +13382,7 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B149" s="5" t="n">
         <v>46171</v>
@@ -13457,7 +13457,7 @@
         <v>1</v>
       </c>
       <c r="V149" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="W149" s="7" t="n">
         <v>0</v>
@@ -13650,7 +13650,7 @@
     </row>
     <row r="152">
       <c r="A152" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B152" s="8" t="n">
         <v>46171</v>
@@ -13721,10 +13721,10 @@
         <v>1</v>
       </c>
       <c r="V152" s="10" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="W152" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X152" s="10" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B153" s="5" t="n">
         <v>46172</v>
@@ -13812,7 +13812,7 @@
         <v>7264</v>
       </c>
       <c r="W153" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X153" s="7" t="n">
         <v>0</v>
@@ -13914,7 +13914,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B155" s="5" t="n">
         <v>46172</v>
@@ -13988,7 +13988,7 @@
         <v>7264</v>
       </c>
       <c r="W155" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X155" s="7" t="n">
         <v>0</v>
@@ -14002,7 +14002,7 @@
     </row>
     <row r="156">
       <c r="A156" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B156" s="8" t="n">
         <v>46172</v>
@@ -14164,7 +14164,7 @@
         <v>7264</v>
       </c>
       <c r="W157" s="7" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="X157" s="7" t="n">
         <v>0</v>
@@ -14252,7 +14252,7 @@
         <v>7264</v>
       </c>
       <c r="W158" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X158" s="10" t="n">
         <v>0</v>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
         <v>3632</v>
       </c>
       <c r="X6" s="10" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="Y6" s="10" t="n">
         <v>0</v>
@@ -951,7 +951,7 @@
         <v>3632</v>
       </c>
       <c r="X7" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="Y7" s="7" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>3632</v>
       </c>
       <c r="X8" s="10" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="Y8" s="10" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>3632</v>
       </c>
       <c r="X9" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="Y9" s="7" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
         <v>3584</v>
       </c>
       <c r="X21" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="Y21" s="7" t="n">
         <v>0</v>
@@ -7027,7 +7027,7 @@
         <v>3680</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y76" s="10" t="n">
         <v>0</v>
@@ -11607,7 +11607,7 @@
         <v>3680</v>
       </c>
       <c r="X128" s="10" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y128" s="10" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>3680</v>
       </c>
       <c r="X130" s="10" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y130" s="10" t="n">
         <v>0</v>
@@ -11959,7 +11959,7 @@
         <v>3680</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y132" s="10" t="n">
         <v>0</v>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:49</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="6">
@@ -3685,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="Z38" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="39">
@@ -4037,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="Z42" s="10" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="43">
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="Z86" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="87">
@@ -8001,7 +8001,7 @@
         <v>0</v>
       </c>
       <c r="Z87" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="88">
@@ -8353,7 +8353,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="92">
@@ -8529,7 +8529,7 @@
         <v>0</v>
       </c>
       <c r="Z93" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="94">
@@ -9321,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="Z102" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="103">

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Trip_Detail" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trip_Detail'!$A$4:$Z$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trip_Detail'!$A$4:$Z$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z158"/>
+  <dimension ref="A1:Z157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:49</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="Y5" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="Z5" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7910,10 +7910,10 @@
         <v>0</v>
       </c>
       <c r="Y86" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="Z86" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -8174,10 +8174,10 @@
         <v>0</v>
       </c>
       <c r="Y89" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="Z89" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="90">
@@ -8185,7 +8185,7 @@
         <v>46162</v>
       </c>
       <c r="B90" s="8" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="C90" s="8" t="n">
         <v>46162</v>
@@ -8197,56 +8197,56 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="I90" s="8" t="n">
-        <v>46162.82657407408</v>
+        <v>46161.7365625</v>
       </c>
       <c r="J90" s="8" t="n">
-        <v>46162.88215277778</v>
+        <v>46161.9807175926</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>1.33</v>
+        <v>5.86</v>
       </c>
       <c r="L90" s="8" t="n">
-        <v>46162.95986111111</v>
+        <v>46162.07633101852</v>
       </c>
       <c r="M90" s="8" t="n">
-        <v>46163.12930555556</v>
+        <v>46162.73322916667</v>
       </c>
       <c r="N90" s="9" t="n">
-        <v>1.86</v>
+        <v>2.29</v>
       </c>
       <c r="O90" s="9" t="n">
-        <v>4.07</v>
+        <v>15.77</v>
       </c>
       <c r="P90" s="9" t="n">
-        <v>4.07</v>
+        <v>15.77</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R90" s="9" t="n">
-        <v>7.27</v>
+        <v>23.92</v>
       </c>
       <c r="S90" s="9" t="n">
-        <v>7.27</v>
+        <v>23.92</v>
       </c>
       <c r="T90" s="9" t="n"/>
       <c r="U90" s="9" t="n">
@@ -8256,7 +8256,7 @@
         <v>7456</v>
       </c>
       <c r="W90" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>0</v>
@@ -8265,7 +8265,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="91">
@@ -8280,61 +8280,61 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="I91" s="5" t="n">
-        <v>46161.7365625</v>
+        <v>46161.87398148148</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>46161.9807175926</v>
+        <v>46162.10988425926</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>5.86</v>
+        <v>5.66</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>46162.07633101852</v>
+        <v>46162.1790625</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>46162.73322916667</v>
+        <v>46162.81619212963</v>
       </c>
       <c r="N91" s="6" t="n">
-        <v>2.29</v>
+        <v>1.66</v>
       </c>
       <c r="O91" s="6" t="n">
-        <v>15.77</v>
+        <v>15.29</v>
       </c>
       <c r="P91" s="6" t="n">
-        <v>15.77</v>
+        <v>15.29</v>
       </c>
       <c r="Q91" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R91" s="6" t="n">
-        <v>23.92</v>
+        <v>22.61</v>
       </c>
       <c r="S91" s="6" t="n">
-        <v>23.92</v>
+        <v>22.61</v>
       </c>
       <c r="T91" s="6" t="n"/>
       <c r="U91" s="6" t="n">
@@ -8353,76 +8353,76 @@
         <v>0</v>
       </c>
       <c r="Z91" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B92" s="8" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="C92" s="8" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="I92" s="8" t="n">
-        <v>46161.87398148148</v>
+        <v>46163.30872685185</v>
       </c>
       <c r="J92" s="8" t="n">
-        <v>46162.10988425926</v>
+        <v>46163.44234953704</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>5.66</v>
+        <v>3.21</v>
       </c>
       <c r="L92" s="8" t="n">
-        <v>46162.1790625</v>
+        <v>46163.52873842593</v>
       </c>
       <c r="M92" s="8" t="n">
-        <v>46162.81619212963</v>
+        <v>46163.65899305556</v>
       </c>
       <c r="N92" s="9" t="n">
-        <v>1.66</v>
+        <v>2.07</v>
       </c>
       <c r="O92" s="9" t="n">
-        <v>15.29</v>
+        <v>3.13</v>
       </c>
       <c r="P92" s="9" t="n">
-        <v>15.29</v>
+        <v>3.13</v>
       </c>
       <c r="Q92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R92" s="9" t="n">
-        <v>22.61</v>
+        <v>8.41</v>
       </c>
       <c r="S92" s="9" t="n">
-        <v>22.61</v>
+        <v>8.41</v>
       </c>
       <c r="T92" s="9" t="n"/>
       <c r="U92" s="9" t="n">
@@ -8432,16 +8432,16 @@
         <v>7456</v>
       </c>
       <c r="W92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="10" t="n">
         <v>3728</v>
-      </c>
-      <c r="X92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -8471,46 +8471,46 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="I93" s="5" t="n">
-        <v>46163.30872685185</v>
+        <v>46163.74399305556</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>46163.44234953704</v>
+        <v>46163.8228125</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>3.21</v>
+        <v>1.89</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>46163.52873842593</v>
+        <v>46163.93035879629</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>46163.65899305556</v>
+        <v>46164.02392361111</v>
       </c>
       <c r="N93" s="6" t="n">
-        <v>2.07</v>
+        <v>2.58</v>
       </c>
       <c r="O93" s="6" t="n">
-        <v>3.13</v>
+        <v>2.25</v>
       </c>
       <c r="P93" s="6" t="n">
-        <v>3.13</v>
+        <v>2.25</v>
       </c>
       <c r="Q93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R93" s="6" t="n">
-        <v>8.41</v>
+        <v>6.72</v>
       </c>
       <c r="S93" s="6" t="n">
-        <v>8.41</v>
+        <v>6.72</v>
       </c>
       <c r="T93" s="6" t="n"/>
       <c r="U93" s="6" t="n">
@@ -8529,7 +8529,7 @@
         <v>0</v>
       </c>
       <c r="Z93" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -8537,7 +8537,7 @@
         <v>46163</v>
       </c>
       <c r="B94" s="8" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="C94" s="8" t="n">
         <v>46163</v>
@@ -8549,56 +8549,56 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>71-8001 มานพ หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="I94" s="8" t="n">
-        <v>46163.74399305556</v>
+        <v>46162.90394675926</v>
       </c>
       <c r="J94" s="8" t="n">
-        <v>46163.8228125</v>
+        <v>46163.22884259259</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.89</v>
+        <v>7.8</v>
       </c>
       <c r="L94" s="8" t="n">
-        <v>46163.93035879629</v>
+        <v>46163.36399305556</v>
       </c>
       <c r="M94" s="8" t="n">
-        <v>46164.02392361111</v>
+        <v>46163.43064814815</v>
       </c>
       <c r="N94" s="9" t="n">
-        <v>2.58</v>
+        <v>3.24</v>
       </c>
       <c r="O94" s="9" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="P94" s="9" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R94" s="9" t="n">
-        <v>6.72</v>
+        <v>12.64</v>
       </c>
       <c r="S94" s="9" t="n">
-        <v>6.72</v>
+        <v>12.64</v>
       </c>
       <c r="T94" s="9" t="n"/>
       <c r="U94" s="9" t="n">
@@ -8608,7 +8608,7 @@
         <v>7456</v>
       </c>
       <c r="W94" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X94" s="10" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
         <v>46163</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C95" s="5" t="n">
         <v>46163</v>
@@ -8637,56 +8637,56 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8005 สมัย หัวลาก10W</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="I95" s="5" t="n">
-        <v>46162.90394675926</v>
+        <v>46163.28854166667</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>46163.22884259259</v>
+        <v>46163.53840277778</v>
       </c>
       <c r="K95" s="6" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>46163.36399305556</v>
+        <v>46163.66119212963</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>46163.43064814815</v>
+        <v>46163.89697916667</v>
       </c>
       <c r="N95" s="6" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="O95" s="6" t="n">
-        <v>1.6</v>
+        <v>5.66</v>
       </c>
       <c r="P95" s="6" t="n">
-        <v>1.6</v>
+        <v>5.66</v>
       </c>
       <c r="Q95" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R95" s="6" t="n">
-        <v>12.64</v>
+        <v>14.6</v>
       </c>
       <c r="S95" s="6" t="n">
-        <v>12.64</v>
+        <v>14.6</v>
       </c>
       <c r="T95" s="6" t="n"/>
       <c r="U95" s="6" t="n">
@@ -8713,7 +8713,7 @@
         <v>46163</v>
       </c>
       <c r="B96" s="8" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="C96" s="8" t="n">
         <v>46163</v>
@@ -8725,56 +8725,56 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="I96" s="8" t="n">
-        <v>46163.28854166667</v>
+        <v>46162.81313657408</v>
       </c>
       <c r="J96" s="8" t="n">
-        <v>46163.53840277778</v>
+        <v>46162.96394675926</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>6</v>
+        <v>3.62</v>
       </c>
       <c r="L96" s="8" t="n">
-        <v>46163.66119212963</v>
+        <v>46163.05145833334</v>
       </c>
       <c r="M96" s="8" t="n">
-        <v>46163.89697916667</v>
+        <v>46163.60020833334</v>
       </c>
       <c r="N96" s="9" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="O96" s="9" t="n">
-        <v>5.66</v>
+        <v>13.17</v>
       </c>
       <c r="P96" s="9" t="n">
-        <v>5.66</v>
+        <v>13.17</v>
       </c>
       <c r="Q96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R96" s="9" t="n">
-        <v>14.6</v>
+        <v>18.89</v>
       </c>
       <c r="S96" s="9" t="n">
-        <v>14.6</v>
+        <v>18.89</v>
       </c>
       <c r="T96" s="9" t="n"/>
       <c r="U96" s="9" t="n">
@@ -8808,61 +8808,61 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="I97" s="5" t="n">
-        <v>46162.81313657408</v>
+        <v>46162.88491898148</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>46162.96394675926</v>
+        <v>46163.71251157407</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>3.62</v>
+        <v>19.86</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>46163.05145833334</v>
+        <v>46163.81291666667</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>46163.60020833334</v>
+        <v>46164.01258101852</v>
       </c>
       <c r="N97" s="6" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="O97" s="6" t="n">
-        <v>13.17</v>
+        <v>4.79</v>
       </c>
       <c r="P97" s="6" t="n">
-        <v>13.17</v>
+        <v>4.79</v>
       </c>
       <c r="Q97" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R97" s="6" t="n">
-        <v>18.89</v>
+        <v>27.06</v>
       </c>
       <c r="S97" s="6" t="n">
-        <v>18.89</v>
+        <v>27.06</v>
       </c>
       <c r="T97" s="6" t="n"/>
       <c r="U97" s="6" t="n">
@@ -8886,71 +8886,71 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B98" s="8" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C98" s="8" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="I98" s="8" t="n">
-        <v>46162.88491898148</v>
+        <v>46164.38288194445</v>
       </c>
       <c r="J98" s="8" t="n">
-        <v>46163.71251157407</v>
+        <v>46164.46175925926</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>19.86</v>
+        <v>1.89</v>
       </c>
       <c r="L98" s="8" t="n">
-        <v>46163.81291666667</v>
+        <v>46164.67049768518</v>
       </c>
       <c r="M98" s="8" t="n">
-        <v>46164.01258101852</v>
+        <v>46164.77396990741</v>
       </c>
       <c r="N98" s="9" t="n">
-        <v>2.41</v>
+        <v>5.01</v>
       </c>
       <c r="O98" s="9" t="n">
-        <v>4.79</v>
+        <v>2.48</v>
       </c>
       <c r="P98" s="9" t="n">
-        <v>4.79</v>
+        <v>2.48</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R98" s="9" t="n">
-        <v>27.06</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="S98" s="9" t="n">
-        <v>27.06</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="T98" s="9" t="n"/>
       <c r="U98" s="9" t="n">
@@ -8989,56 +8989,56 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>71-8001 มานพ หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="I99" s="5" t="n">
-        <v>46164.38288194445</v>
+        <v>46164.60027777778</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>46164.46175925926</v>
+        <v>46164.77232638889</v>
       </c>
       <c r="K99" s="6" t="n">
-        <v>1.89</v>
+        <v>4.13</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>46164.67049768518</v>
+        <v>46164.87579861111</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>46164.77396990741</v>
+        <v>46165.00855324074</v>
       </c>
       <c r="N99" s="6" t="n">
-        <v>5.01</v>
+        <v>2.48</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>2.48</v>
+        <v>3.19</v>
       </c>
       <c r="P99" s="6" t="n">
-        <v>2.48</v>
+        <v>3.19</v>
       </c>
       <c r="Q99" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R99" s="6" t="n">
-        <v>9.390000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S99" s="6" t="n">
-        <v>9.390000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T99" s="6" t="n"/>
       <c r="U99" s="6" t="n">
@@ -9077,56 +9077,56 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8005 สมัย หัวลาก10W</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="I100" s="8" t="n">
-        <v>46164.60027777778</v>
+        <v>46164.23960648148</v>
       </c>
       <c r="J100" s="8" t="n">
-        <v>46164.77232638889</v>
+        <v>46164.39332175926</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>4.13</v>
+        <v>3.69</v>
       </c>
       <c r="L100" s="8" t="n">
-        <v>46164.87579861111</v>
+        <v>46164.48960648148</v>
       </c>
       <c r="M100" s="8" t="n">
-        <v>46165.00855324074</v>
+        <v>46164.76618055555</v>
       </c>
       <c r="N100" s="9" t="n">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="O100" s="9" t="n">
-        <v>3.19</v>
+        <v>6.64</v>
       </c>
       <c r="P100" s="9" t="n">
-        <v>3.19</v>
+        <v>6.64</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R100" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>12.64</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>12.64</v>
       </c>
       <c r="T100" s="9" t="n"/>
       <c r="U100" s="9" t="n">
@@ -9153,7 +9153,7 @@
         <v>46164</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="C101" s="5" t="n">
         <v>46164</v>
@@ -9165,56 +9165,56 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="I101" s="5" t="n">
-        <v>46164.23960648148</v>
+        <v>46163.80703703704</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>46164.39332175926</v>
+        <v>46163.98831018519</v>
       </c>
       <c r="K101" s="6" t="n">
-        <v>3.69</v>
+        <v>4.35</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>46164.48960648148</v>
+        <v>46164.06736111111</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>46164.76618055555</v>
+        <v>46164.46622685185</v>
       </c>
       <c r="N101" s="6" t="n">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>6.64</v>
+        <v>9.57</v>
       </c>
       <c r="P101" s="6" t="n">
-        <v>6.64</v>
+        <v>9.57</v>
       </c>
       <c r="Q101" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R101" s="6" t="n">
-        <v>12.64</v>
+        <v>15.82</v>
       </c>
       <c r="S101" s="6" t="n">
-        <v>12.64</v>
+        <v>15.82</v>
       </c>
       <c r="T101" s="6" t="n"/>
       <c r="U101" s="6" t="n">
@@ -9224,16 +9224,16 @@
         <v>7456</v>
       </c>
       <c r="W101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="7" t="n">
         <v>3728</v>
-      </c>
-      <c r="X101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -9241,7 +9241,7 @@
         <v>46164</v>
       </c>
       <c r="B102" s="8" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C102" s="8" t="n">
         <v>46164</v>
@@ -9263,46 +9263,46 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="I102" s="8" t="n">
-        <v>46163.80703703704</v>
+        <v>46164.53945601852</v>
       </c>
       <c r="J102" s="8" t="n">
-        <v>46163.98831018519</v>
+        <v>46164.71108796296</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>4.35</v>
+        <v>4.12</v>
       </c>
       <c r="L102" s="8" t="n">
-        <v>46164.06736111111</v>
+        <v>46164.80984953704</v>
       </c>
       <c r="M102" s="8" t="n">
-        <v>46164.46622685185</v>
+        <v>46164.98965277777</v>
       </c>
       <c r="N102" s="9" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="O102" s="9" t="n">
-        <v>9.57</v>
+        <v>4.32</v>
       </c>
       <c r="P102" s="9" t="n">
-        <v>9.57</v>
+        <v>4.32</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R102" s="9" t="n">
-        <v>15.82</v>
+        <v>10.8</v>
       </c>
       <c r="S102" s="9" t="n">
-        <v>15.82</v>
+        <v>10.8</v>
       </c>
       <c r="T102" s="9" t="n"/>
       <c r="U102" s="9" t="n">
@@ -9321,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="Z102" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -9336,61 +9336,61 @@
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I103" s="5" t="n">
-        <v>46164.53945601852</v>
+        <v>46164.079375</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>46164.71108796296</v>
+        <v>46164.15428240741</v>
       </c>
       <c r="K103" s="6" t="n">
-        <v>4.12</v>
+        <v>1.8</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>46164.80984953704</v>
+        <v>46164.22637731482</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>46164.98965277777</v>
+        <v>46164.61162037037</v>
       </c>
       <c r="N103" s="6" t="n">
-        <v>2.37</v>
+        <v>1.73</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>4.32</v>
+        <v>9.25</v>
       </c>
       <c r="P103" s="6" t="n">
-        <v>4.32</v>
+        <v>9.25</v>
       </c>
       <c r="Q103" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R103" s="6" t="n">
-        <v>10.8</v>
+        <v>12.77</v>
       </c>
       <c r="S103" s="6" t="n">
-        <v>10.8</v>
+        <v>12.77</v>
       </c>
       <c r="T103" s="6" t="n"/>
       <c r="U103" s="6" t="n">
@@ -9400,7 +9400,7 @@
         <v>7456</v>
       </c>
       <c r="W103" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X103" s="7" t="n">
         <v>0</v>
@@ -9414,71 +9414,71 @@
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B104" s="8" t="n">
         <v>46164</v>
       </c>
       <c r="C104" s="8" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="I104" s="8" t="n">
-        <v>46164.079375</v>
+        <v>46164.87059027778</v>
       </c>
       <c r="J104" s="8" t="n">
-        <v>46164.15428240741</v>
+        <v>46165.14693287037</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.8</v>
+        <v>6.63</v>
       </c>
       <c r="L104" s="8" t="n">
-        <v>46164.22637731482</v>
+        <v>46165.22105324074</v>
       </c>
       <c r="M104" s="8" t="n">
-        <v>46164.61162037037</v>
+        <v>46165.45586805556</v>
       </c>
       <c r="N104" s="9" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="O104" s="9" t="n">
-        <v>9.25</v>
+        <v>5.64</v>
       </c>
       <c r="P104" s="9" t="n">
-        <v>9.25</v>
+        <v>5.64</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R104" s="9" t="n">
-        <v>12.77</v>
+        <v>14.05</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>12.77</v>
+        <v>14.05</v>
       </c>
       <c r="T104" s="9" t="n"/>
       <c r="U104" s="9" t="n">
@@ -9488,7 +9488,7 @@
         <v>7456</v>
       </c>
       <c r="W104" s="10" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>0</v>
@@ -9505,7 +9505,7 @@
         <v>46165</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="C105" s="5" t="n">
         <v>46165</v>
@@ -9527,46 +9527,46 @@
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="I105" s="5" t="n">
-        <v>46164.87059027778</v>
+        <v>46165.62391203704</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>46165.14693287037</v>
+        <v>46165.71038194445</v>
       </c>
       <c r="K105" s="6" t="n">
-        <v>6.63</v>
+        <v>2.08</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>46165.22105324074</v>
+        <v>46165.80432870371</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>46165.45586805556</v>
+        <v>46166.12329861111</v>
       </c>
       <c r="N105" s="6" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="O105" s="6" t="n">
-        <v>5.64</v>
+        <v>7.66</v>
       </c>
       <c r="P105" s="6" t="n">
-        <v>5.64</v>
+        <v>7.66</v>
       </c>
       <c r="Q105" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R105" s="6" t="n">
-        <v>14.05</v>
+        <v>11.99</v>
       </c>
       <c r="S105" s="6" t="n">
-        <v>14.05</v>
+        <v>11.99</v>
       </c>
       <c r="T105" s="6" t="n"/>
       <c r="U105" s="6" t="n">
@@ -9605,56 +9605,56 @@
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>71-8001 มานพ หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="I106" s="8" t="n">
-        <v>46165.62391203704</v>
+        <v>46165.28190972222</v>
       </c>
       <c r="J106" s="8" t="n">
-        <v>46165.71038194445</v>
+        <v>46165.42890046296</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>2.08</v>
+        <v>3.53</v>
       </c>
       <c r="L106" s="8" t="n">
-        <v>46165.80432870371</v>
+        <v>46165.49708333334</v>
       </c>
       <c r="M106" s="8" t="n">
-        <v>46166.12329861111</v>
+        <v>46165.93899305556</v>
       </c>
       <c r="N106" s="9" t="n">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="O106" s="9" t="n">
-        <v>7.66</v>
+        <v>10.61</v>
       </c>
       <c r="P106" s="9" t="n">
-        <v>7.66</v>
+        <v>10.61</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R106" s="9" t="n">
-        <v>11.99</v>
+        <v>15.77</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>11.99</v>
+        <v>15.77</v>
       </c>
       <c r="T106" s="9" t="n"/>
       <c r="U106" s="9" t="n">
@@ -9664,7 +9664,7 @@
         <v>7456</v>
       </c>
       <c r="W106" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>0</v>
@@ -9693,56 +9693,56 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="I107" s="5" t="n">
-        <v>46165.28190972222</v>
+        <v>46165.085</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>46165.42890046296</v>
+        <v>46165.3</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>3.53</v>
+        <v>5.16</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>46165.49708333334</v>
+        <v>46165.36947916666</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>46165.93899305556</v>
+        <v>46165.67659722222</v>
       </c>
       <c r="N107" s="6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>10.61</v>
+        <v>7.37</v>
       </c>
       <c r="P107" s="6" t="n">
-        <v>10.61</v>
+        <v>7.37</v>
       </c>
       <c r="Q107" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R107" s="6" t="n">
-        <v>15.77</v>
+        <v>14.2</v>
       </c>
       <c r="S107" s="6" t="n">
-        <v>15.77</v>
+        <v>14.2</v>
       </c>
       <c r="T107" s="6" t="n"/>
       <c r="U107" s="6" t="n">
@@ -9769,68 +9769,68 @@
         <v>46165</v>
       </c>
       <c r="B108" s="8" t="n">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="C108" s="8" t="n">
         <v>46165</v>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="I108" s="8" t="n">
-        <v>46165.085</v>
+        <v>46164.68181712963</v>
       </c>
       <c r="J108" s="8" t="n">
-        <v>46165.3</v>
+        <v>46165.11505787037</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>5.16</v>
+        <v>10.4</v>
       </c>
       <c r="L108" s="8" t="n">
-        <v>46165.36947916666</v>
+        <v>46165.22395833334</v>
       </c>
       <c r="M108" s="8" t="n">
-        <v>46165.67659722222</v>
+        <v>46165.57903935185</v>
       </c>
       <c r="N108" s="9" t="n">
-        <v>1.67</v>
+        <v>2.61</v>
       </c>
       <c r="O108" s="9" t="n">
-        <v>7.37</v>
+        <v>8.52</v>
       </c>
       <c r="P108" s="9" t="n">
-        <v>7.37</v>
+        <v>8.52</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R108" s="9" t="n">
-        <v>14.2</v>
+        <v>21.53</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>14.2</v>
+        <v>21.53</v>
       </c>
       <c r="T108" s="9" t="n"/>
       <c r="U108" s="9" t="n">
@@ -9854,10 +9854,10 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B109" s="5" t="n">
         <v>46165</v>
-      </c>
-      <c r="B109" s="5" t="n">
-        <v>46164</v>
       </c>
       <c r="C109" s="5" t="n">
         <v>46165</v>
@@ -9879,46 +9879,46 @@
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
           <t>2.31</t>
         </is>
       </c>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
       <c r="I109" s="5" t="n">
-        <v>46164.68181712963</v>
+        <v>46165.6528587963</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>46165.11505787037</v>
+        <v>46165.92780092593</v>
       </c>
       <c r="K109" s="6" t="n">
-        <v>10.4</v>
+        <v>6.6</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>46165.22395833334</v>
+        <v>46165.9957175926</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>46165.57903935185</v>
+        <v>46166.38497685185</v>
       </c>
       <c r="N109" s="6" t="n">
-        <v>2.61</v>
+        <v>1.63</v>
       </c>
       <c r="O109" s="6" t="n">
-        <v>8.52</v>
+        <v>9.34</v>
       </c>
       <c r="P109" s="6" t="n">
-        <v>8.52</v>
+        <v>9.34</v>
       </c>
       <c r="Q109" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R109" s="6" t="n">
-        <v>21.53</v>
+        <v>17.57</v>
       </c>
       <c r="S109" s="6" t="n">
-        <v>21.53</v>
+        <v>17.57</v>
       </c>
       <c r="T109" s="6" t="n"/>
       <c r="U109" s="6" t="n">
@@ -9928,7 +9928,7 @@
         <v>7456</v>
       </c>
       <c r="W109" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X109" s="7" t="n">
         <v>0</v>
@@ -9945,68 +9945,68 @@
         <v>46166</v>
       </c>
       <c r="B110" s="8" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C110" s="8" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="I110" s="8" t="n">
-        <v>46165.6528587963</v>
+        <v>46166.1890625</v>
       </c>
       <c r="J110" s="8" t="n">
-        <v>46165.92780092593</v>
+        <v>46166.41642361111</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>6.6</v>
+        <v>5.46</v>
       </c>
       <c r="L110" s="8" t="n">
-        <v>46165.9957175926</v>
+        <v>46166.48547453704</v>
       </c>
       <c r="M110" s="8" t="n">
-        <v>46166.38497685185</v>
+        <v>46166.63261574074</v>
       </c>
       <c r="N110" s="9" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="O110" s="9" t="n">
-        <v>9.34</v>
+        <v>3.53</v>
       </c>
       <c r="P110" s="9" t="n">
-        <v>9.34</v>
+        <v>3.53</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R110" s="9" t="n">
-        <v>17.57</v>
+        <v>10.65</v>
       </c>
       <c r="S110" s="9" t="n">
-        <v>17.57</v>
+        <v>10.65</v>
       </c>
       <c r="T110" s="9" t="n"/>
       <c r="U110" s="9" t="n">
@@ -10016,7 +10016,7 @@
         <v>7456</v>
       </c>
       <c r="W110" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>0</v>
@@ -10045,56 +10045,56 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>71-8001 มานพ หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="I111" s="5" t="n">
-        <v>46166.1890625</v>
+        <v>46166.01222222222</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>46166.41642361111</v>
+        <v>46166.27747685185</v>
       </c>
       <c r="K111" s="6" t="n">
-        <v>5.46</v>
+        <v>6.37</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>46166.48547453704</v>
+        <v>46166.34541666666</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>46166.63261574074</v>
+        <v>46166.42417824074</v>
       </c>
       <c r="N111" s="6" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="O111" s="6" t="n">
-        <v>3.53</v>
+        <v>1.89</v>
       </c>
       <c r="P111" s="6" t="n">
-        <v>3.53</v>
+        <v>1.89</v>
       </c>
       <c r="Q111" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R111" s="6" t="n">
-        <v>10.65</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="S111" s="6" t="n">
-        <v>10.65</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="T111" s="6" t="n"/>
       <c r="U111" s="6" t="n">
@@ -10104,7 +10104,7 @@
         <v>7456</v>
       </c>
       <c r="W111" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>0</v>
@@ -10143,46 +10143,46 @@
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="I112" s="8" t="n">
-        <v>46166.01222222222</v>
+        <v>46166.50324074074</v>
       </c>
       <c r="J112" s="8" t="n">
-        <v>46166.27747685185</v>
+        <v>46166.72085648148</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>6.37</v>
+        <v>5.22</v>
       </c>
       <c r="L112" s="8" t="n">
-        <v>46166.34541666666</v>
+        <v>46166.81292824074</v>
       </c>
       <c r="M112" s="8" t="n">
-        <v>46166.42417824074</v>
+        <v>46166.92396990741</v>
       </c>
       <c r="N112" s="9" t="n">
-        <v>1.63</v>
+        <v>2.21</v>
       </c>
       <c r="O112" s="9" t="n">
-        <v>1.89</v>
+        <v>2.67</v>
       </c>
       <c r="P112" s="9" t="n">
-        <v>1.89</v>
+        <v>2.67</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R112" s="9" t="n">
-        <v>9.890000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>9.890000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="T112" s="9" t="n"/>
       <c r="U112" s="9" t="n">
@@ -10206,10 +10206,10 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="C113" s="5" t="n">
         <v>46166</v>
@@ -10221,56 +10221,56 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8005 สมัย หัวลาก10W</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="I113" s="5" t="n">
-        <v>46166.50324074074</v>
+        <v>46165.97453703704</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>46166.72085648148</v>
+        <v>46165.97988425926</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>5.22</v>
+        <v>0.13</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>46166.81292824074</v>
+        <v>46166.05300925926</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>46166.92396990741</v>
+        <v>46166.17</v>
       </c>
       <c r="N113" s="6" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="P113" s="6" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="Q113" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R113" s="6" t="n">
-        <v>10.1</v>
+        <v>4.69</v>
       </c>
       <c r="S113" s="6" t="n">
-        <v>10.1</v>
+        <v>4.69</v>
       </c>
       <c r="T113" s="6" t="n"/>
       <c r="U113" s="6" t="n">
@@ -10280,7 +10280,7 @@
         <v>7456</v>
       </c>
       <c r="W113" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X113" s="7" t="n">
         <v>0</v>
@@ -10294,10 +10294,10 @@
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B114" s="8" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C114" s="8" t="n">
         <v>46166</v>
@@ -10319,46 +10319,46 @@
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="I114" s="8" t="n">
-        <v>46165.97453703704</v>
+        <v>46166.34086805556</v>
       </c>
       <c r="J114" s="8" t="n">
-        <v>46165.97988425926</v>
+        <v>46166.50527777777</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.13</v>
+        <v>3.95</v>
       </c>
       <c r="L114" s="8" t="n">
-        <v>46166.05300925926</v>
+        <v>46166.61885416666</v>
       </c>
       <c r="M114" s="8" t="n">
-        <v>46166.17</v>
+        <v>46166.65587962963</v>
       </c>
       <c r="N114" s="9" t="n">
-        <v>1.75</v>
+        <v>2.73</v>
       </c>
       <c r="O114" s="9" t="n">
-        <v>2.81</v>
+        <v>0.89</v>
       </c>
       <c r="P114" s="9" t="n">
-        <v>2.81</v>
+        <v>0.89</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R114" s="9" t="n">
-        <v>4.69</v>
+        <v>7.56</v>
       </c>
       <c r="S114" s="9" t="n">
-        <v>4.69</v>
+        <v>7.56</v>
       </c>
       <c r="T114" s="9" t="n"/>
       <c r="U114" s="9" t="n">
@@ -10385,7 +10385,7 @@
         <v>46166</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="C115" s="5" t="n">
         <v>46166</v>
@@ -10397,56 +10397,56 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I115" s="5" t="n">
-        <v>46166.34086805556</v>
+        <v>46165.76631944445</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>46166.50527777777</v>
+        <v>46166.12497685185</v>
       </c>
       <c r="K115" s="6" t="n">
-        <v>3.95</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>46166.61885416666</v>
+        <v>46166.20672453703</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>46166.65587962963</v>
+        <v>46166.40715277778</v>
       </c>
       <c r="N115" s="6" t="n">
-        <v>2.73</v>
+        <v>1.96</v>
       </c>
       <c r="O115" s="6" t="n">
-        <v>0.89</v>
+        <v>4.81</v>
       </c>
       <c r="P115" s="6" t="n">
-        <v>0.89</v>
+        <v>4.81</v>
       </c>
       <c r="Q115" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R115" s="6" t="n">
-        <v>7.56</v>
+        <v>15.38</v>
       </c>
       <c r="S115" s="6" t="n">
-        <v>7.56</v>
+        <v>15.38</v>
       </c>
       <c r="T115" s="6" t="n"/>
       <c r="U115" s="6" t="n">
@@ -10456,7 +10456,7 @@
         <v>7456</v>
       </c>
       <c r="W115" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X115" s="7" t="n">
         <v>0</v>
@@ -10473,7 +10473,7 @@
         <v>46166</v>
       </c>
       <c r="B116" s="8" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C116" s="8" t="n">
         <v>46166</v>
@@ -10495,46 +10495,46 @@
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="H116" s="9" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="I116" s="8" t="n">
-        <v>46165.76631944445</v>
+        <v>46166.49901620371</v>
       </c>
       <c r="J116" s="8" t="n">
-        <v>46166.12497685185</v>
+        <v>46166.6827662037</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>8.609999999999999</v>
+        <v>4.41</v>
       </c>
       <c r="L116" s="8" t="n">
-        <v>46166.20672453703</v>
+        <v>46166.75684027778</v>
       </c>
       <c r="M116" s="8" t="n">
-        <v>46166.40715277778</v>
+        <v>46166.78159722222</v>
       </c>
       <c r="N116" s="9" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="O116" s="9" t="n">
-        <v>4.81</v>
+        <v>0.59</v>
       </c>
       <c r="P116" s="9" t="n">
-        <v>4.81</v>
+        <v>0.59</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R116" s="9" t="n">
-        <v>15.38</v>
+        <v>6.78</v>
       </c>
       <c r="S116" s="9" t="n">
-        <v>15.38</v>
+        <v>6.78</v>
       </c>
       <c r="T116" s="9" t="n"/>
       <c r="U116" s="9" t="n">
@@ -10568,61 +10568,61 @@
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I117" s="5" t="n">
-        <v>46166.49901620371</v>
+        <v>46166.45078703704</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>46166.6827662037</v>
+        <v>46166.65200231481</v>
       </c>
       <c r="K117" s="6" t="n">
-        <v>4.41</v>
+        <v>4.83</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>46166.75684027778</v>
+        <v>46166.72008101852</v>
       </c>
       <c r="M117" s="5" t="n">
-        <v>46166.78159722222</v>
+        <v>46166.76737268519</v>
       </c>
       <c r="N117" s="6" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="O117" s="6" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="P117" s="6" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="Q117" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R117" s="6" t="n">
-        <v>6.78</v>
+        <v>7.6</v>
       </c>
       <c r="S117" s="6" t="n">
-        <v>6.78</v>
+        <v>7.6</v>
       </c>
       <c r="T117" s="6" t="n"/>
       <c r="U117" s="6" t="n">
@@ -10646,71 +10646,71 @@
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B118" s="8" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="C118" s="8" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="H118" s="9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="I118" s="8" t="n">
-        <v>46166.45078703704</v>
+        <v>46167.03607638889</v>
       </c>
       <c r="J118" s="8" t="n">
-        <v>46166.65200231481</v>
+        <v>46167.16278935185</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="L118" s="8" t="n">
-        <v>46166.72008101852</v>
+        <v>46167.27425925926</v>
       </c>
       <c r="M118" s="8" t="n">
-        <v>46166.76737268519</v>
+        <v>46167.59642361111</v>
       </c>
       <c r="N118" s="9" t="n">
-        <v>1.63</v>
+        <v>2.68</v>
       </c>
       <c r="O118" s="9" t="n">
-        <v>1.14</v>
+        <v>7.73</v>
       </c>
       <c r="P118" s="9" t="n">
-        <v>1.14</v>
+        <v>7.73</v>
       </c>
       <c r="Q118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R118" s="9" t="n">
-        <v>7.6</v>
+        <v>13.45</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>7.6</v>
+        <v>13.45</v>
       </c>
       <c r="T118" s="9" t="n"/>
       <c r="U118" s="9" t="n">
@@ -10720,7 +10720,7 @@
         <v>7456</v>
       </c>
       <c r="W118" s="10" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>0</v>
@@ -10749,56 +10749,56 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8005 สมัย หัวลาก10W</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="I119" s="5" t="n">
-        <v>46167.03607638889</v>
+        <v>46167.58994212963</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>46167.16278935185</v>
+        <v>46167.64440972222</v>
       </c>
       <c r="K119" s="6" t="n">
-        <v>3.04</v>
+        <v>1.31</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>46167.27425925926</v>
+        <v>46167.79445601852</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>46167.59642361111</v>
+        <v>46168.14833333333</v>
       </c>
       <c r="N119" s="6" t="n">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="O119" s="6" t="n">
-        <v>7.73</v>
+        <v>8.49</v>
       </c>
       <c r="P119" s="6" t="n">
-        <v>7.73</v>
+        <v>8.49</v>
       </c>
       <c r="Q119" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R119" s="6" t="n">
-        <v>13.45</v>
+        <v>13.4</v>
       </c>
       <c r="S119" s="6" t="n">
-        <v>13.45</v>
+        <v>13.4</v>
       </c>
       <c r="T119" s="6" t="n"/>
       <c r="U119" s="6" t="n">
@@ -10825,7 +10825,7 @@
         <v>46167</v>
       </c>
       <c r="B120" s="8" t="n">
-        <v>46167</v>
+        <v>46166</v>
       </c>
       <c r="C120" s="8" t="n">
         <v>46167</v>
@@ -10837,56 +10837,56 @@
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="I120" s="8" t="n">
-        <v>46167.58994212963</v>
+        <v>46166.89329861111</v>
       </c>
       <c r="J120" s="8" t="n">
-        <v>46167.64440972222</v>
+        <v>46167.12024305556</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.31</v>
+        <v>5.45</v>
       </c>
       <c r="L120" s="8" t="n">
-        <v>46167.79445601852</v>
+        <v>46167.41954861111</v>
       </c>
       <c r="M120" s="8" t="n">
-        <v>46168.14833333333</v>
+        <v>46167.78295138889</v>
       </c>
       <c r="N120" s="9" t="n">
-        <v>3.6</v>
+        <v>7.18</v>
       </c>
       <c r="O120" s="9" t="n">
-        <v>8.49</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="P120" s="9" t="n">
-        <v>8.49</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R120" s="9" t="n">
-        <v>13.4</v>
+        <v>21.35</v>
       </c>
       <c r="S120" s="9" t="n">
-        <v>13.4</v>
+        <v>21.35</v>
       </c>
       <c r="T120" s="9" t="n"/>
       <c r="U120" s="9" t="n">
@@ -10920,63 +10920,67 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I121" s="5" t="n">
-        <v>46166.89329861111</v>
+        <v>46166.86069444445</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>46167.12024305556</v>
+        <v>46167.01652777778</v>
       </c>
       <c r="K121" s="6" t="n">
-        <v>5.45</v>
+        <v>3.74</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>46167.41954861111</v>
+        <v>46167.49322916667</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>46167.78295138889</v>
+        <v>46167.80994212963</v>
       </c>
       <c r="N121" s="6" t="n">
-        <v>7.18</v>
+        <v>11.44</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>8.720000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P121" s="6" t="n">
-        <v>8.720000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="Q121" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R121" s="6" t="n">
-        <v>21.35</v>
+        <v>22.78</v>
       </c>
       <c r="S121" s="6" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="T121" s="6" t="n"/>
+        <v>22.78</v>
+      </c>
+      <c r="T121" s="6" t="inlineStr">
+        <is>
+          <t>ABNORMAL</t>
+        </is>
+      </c>
       <c r="U121" s="6" t="n">
         <v>1</v>
       </c>
@@ -10984,7 +10988,7 @@
         <v>7456</v>
       </c>
       <c r="W121" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X121" s="7" t="n">
         <v>0</v>
@@ -10998,85 +11002,81 @@
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B122" s="8" t="n">
         <v>46167</v>
       </c>
-      <c r="B122" s="8" t="n">
-        <v>46166</v>
-      </c>
       <c r="C122" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="I122" s="8" t="n">
-        <v>46166.86069444445</v>
+        <v>46167.72461805555</v>
       </c>
       <c r="J122" s="8" t="n">
-        <v>46167.01652777778</v>
+        <v>46168.19608796296</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>3.74</v>
+        <v>11.32</v>
       </c>
       <c r="L122" s="8" t="n">
-        <v>46167.49322916667</v>
+        <v>46168.27104166667</v>
       </c>
       <c r="M122" s="8" t="n">
-        <v>46167.80994212963</v>
+        <v>46168.69186342593</v>
       </c>
       <c r="N122" s="9" t="n">
-        <v>11.44</v>
+        <v>1.8</v>
       </c>
       <c r="O122" s="9" t="n">
-        <v>7.6</v>
+        <v>10.1</v>
       </c>
       <c r="P122" s="9" t="n">
-        <v>7.6</v>
+        <v>10.1</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R122" s="9" t="n">
-        <v>22.78</v>
+        <v>23.21</v>
       </c>
       <c r="S122" s="9" t="n">
-        <v>22.78</v>
-      </c>
-      <c r="T122" s="9" t="inlineStr">
-        <is>
-          <t>ABNORMAL</t>
-        </is>
-      </c>
+        <v>23.21</v>
+      </c>
+      <c r="T122" s="9" t="n"/>
       <c r="U122" s="9" t="n">
         <v>1</v>
       </c>
       <c r="V122" s="10" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="W122" s="10" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>0</v>
@@ -11093,7 +11093,7 @@
         <v>46168</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="C123" s="5" t="n">
         <v>46168</v>
@@ -11105,56 +11105,56 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8005 สมัย หัวลาก10W</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="I123" s="5" t="n">
-        <v>46167.72461805555</v>
+        <v>46168.23354166667</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>46168.19608796296</v>
+        <v>46168.34030092593</v>
       </c>
       <c r="K123" s="6" t="n">
-        <v>11.32</v>
+        <v>2.56</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>46168.27104166667</v>
+        <v>46168.41813657407</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>46168.69186342593</v>
+        <v>46168.79332175926</v>
       </c>
       <c r="N123" s="6" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="P123" s="6" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="Q123" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R123" s="6" t="n">
-        <v>23.21</v>
+        <v>13.43</v>
       </c>
       <c r="S123" s="6" t="n">
-        <v>23.21</v>
+        <v>13.43</v>
       </c>
       <c r="T123" s="6" t="n"/>
       <c r="U123" s="6" t="n">
@@ -11181,7 +11181,7 @@
         <v>46168</v>
       </c>
       <c r="B124" s="8" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="C124" s="8" t="n">
         <v>46168</v>
@@ -11193,56 +11193,56 @@
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="I124" s="8" t="n">
-        <v>46168.23354166667</v>
+        <v>46167.8870949074</v>
       </c>
       <c r="J124" s="8" t="n">
-        <v>46168.34030092593</v>
+        <v>46167.96597222222</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>2.56</v>
+        <v>1.89</v>
       </c>
       <c r="L124" s="8" t="n">
-        <v>46168.41813657407</v>
+        <v>46168.04552083334</v>
       </c>
       <c r="M124" s="8" t="n">
-        <v>46168.79332175926</v>
+        <v>46168.3191087963</v>
       </c>
       <c r="N124" s="9" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O124" s="9" t="n">
-        <v>9</v>
+        <v>6.57</v>
       </c>
       <c r="P124" s="9" t="n">
-        <v>9</v>
+        <v>6.57</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R124" s="9" t="n">
-        <v>13.43</v>
+        <v>10.37</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>13.43</v>
+        <v>10.37</v>
       </c>
       <c r="T124" s="9" t="n"/>
       <c r="U124" s="9" t="n">
@@ -11266,10 +11266,10 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B125" s="5" t="n">
         <v>46168</v>
-      </c>
-      <c r="B125" s="5" t="n">
-        <v>46167</v>
       </c>
       <c r="C125" s="5" t="n">
         <v>46168</v>
@@ -11291,46 +11291,46 @@
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="I125" s="5" t="n">
-        <v>46167.8870949074</v>
+        <v>46168.39633101852</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>46167.96597222222</v>
+        <v>46168.57978009259</v>
       </c>
       <c r="K125" s="6" t="n">
-        <v>1.89</v>
+        <v>4.4</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>46168.04552083334</v>
+        <v>46168.65016203704</v>
       </c>
       <c r="M125" s="5" t="n">
-        <v>46168.3191087963</v>
+        <v>46169.98444444445</v>
       </c>
       <c r="N125" s="6" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>6.57</v>
+        <v>32.02</v>
       </c>
       <c r="P125" s="6" t="n">
-        <v>6.57</v>
+        <v>32.02</v>
       </c>
       <c r="Q125" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R125" s="6" t="n">
-        <v>10.37</v>
+        <v>38.11</v>
       </c>
       <c r="S125" s="6" t="n">
-        <v>10.37</v>
+        <v>38.11</v>
       </c>
       <c r="T125" s="6" t="n"/>
       <c r="U125" s="6" t="n">
@@ -11354,81 +11354,81 @@
     </row>
     <row r="126">
       <c r="A126" s="8" t="n">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B126" s="8" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="C126" s="8" t="n">
         <v>46168</v>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I126" s="8" t="n">
-        <v>46168.39633101852</v>
+        <v>46167.88145833334</v>
       </c>
       <c r="J126" s="8" t="n">
-        <v>46168.57978009259</v>
+        <v>46167.93736111111</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>4.4</v>
+        <v>1.34</v>
       </c>
       <c r="L126" s="8" t="n">
-        <v>46168.65016203704</v>
+        <v>46168.00524305556</v>
       </c>
       <c r="M126" s="8" t="n">
-        <v>46169.98444444445</v>
+        <v>46168.24994212963</v>
       </c>
       <c r="N126" s="9" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="O126" s="9" t="n">
-        <v>32.02</v>
+        <v>5.87</v>
       </c>
       <c r="P126" s="9" t="n">
-        <v>32.02</v>
+        <v>5.87</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R126" s="9" t="n">
-        <v>38.11</v>
+        <v>8.84</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>38.11</v>
+        <v>8.84</v>
       </c>
       <c r="T126" s="9" t="n"/>
       <c r="U126" s="9" t="n">
         <v>1</v>
       </c>
       <c r="V126" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="W126" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>0</v>
@@ -11442,10 +11442,10 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="C127" s="5" t="n">
         <v>46168</v>
@@ -11467,59 +11467,59 @@
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
           <t>2.35</t>
         </is>
       </c>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
       <c r="I127" s="5" t="n">
-        <v>46167.88145833334</v>
+        <v>46168.34814814815</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>46167.93736111111</v>
+        <v>46168.47204861111</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>1.34</v>
+        <v>2.97</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>46168.00524305556</v>
+        <v>46168.54461805556</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>46168.24994212963</v>
+        <v>46169.68572916667</v>
       </c>
       <c r="N127" s="6" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>5.87</v>
+        <v>27.39</v>
       </c>
       <c r="P127" s="6" t="n">
-        <v>5.87</v>
+        <v>27.39</v>
       </c>
       <c r="Q127" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R127" s="6" t="n">
-        <v>8.84</v>
+        <v>32.1</v>
       </c>
       <c r="S127" s="6" t="n">
-        <v>8.84</v>
+        <v>32.1</v>
       </c>
       <c r="T127" s="6" t="n"/>
       <c r="U127" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V127" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="W127" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X127" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y127" s="7" t="n">
         <v>0</v>
@@ -11536,65 +11536,65 @@
         <v>46168</v>
       </c>
       <c r="C128" s="8" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="H128" s="9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="I128" s="8" t="n">
-        <v>46168.34814814815</v>
+        <v>46168.79240740741</v>
       </c>
       <c r="J128" s="8" t="n">
-        <v>46168.47204861111</v>
+        <v>46169.13828703704</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.97</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L128" s="8" t="n">
-        <v>46168.54461805556</v>
+        <v>46169.20743055556</v>
       </c>
       <c r="M128" s="8" t="n">
-        <v>46169.68572916667</v>
+        <v>46169.67351851852</v>
       </c>
       <c r="N128" s="9" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="O128" s="9" t="n">
-        <v>27.39</v>
+        <v>11.19</v>
       </c>
       <c r="P128" s="9" t="n">
-        <v>27.39</v>
+        <v>11.19</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R128" s="9" t="n">
-        <v>32.1</v>
+        <v>21.15</v>
       </c>
       <c r="S128" s="9" t="n">
-        <v>32.1</v>
+        <v>21.15</v>
       </c>
       <c r="T128" s="9" t="n"/>
       <c r="U128" s="9" t="n">
@@ -11607,7 +11607,7 @@
         <v>3680</v>
       </c>
       <c r="X128" s="10" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="Y128" s="10" t="n">
         <v>0</v>
@@ -11633,56 +11633,56 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="I129" s="5" t="n">
-        <v>46168.79240740741</v>
+        <v>46168.95151620371</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>46169.13828703704</v>
+        <v>46169.36881944445</v>
       </c>
       <c r="K129" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>46169.20743055556</v>
+        <v>46169.45774305556</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>46169.67351851852</v>
+        <v>46169.6916550926</v>
       </c>
       <c r="N129" s="6" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>11.19</v>
+        <v>5.61</v>
       </c>
       <c r="P129" s="6" t="n">
-        <v>11.19</v>
+        <v>5.61</v>
       </c>
       <c r="Q129" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R129" s="6" t="n">
-        <v>21.15</v>
+        <v>17.76</v>
       </c>
       <c r="S129" s="6" t="n">
-        <v>21.15</v>
+        <v>17.76</v>
       </c>
       <c r="T129" s="6" t="n"/>
       <c r="U129" s="6" t="n">
@@ -11695,7 +11695,7 @@
         <v>3680</v>
       </c>
       <c r="X129" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y129" s="7" t="n">
         <v>0</v>
@@ -11706,71 +11706,71 @@
     </row>
     <row r="130">
       <c r="A130" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B130" s="8" t="n">
         <v>46169</v>
-      </c>
-      <c r="B130" s="8" t="n">
-        <v>46168</v>
       </c>
       <c r="C130" s="8" t="n">
         <v>46169</v>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="H130" s="9" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I130" s="8" t="n">
-        <v>46168.95151620371</v>
+        <v>46169.77158564814</v>
       </c>
       <c r="J130" s="8" t="n">
-        <v>46169.36881944445</v>
+        <v>46169.9080787037</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>10.02</v>
+        <v>3.28</v>
       </c>
       <c r="L130" s="8" t="n">
-        <v>46169.45774305556</v>
+        <v>46169.97532407408</v>
       </c>
       <c r="M130" s="8" t="n">
-        <v>46169.6916550926</v>
+        <v>46170.45916666667</v>
       </c>
       <c r="N130" s="9" t="n">
-        <v>2.13</v>
+        <v>1.61</v>
       </c>
       <c r="O130" s="9" t="n">
-        <v>5.61</v>
+        <v>11.61</v>
       </c>
       <c r="P130" s="9" t="n">
-        <v>5.61</v>
+        <v>11.61</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R130" s="9" t="n">
-        <v>17.76</v>
+        <v>16.5</v>
       </c>
       <c r="S130" s="9" t="n">
-        <v>17.76</v>
+        <v>16.5</v>
       </c>
       <c r="T130" s="9" t="n"/>
       <c r="U130" s="9" t="n">
@@ -11783,7 +11783,7 @@
         <v>3680</v>
       </c>
       <c r="X130" s="10" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="Y130" s="10" t="n">
         <v>0</v>
@@ -11800,65 +11800,65 @@
         <v>46169</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="I131" s="5" t="n">
-        <v>46169.77158564814</v>
+        <v>46169.71230324074</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>46169.9080787037</v>
+        <v>46170.50636574074</v>
       </c>
       <c r="K131" s="6" t="n">
-        <v>3.28</v>
+        <v>19.06</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>46169.97532407408</v>
+        <v>46170.58515046296</v>
       </c>
       <c r="M131" s="5" t="n">
-        <v>46170.45916666667</v>
+        <v>46171.03496527778</v>
       </c>
       <c r="N131" s="6" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="O131" s="6" t="n">
-        <v>11.61</v>
+        <v>10.8</v>
       </c>
       <c r="P131" s="6" t="n">
-        <v>11.61</v>
+        <v>10.8</v>
       </c>
       <c r="Q131" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R131" s="6" t="n">
-        <v>16.5</v>
+        <v>31.74</v>
       </c>
       <c r="S131" s="6" t="n">
-        <v>16.5</v>
+        <v>31.74</v>
       </c>
       <c r="T131" s="6" t="n"/>
       <c r="U131" s="6" t="n">
@@ -11871,7 +11871,7 @@
         <v>3680</v>
       </c>
       <c r="X131" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y131" s="7" t="n">
         <v>0</v>
@@ -11897,56 +11897,56 @@
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>71-8001 มานพ หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="H132" s="9" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="I132" s="8" t="n">
-        <v>46169.71230324074</v>
+        <v>46169.76866898148</v>
       </c>
       <c r="J132" s="8" t="n">
-        <v>46170.50636574074</v>
+        <v>46169.92724537037</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>19.06</v>
+        <v>3.81</v>
       </c>
       <c r="L132" s="8" t="n">
-        <v>46170.58515046296</v>
+        <v>46170.0078587963</v>
       </c>
       <c r="M132" s="8" t="n">
-        <v>46171.03496527778</v>
+        <v>46170.40075231482</v>
       </c>
       <c r="N132" s="9" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O132" s="9" t="n">
-        <v>10.8</v>
+        <v>9.43</v>
       </c>
       <c r="P132" s="9" t="n">
-        <v>10.8</v>
+        <v>9.43</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R132" s="9" t="n">
-        <v>31.74</v>
+        <v>15.17</v>
       </c>
       <c r="S132" s="9" t="n">
-        <v>31.74</v>
+        <v>15.17</v>
       </c>
       <c r="T132" s="9" t="n"/>
       <c r="U132" s="9" t="n">
@@ -11956,10 +11956,10 @@
         <v>7360</v>
       </c>
       <c r="W132" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="Y132" s="10" t="n">
         <v>0</v>
@@ -11973,7 +11973,7 @@
         <v>46170</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C133" s="5" t="n">
         <v>46170</v>
@@ -11995,46 +11995,46 @@
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="I133" s="5" t="n">
-        <v>46169.76866898148</v>
+        <v>46170.58152777778</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>46169.92724537037</v>
+        <v>46170.66003472222</v>
       </c>
       <c r="K133" s="6" t="n">
-        <v>3.81</v>
+        <v>1.88</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>46170.0078587963</v>
+        <v>46170.72534722222</v>
       </c>
       <c r="M133" s="5" t="n">
-        <v>46170.40075231482</v>
+        <v>46170.76195601852</v>
       </c>
       <c r="N133" s="6" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="O133" s="6" t="n">
-        <v>9.43</v>
+        <v>0.88</v>
       </c>
       <c r="P133" s="6" t="n">
-        <v>9.43</v>
+        <v>0.88</v>
       </c>
       <c r="Q133" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R133" s="6" t="n">
-        <v>15.17</v>
+        <v>4.33</v>
       </c>
       <c r="S133" s="6" t="n">
-        <v>15.17</v>
+        <v>4.33</v>
       </c>
       <c r="T133" s="6" t="n"/>
       <c r="U133" s="6" t="n">
@@ -12058,7 +12058,7 @@
     </row>
     <row r="134">
       <c r="A134" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B134" s="8" t="n">
         <v>46170</v>
@@ -12083,46 +12083,46 @@
       </c>
       <c r="G134" s="9" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="I134" s="8" t="n">
-        <v>46170.58152777778</v>
+        <v>46170.87883101852</v>
       </c>
       <c r="J134" s="8" t="n">
-        <v>46170.66003472222</v>
+        <v>46170.92953703704</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="L134" s="8" t="n">
-        <v>46170.72534722222</v>
+        <v>46170.99549768519</v>
       </c>
       <c r="M134" s="8" t="n">
-        <v>46170.76195601852</v>
+        <v>46171.26299768518</v>
       </c>
       <c r="N134" s="9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O134" s="9" t="n">
-        <v>0.88</v>
+        <v>6.42</v>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0.88</v>
+        <v>6.42</v>
       </c>
       <c r="Q134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R134" s="9" t="n">
-        <v>4.33</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>4.33</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="T134" s="9" t="n"/>
       <c r="U134" s="9" t="n">
@@ -12146,10 +12146,10 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C135" s="5" t="n">
         <v>46170</v>
@@ -12161,56 +12161,56 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="I135" s="5" t="n">
-        <v>46170.87883101852</v>
+        <v>46169.78903935185</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>46170.92953703704</v>
+        <v>46169.98337962963</v>
       </c>
       <c r="K135" s="6" t="n">
-        <v>1.22</v>
+        <v>4.66</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>46170.99549768519</v>
+        <v>46170.07542824074</v>
       </c>
       <c r="M135" s="5" t="n">
-        <v>46171.26299768518</v>
+        <v>46170.40826388889</v>
       </c>
       <c r="N135" s="6" t="n">
-        <v>1.58</v>
+        <v>2.21</v>
       </c>
       <c r="O135" s="6" t="n">
-        <v>6.42</v>
+        <v>7.99</v>
       </c>
       <c r="P135" s="6" t="n">
-        <v>6.42</v>
+        <v>7.99</v>
       </c>
       <c r="Q135" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R135" s="6" t="n">
-        <v>9.220000000000001</v>
+        <v>14.86</v>
       </c>
       <c r="S135" s="6" t="n">
-        <v>9.220000000000001</v>
+        <v>14.86</v>
       </c>
       <c r="T135" s="6" t="n"/>
       <c r="U135" s="6" t="n">
@@ -12237,7 +12237,7 @@
         <v>46170</v>
       </c>
       <c r="B136" s="8" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C136" s="8" t="n">
         <v>46170</v>
@@ -12259,46 +12259,46 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="I136" s="8" t="n">
-        <v>46169.78903935185</v>
+        <v>46170.5037037037</v>
       </c>
       <c r="J136" s="8" t="n">
-        <v>46169.98337962963</v>
+        <v>46170.62738425926</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>4.66</v>
+        <v>2.97</v>
       </c>
       <c r="L136" s="8" t="n">
-        <v>46170.07542824074</v>
+        <v>46170.72587962963</v>
       </c>
       <c r="M136" s="8" t="n">
-        <v>46170.40826388889</v>
+        <v>46170.7800462963</v>
       </c>
       <c r="N136" s="9" t="n">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="O136" s="9" t="n">
-        <v>7.99</v>
+        <v>1.3</v>
       </c>
       <c r="P136" s="9" t="n">
-        <v>7.99</v>
+        <v>1.3</v>
       </c>
       <c r="Q136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R136" s="9" t="n">
-        <v>14.86</v>
+        <v>6.63</v>
       </c>
       <c r="S136" s="9" t="n">
-        <v>14.86</v>
+        <v>6.63</v>
       </c>
       <c r="T136" s="9" t="n"/>
       <c r="U136" s="9" t="n">
@@ -12337,58 +12337,62 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="I137" s="5" t="n">
-        <v>46170.5037037037</v>
+        <v>46170.11607638889</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>46170.62738425926</v>
+        <v>46170.26921296296</v>
       </c>
       <c r="K137" s="6" t="n">
-        <v>2.97</v>
+        <v>3.68</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>46170.72587962963</v>
+        <v>46170.83622685185</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>46170.7800462963</v>
+        <v>46170.9013425926</v>
       </c>
       <c r="N137" s="6" t="n">
-        <v>2.36</v>
+        <v>13.61</v>
       </c>
       <c r="O137" s="6" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="P137" s="6" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="Q137" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R137" s="6" t="n">
-        <v>6.63</v>
+        <v>18.85</v>
       </c>
       <c r="S137" s="6" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="T137" s="6" t="n"/>
+        <v>18.85</v>
+      </c>
+      <c r="T137" s="6" t="inlineStr">
+        <is>
+          <t>ABNORMAL</t>
+        </is>
+      </c>
       <c r="U137" s="6" t="n">
         <v>1</v>
       </c>
@@ -12396,7 +12400,7 @@
         <v>7360</v>
       </c>
       <c r="W137" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X137" s="7" t="n">
         <v>0</v>
@@ -12410,7 +12414,7 @@
     </row>
     <row r="138">
       <c r="A138" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B138" s="8" t="n">
         <v>46170</v>
@@ -12420,67 +12424,63 @@
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I138" s="8" t="n">
-        <v>46170.11607638889</v>
+        <v>46170.58722222222</v>
       </c>
       <c r="J138" s="8" t="n">
-        <v>46170.26921296296</v>
+        <v>46170.89265046296</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>3.68</v>
+        <v>7.33</v>
       </c>
       <c r="L138" s="8" t="n">
-        <v>46170.83622685185</v>
+        <v>46170.96063657408</v>
       </c>
       <c r="M138" s="8" t="n">
-        <v>46170.9013425926</v>
+        <v>46171.30994212963</v>
       </c>
       <c r="N138" s="9" t="n">
-        <v>13.61</v>
+        <v>1.63</v>
       </c>
       <c r="O138" s="9" t="n">
-        <v>1.56</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="P138" s="9" t="n">
-        <v>1.56</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="Q138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R138" s="9" t="n">
-        <v>18.85</v>
+        <v>17.35</v>
       </c>
       <c r="S138" s="9" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="T138" s="9" t="inlineStr">
-        <is>
-          <t>ABNORMAL</t>
-        </is>
-      </c>
+        <v>17.35</v>
+      </c>
+      <c r="T138" s="9" t="n"/>
       <c r="U138" s="9" t="n">
         <v>1</v>
       </c>
@@ -12505,68 +12505,68 @@
         <v>46171</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I139" s="5" t="n">
-        <v>46170.58722222222</v>
+        <v>46171.16535879629</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>46170.89265046296</v>
+        <v>46171.27927083334</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>7.33</v>
+        <v>2.73</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>46170.96063657408</v>
+        <v>46171.37247685185</v>
       </c>
       <c r="M139" s="5" t="n">
-        <v>46171.30994212963</v>
+        <v>46171.61934027778</v>
       </c>
       <c r="N139" s="6" t="n">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="O139" s="6" t="n">
-        <v>8.380000000000001</v>
+        <v>5.92</v>
       </c>
       <c r="P139" s="6" t="n">
-        <v>8.380000000000001</v>
+        <v>5.92</v>
       </c>
       <c r="Q139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R139" s="6" t="n">
-        <v>17.35</v>
+        <v>10.9</v>
       </c>
       <c r="S139" s="6" t="n">
-        <v>17.35</v>
+        <v>10.9</v>
       </c>
       <c r="T139" s="6" t="n"/>
       <c r="U139" s="6" t="n">
@@ -12576,7 +12576,7 @@
         <v>7360</v>
       </c>
       <c r="W139" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X139" s="7" t="n">
         <v>0</v>
@@ -12615,46 +12615,46 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I140" s="8" t="n">
-        <v>46171.16535879629</v>
+        <v>46171.78201388889</v>
       </c>
       <c r="J140" s="8" t="n">
-        <v>46171.27927083334</v>
+        <v>46171.89481481481</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="L140" s="8" t="n">
-        <v>46171.37247685185</v>
+        <v>46171.96677083334</v>
       </c>
       <c r="M140" s="8" t="n">
-        <v>46171.61934027778</v>
+        <v>46172.09275462963</v>
       </c>
       <c r="N140" s="9" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="O140" s="9" t="n">
-        <v>5.92</v>
+        <v>3.02</v>
       </c>
       <c r="P140" s="9" t="n">
-        <v>5.92</v>
+        <v>3.02</v>
       </c>
       <c r="Q140" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R140" s="9" t="n">
-        <v>10.9</v>
+        <v>7.46</v>
       </c>
       <c r="S140" s="9" t="n">
-        <v>10.9</v>
+        <v>7.46</v>
       </c>
       <c r="T140" s="9" t="n"/>
       <c r="U140" s="9" t="n">
@@ -12693,56 +12693,56 @@
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I141" s="5" t="n">
-        <v>46171.78201388889</v>
+        <v>46171.33181712963</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>46171.89481481481</v>
+        <v>46171.60032407408</v>
       </c>
       <c r="K141" s="6" t="n">
-        <v>2.71</v>
+        <v>6.44</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>46171.96677083334</v>
+        <v>46171.67759259259</v>
       </c>
       <c r="M141" s="5" t="n">
-        <v>46172.09275462963</v>
+        <v>46171.70689814815</v>
       </c>
       <c r="N141" s="6" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="O141" s="6" t="n">
-        <v>3.02</v>
+        <v>0.7</v>
       </c>
       <c r="P141" s="6" t="n">
-        <v>3.02</v>
+        <v>0.7</v>
       </c>
       <c r="Q141" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R141" s="6" t="n">
-        <v>7.46</v>
+        <v>9</v>
       </c>
       <c r="S141" s="6" t="n">
-        <v>7.46</v>
+        <v>9</v>
       </c>
       <c r="T141" s="6" t="n"/>
       <c r="U141" s="6" t="n">
@@ -12769,7 +12769,7 @@
         <v>46171</v>
       </c>
       <c r="B142" s="8" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="C142" s="8" t="n">
         <v>46171</v>
@@ -12781,56 +12781,56 @@
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="H142" s="9" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="I142" s="8" t="n">
-        <v>46171.33181712963</v>
+        <v>46170.99238425926</v>
       </c>
       <c r="J142" s="8" t="n">
-        <v>46171.60032407408</v>
+        <v>46171.28165509259</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>6.44</v>
+        <v>6.94</v>
       </c>
       <c r="L142" s="8" t="n">
-        <v>46171.67759259259</v>
+        <v>46171.3696875</v>
       </c>
       <c r="M142" s="8" t="n">
-        <v>46171.70689814815</v>
+        <v>46171.59075231481</v>
       </c>
       <c r="N142" s="9" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="O142" s="9" t="n">
-        <v>0.7</v>
+        <v>5.31</v>
       </c>
       <c r="P142" s="9" t="n">
-        <v>0.7</v>
+        <v>5.31</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R142" s="9" t="n">
-        <v>9</v>
+        <v>14.36</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>9</v>
+        <v>14.36</v>
       </c>
       <c r="T142" s="9" t="n"/>
       <c r="U142" s="9" t="n">
@@ -12857,7 +12857,7 @@
         <v>46171</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C143" s="5" t="n">
         <v>46171</v>
@@ -12879,46 +12879,46 @@
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="I143" s="5" t="n">
-        <v>46170.99238425926</v>
+        <v>46171.66229166667</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>46171.28165509259</v>
+        <v>46171.72710648148</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>6.94</v>
+        <v>1.56</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>46171.3696875</v>
+        <v>46171.82959490741</v>
       </c>
       <c r="M143" s="5" t="n">
-        <v>46171.59075231481</v>
+        <v>46171.94225694444</v>
       </c>
       <c r="N143" s="6" t="n">
-        <v>2.11</v>
+        <v>2.46</v>
       </c>
       <c r="O143" s="6" t="n">
-        <v>5.31</v>
+        <v>2.7</v>
       </c>
       <c r="P143" s="6" t="n">
-        <v>5.31</v>
+        <v>2.7</v>
       </c>
       <c r="Q143" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R143" s="6" t="n">
-        <v>14.36</v>
+        <v>6.72</v>
       </c>
       <c r="S143" s="6" t="n">
-        <v>14.36</v>
+        <v>6.72</v>
       </c>
       <c r="T143" s="6" t="n"/>
       <c r="U143" s="6" t="n">
@@ -12957,56 +12957,56 @@
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H144" s="9" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="I144" s="8" t="n">
-        <v>46171.66229166667</v>
+        <v>46171.00243055556</v>
       </c>
       <c r="J144" s="8" t="n">
-        <v>46171.72710648148</v>
+        <v>46171.46831018518</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>1.56</v>
+        <v>11.18</v>
       </c>
       <c r="L144" s="8" t="n">
-        <v>46171.82959490741</v>
+        <v>46171.54582175926</v>
       </c>
       <c r="M144" s="8" t="n">
-        <v>46171.94225694444</v>
+        <v>46171.60834490741</v>
       </c>
       <c r="N144" s="9" t="n">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="O144" s="9" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="P144" s="9" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R144" s="9" t="n">
-        <v>6.72</v>
+        <v>14.54</v>
       </c>
       <c r="S144" s="9" t="n">
-        <v>6.72</v>
+        <v>14.54</v>
       </c>
       <c r="T144" s="9" t="n"/>
       <c r="U144" s="9" t="n">
@@ -13055,46 +13055,46 @@
       </c>
       <c r="G145" s="6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I145" s="5" t="n">
-        <v>46171.00243055556</v>
+        <v>46171.67638888889</v>
       </c>
       <c r="J145" s="5" t="n">
-        <v>46171.46831018518</v>
+        <v>46171.7416087963</v>
       </c>
       <c r="K145" s="6" t="n">
-        <v>11.18</v>
+        <v>1.57</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>46171.54582175926</v>
+        <v>46171.82641203704</v>
       </c>
       <c r="M145" s="5" t="n">
-        <v>46171.60834490741</v>
+        <v>46171.875625</v>
       </c>
       <c r="N145" s="6" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="O145" s="6" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="P145" s="6" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="Q145" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R145" s="6" t="n">
-        <v>14.54</v>
+        <v>4.78</v>
       </c>
       <c r="S145" s="6" t="n">
-        <v>14.54</v>
+        <v>4.78</v>
       </c>
       <c r="T145" s="6" t="n"/>
       <c r="U145" s="6" t="n">
@@ -13118,7 +13118,7 @@
     </row>
     <row r="146">
       <c r="A146" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B146" s="8" t="n">
         <v>46171</v>
@@ -13128,68 +13128,68 @@
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="H146" s="9" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I146" s="8" t="n">
-        <v>46171.67638888889</v>
+        <v>46171.72065972222</v>
       </c>
       <c r="J146" s="8" t="n">
-        <v>46171.7416087963</v>
+        <v>46171.87474537037</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="L146" s="8" t="n">
-        <v>46171.82641203704</v>
+        <v>46171.94614583333</v>
       </c>
       <c r="M146" s="8" t="n">
-        <v>46171.875625</v>
+        <v>46172.63309027778</v>
       </c>
       <c r="N146" s="9" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="O146" s="9" t="n">
-        <v>1.18</v>
+        <v>16.49</v>
       </c>
       <c r="P146" s="9" t="n">
-        <v>1.18</v>
+        <v>16.49</v>
       </c>
       <c r="Q146" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R146" s="9" t="n">
-        <v>4.78</v>
+        <v>21.9</v>
       </c>
       <c r="S146" s="9" t="n">
-        <v>4.78</v>
+        <v>21.9</v>
       </c>
       <c r="T146" s="9" t="n"/>
       <c r="U146" s="9" t="n">
         <v>1</v>
       </c>
       <c r="V146" s="10" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="W146" s="10" t="n">
         <v>0</v>
@@ -13209,68 +13209,68 @@
         <v>46172</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I147" s="5" t="n">
-        <v>46171.72065972222</v>
+        <v>46172.32059027778</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>46171.87474537037</v>
+        <v>46172.47302083333</v>
       </c>
       <c r="K147" s="6" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>46171.94614583333</v>
+        <v>46172.56171296296</v>
       </c>
       <c r="M147" s="5" t="n">
-        <v>46172.63309027778</v>
+        <v>46172.81743055556</v>
       </c>
       <c r="N147" s="6" t="n">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="O147" s="6" t="n">
-        <v>16.49</v>
+        <v>6.14</v>
       </c>
       <c r="P147" s="6" t="n">
-        <v>16.49</v>
+        <v>6.14</v>
       </c>
       <c r="Q147" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R147" s="6" t="n">
-        <v>21.9</v>
+        <v>11.92</v>
       </c>
       <c r="S147" s="6" t="n">
-        <v>21.9</v>
+        <v>11.92</v>
       </c>
       <c r="T147" s="6" t="n"/>
       <c r="U147" s="6" t="n">
@@ -13280,7 +13280,7 @@
         <v>7264</v>
       </c>
       <c r="W147" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X147" s="7" t="n">
         <v>0</v>
@@ -13297,7 +13297,7 @@
         <v>46172</v>
       </c>
       <c r="B148" s="8" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="C148" s="8" t="n">
         <v>46172</v>
@@ -13309,58 +13309,62 @@
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="I148" s="8" t="n">
-        <v>46172.32059027778</v>
+        <v>46171.82071759259</v>
       </c>
       <c r="J148" s="8" t="n">
-        <v>46172.47302083333</v>
+        <v>46171.92391203704</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>3.66</v>
+        <v>2.48</v>
       </c>
       <c r="L148" s="8" t="n">
-        <v>46172.56171296296</v>
+        <v>46172.29966435185</v>
       </c>
       <c r="M148" s="8" t="n">
-        <v>46172.81743055556</v>
+        <v>46172.37111111111</v>
       </c>
       <c r="N148" s="9" t="n">
-        <v>2.13</v>
+        <v>9.02</v>
       </c>
       <c r="O148" s="9" t="n">
-        <v>6.14</v>
+        <v>1.71</v>
       </c>
       <c r="P148" s="9" t="n">
-        <v>6.14</v>
+        <v>1.71</v>
       </c>
       <c r="Q148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R148" s="9" t="n">
-        <v>11.92</v>
+        <v>13.21</v>
       </c>
       <c r="S148" s="9" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="T148" s="9" t="n"/>
+        <v>13.21</v>
+      </c>
+      <c r="T148" s="9" t="inlineStr">
+        <is>
+          <t>ABNORMAL</t>
+        </is>
+      </c>
       <c r="U148" s="9" t="n">
         <v>1</v>
       </c>
@@ -13368,7 +13372,7 @@
         <v>7264</v>
       </c>
       <c r="W148" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X148" s="10" t="n">
         <v>0</v>
@@ -13385,7 +13389,7 @@
         <v>46172</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="C149" s="5" t="n">
         <v>46172</v>
@@ -13407,52 +13411,48 @@
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="I149" s="5" t="n">
-        <v>46171.82071759259</v>
+        <v>46172.43083333333</v>
       </c>
       <c r="J149" s="5" t="n">
-        <v>46171.92391203704</v>
+        <v>46172.52552083333</v>
       </c>
       <c r="K149" s="6" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>46172.29966435185</v>
+        <v>46172.61280092593</v>
       </c>
       <c r="M149" s="5" t="n">
-        <v>46172.37111111111</v>
+        <v>46172.86035879629</v>
       </c>
       <c r="N149" s="6" t="n">
-        <v>9.02</v>
+        <v>2.09</v>
       </c>
       <c r="O149" s="6" t="n">
-        <v>1.71</v>
+        <v>5.94</v>
       </c>
       <c r="P149" s="6" t="n">
-        <v>1.71</v>
+        <v>5.94</v>
       </c>
       <c r="Q149" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R149" s="6" t="n">
-        <v>13.21</v>
+        <v>10.31</v>
       </c>
       <c r="S149" s="6" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="T149" s="6" t="inlineStr">
-        <is>
-          <t>ABNORMAL</t>
-        </is>
-      </c>
+        <v>10.31</v>
+      </c>
+      <c r="T149" s="6" t="n"/>
       <c r="U149" s="6" t="n">
         <v>1</v>
       </c>
@@ -13489,56 +13489,56 @@
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="I150" s="8" t="n">
-        <v>46172.43083333333</v>
+        <v>46172.03034722222</v>
       </c>
       <c r="J150" s="8" t="n">
-        <v>46172.52552083333</v>
+        <v>46172.28571759259</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>2.27</v>
+        <v>6.13</v>
       </c>
       <c r="L150" s="8" t="n">
-        <v>46172.61280092593</v>
+        <v>46172.36446759259</v>
       </c>
       <c r="M150" s="8" t="n">
-        <v>46172.86035879629</v>
+        <v>46172.49165509259</v>
       </c>
       <c r="N150" s="9" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="O150" s="9" t="n">
-        <v>5.94</v>
+        <v>3.05</v>
       </c>
       <c r="P150" s="9" t="n">
-        <v>5.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R150" s="9" t="n">
-        <v>10.31</v>
+        <v>11.07</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>10.31</v>
+        <v>11.07</v>
       </c>
       <c r="T150" s="9" t="n"/>
       <c r="U150" s="9" t="n">
@@ -13548,7 +13548,7 @@
         <v>7264</v>
       </c>
       <c r="W150" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>0</v>
@@ -13565,7 +13565,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="C151" s="5" t="n">
         <v>46172</v>
@@ -13577,56 +13577,56 @@
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I151" s="5" t="n">
-        <v>46172.03034722222</v>
+        <v>46171.99543981482</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>46172.28571759259</v>
+        <v>46172.2858449074</v>
       </c>
       <c r="K151" s="6" t="n">
-        <v>6.13</v>
+        <v>6.97</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>46172.36446759259</v>
+        <v>46172.40947916666</v>
       </c>
       <c r="M151" s="5" t="n">
-        <v>46172.49165509259</v>
+        <v>46172.62247685185</v>
       </c>
       <c r="N151" s="6" t="n">
-        <v>1.89</v>
+        <v>2.97</v>
       </c>
       <c r="O151" s="6" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="P151" s="6" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="Q151" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R151" s="6" t="n">
-        <v>11.07</v>
+        <v>15.05</v>
       </c>
       <c r="S151" s="6" t="n">
-        <v>11.07</v>
+        <v>15.05</v>
       </c>
       <c r="T151" s="6" t="n"/>
       <c r="U151" s="6" t="n">
@@ -13650,13 +13650,13 @@
     </row>
     <row r="152">
       <c r="A152" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B152" s="8" t="n">
         <v>46172</v>
       </c>
-      <c r="B152" s="8" t="n">
-        <v>46171</v>
-      </c>
       <c r="C152" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
@@ -13665,56 +13665,56 @@
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H152" s="9" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I152" s="8" t="n">
-        <v>46171.99543981482</v>
+        <v>46172.945</v>
       </c>
       <c r="J152" s="8" t="n">
-        <v>46172.2858449074</v>
+        <v>46173.25171296296</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>6.97</v>
+        <v>7.36</v>
       </c>
       <c r="L152" s="8" t="n">
-        <v>46172.40947916666</v>
+        <v>46173.33864583333</v>
       </c>
       <c r="M152" s="8" t="n">
-        <v>46172.62247685185</v>
+        <v>46173.38333333333</v>
       </c>
       <c r="N152" s="9" t="n">
-        <v>2.97</v>
+        <v>2.09</v>
       </c>
       <c r="O152" s="9" t="n">
-        <v>5.11</v>
+        <v>1.07</v>
       </c>
       <c r="P152" s="9" t="n">
-        <v>5.11</v>
+        <v>1.07</v>
       </c>
       <c r="Q152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R152" s="9" t="n">
-        <v>15.05</v>
+        <v>10.52</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>15.05</v>
+        <v>10.52</v>
       </c>
       <c r="T152" s="9" t="n"/>
       <c r="U152" s="9" t="n">
@@ -13724,7 +13724,7 @@
         <v>7264</v>
       </c>
       <c r="W152" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X152" s="10" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>46173</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="C153" s="5" t="n">
         <v>46173</v>
@@ -13763,46 +13763,46 @@
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="I153" s="5" t="n">
-        <v>46172.945</v>
+        <v>46173.50255787037</v>
       </c>
       <c r="J153" s="5" t="n">
-        <v>46173.25171296296</v>
+        <v>46173.72892361111</v>
       </c>
       <c r="K153" s="6" t="n">
-        <v>7.36</v>
+        <v>5.43</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>46173.33864583333</v>
+        <v>46173.81170138889</v>
       </c>
       <c r="M153" s="5" t="n">
-        <v>46173.38333333333</v>
+        <v>46173.91047453704</v>
       </c>
       <c r="N153" s="6" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="O153" s="6" t="n">
-        <v>1.07</v>
+        <v>2.37</v>
       </c>
       <c r="P153" s="6" t="n">
-        <v>1.07</v>
+        <v>2.37</v>
       </c>
       <c r="Q153" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R153" s="6" t="n">
-        <v>10.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="S153" s="6" t="n">
-        <v>10.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="T153" s="6" t="n"/>
       <c r="U153" s="6" t="n">
@@ -13829,7 +13829,7 @@
         <v>46173</v>
       </c>
       <c r="B154" s="8" t="n">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="C154" s="8" t="n">
         <v>46173</v>
@@ -13841,56 +13841,56 @@
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="I154" s="8" t="n">
-        <v>46173.50255787037</v>
+        <v>46172.96576388889</v>
       </c>
       <c r="J154" s="8" t="n">
-        <v>46173.72892361111</v>
+        <v>46173.20033564815</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>5.43</v>
+        <v>5.63</v>
       </c>
       <c r="L154" s="8" t="n">
-        <v>46173.81170138889</v>
+        <v>46173.26480324074</v>
       </c>
       <c r="M154" s="8" t="n">
-        <v>46173.91047453704</v>
+        <v>46173.38116898148</v>
       </c>
       <c r="N154" s="9" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="O154" s="9" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="P154" s="9" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="Q154" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R154" s="9" t="n">
-        <v>9.789999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S154" s="9" t="n">
-        <v>9.789999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="T154" s="9" t="n"/>
       <c r="U154" s="9" t="n">
@@ -13900,7 +13900,7 @@
         <v>7264</v>
       </c>
       <c r="W154" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X154" s="10" t="n">
         <v>0</v>
@@ -13929,56 +13929,56 @@
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I155" s="5" t="n">
-        <v>46172.96576388889</v>
+        <v>46172.97828703704</v>
       </c>
       <c r="J155" s="5" t="n">
-        <v>46173.20033564815</v>
+        <v>46173.5018287037</v>
       </c>
       <c r="K155" s="6" t="n">
-        <v>5.63</v>
+        <v>12.56</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>46173.26480324074</v>
+        <v>46173.57653935185</v>
       </c>
       <c r="M155" s="5" t="n">
-        <v>46173.38116898148</v>
+        <v>46173.62144675926</v>
       </c>
       <c r="N155" s="6" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="O155" s="6" t="n">
-        <v>2.79</v>
+        <v>1.08</v>
       </c>
       <c r="P155" s="6" t="n">
-        <v>2.79</v>
+        <v>1.08</v>
       </c>
       <c r="Q155" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R155" s="6" t="n">
-        <v>9.970000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="S155" s="6" t="n">
-        <v>9.970000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="T155" s="6" t="n"/>
       <c r="U155" s="6" t="n">
@@ -14002,7 +14002,7 @@
     </row>
     <row r="156">
       <c r="A156" s="8" t="n">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="B156" s="8" t="n">
         <v>46172</v>
@@ -14012,61 +14012,61 @@
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E156" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="H156" s="9" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I156" s="8" t="n">
-        <v>46172.97828703704</v>
+        <v>46172.75962962963</v>
       </c>
       <c r="J156" s="8" t="n">
-        <v>46173.5018287037</v>
+        <v>46173.02157407408</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>12.56</v>
+        <v>6.29</v>
       </c>
       <c r="L156" s="8" t="n">
-        <v>46173.57653935185</v>
+        <v>46173.09358796296</v>
       </c>
       <c r="M156" s="8" t="n">
-        <v>46173.62144675926</v>
+        <v>46173.18756944445</v>
       </c>
       <c r="N156" s="9" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="O156" s="9" t="n">
-        <v>1.08</v>
+        <v>2.26</v>
       </c>
       <c r="P156" s="9" t="n">
-        <v>1.08</v>
+        <v>2.26</v>
       </c>
       <c r="Q156" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R156" s="9" t="n">
-        <v>15.44</v>
+        <v>10.27</v>
       </c>
       <c r="S156" s="9" t="n">
-        <v>15.44</v>
+        <v>10.27</v>
       </c>
       <c r="T156" s="9" t="n"/>
       <c r="U156" s="9" t="n">
@@ -14076,7 +14076,7 @@
         <v>7264</v>
       </c>
       <c r="W156" s="10" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X156" s="10" t="n">
         <v>0</v>
@@ -14090,10 +14090,10 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="C157" s="5" t="n">
         <v>46173</v>
@@ -14115,46 +14115,46 @@
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="H157" s="6" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="I157" s="5" t="n">
-        <v>46172.75962962963</v>
+        <v>46173.25349537037</v>
       </c>
       <c r="J157" s="5" t="n">
-        <v>46173.02157407408</v>
+        <v>46173.31078703704</v>
       </c>
       <c r="K157" s="6" t="n">
-        <v>6.29</v>
+        <v>1.38</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>46173.09358796296</v>
+        <v>46173.385625</v>
       </c>
       <c r="M157" s="5" t="n">
-        <v>46173.18756944445</v>
+        <v>46173.41065972222</v>
       </c>
       <c r="N157" s="6" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O157" s="6" t="n">
-        <v>2.26</v>
+        <v>0.6</v>
       </c>
       <c r="P157" s="6" t="n">
-        <v>2.26</v>
+        <v>0.6</v>
       </c>
       <c r="Q157" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R157" s="6" t="n">
-        <v>10.27</v>
+        <v>3.77</v>
       </c>
       <c r="S157" s="6" t="n">
-        <v>10.27</v>
+        <v>3.77</v>
       </c>
       <c r="T157" s="6" t="n"/>
       <c r="U157" s="6" t="n">
@@ -14164,7 +14164,7 @@
         <v>7264</v>
       </c>
       <c r="W157" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X157" s="7" t="n">
         <v>0</v>
@@ -14176,96 +14176,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B158" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="C158" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D158" s="9" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="E158" s="9" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="F158" s="9" t="inlineStr">
-        <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
-        </is>
-      </c>
-      <c r="G158" s="9" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="H158" s="9" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="I158" s="8" t="n">
-        <v>46173.25349537037</v>
-      </c>
-      <c r="J158" s="8" t="n">
-        <v>46173.31078703704</v>
-      </c>
-      <c r="K158" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="L158" s="8" t="n">
-        <v>46173.385625</v>
-      </c>
-      <c r="M158" s="8" t="n">
-        <v>46173.41065972222</v>
-      </c>
-      <c r="N158" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O158" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P158" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" s="9" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="S158" s="9" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="T158" s="9" t="n"/>
-      <c r="U158" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V158" s="10" t="n">
-        <v>7264</v>
-      </c>
-      <c r="W158" s="10" t="n">
-        <v>3632</v>
-      </c>
-      <c r="X158" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y158" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z158" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:Z158"/>
+  <autoFilter ref="A4:Z157"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Trip_Detail" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trip_Detail'!$A$4:$Z$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trip_Detail'!$A$4:$Z$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z157"/>
+  <dimension ref="A1:Z156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B137" s="5" t="n">
         <v>46170</v>
@@ -12332,67 +12332,63 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I137" s="5" t="n">
-        <v>46170.11607638889</v>
+        <v>46170.58722222222</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>46170.26921296296</v>
+        <v>46170.89265046296</v>
       </c>
       <c r="K137" s="6" t="n">
-        <v>3.68</v>
+        <v>7.33</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>46170.83622685185</v>
+        <v>46170.96063657408</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>46170.9013425926</v>
+        <v>46171.30994212963</v>
       </c>
       <c r="N137" s="6" t="n">
-        <v>13.61</v>
+        <v>1.63</v>
       </c>
       <c r="O137" s="6" t="n">
-        <v>1.56</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="P137" s="6" t="n">
-        <v>1.56</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="Q137" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R137" s="6" t="n">
-        <v>18.85</v>
+        <v>17.35</v>
       </c>
       <c r="S137" s="6" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="T137" s="6" t="inlineStr">
-        <is>
-          <t>ABNORMAL</t>
-        </is>
-      </c>
+        <v>17.35</v>
+      </c>
+      <c r="T137" s="6" t="n"/>
       <c r="U137" s="6" t="n">
         <v>1</v>
       </c>
@@ -12417,68 +12413,68 @@
         <v>46171</v>
       </c>
       <c r="B138" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C138" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I138" s="8" t="n">
-        <v>46170.58722222222</v>
+        <v>46171.16535879629</v>
       </c>
       <c r="J138" s="8" t="n">
-        <v>46170.89265046296</v>
+        <v>46171.27927083334</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>7.33</v>
+        <v>2.73</v>
       </c>
       <c r="L138" s="8" t="n">
-        <v>46170.96063657408</v>
+        <v>46171.37247685185</v>
       </c>
       <c r="M138" s="8" t="n">
-        <v>46171.30994212963</v>
+        <v>46171.61934027778</v>
       </c>
       <c r="N138" s="9" t="n">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="O138" s="9" t="n">
-        <v>8.380000000000001</v>
+        <v>5.92</v>
       </c>
       <c r="P138" s="9" t="n">
-        <v>8.380000000000001</v>
+        <v>5.92</v>
       </c>
       <c r="Q138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R138" s="9" t="n">
-        <v>17.35</v>
+        <v>10.9</v>
       </c>
       <c r="S138" s="9" t="n">
-        <v>17.35</v>
+        <v>10.9</v>
       </c>
       <c r="T138" s="9" t="n"/>
       <c r="U138" s="9" t="n">
@@ -12488,7 +12484,7 @@
         <v>7360</v>
       </c>
       <c r="W138" s="10" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
         <v>0</v>
@@ -12527,46 +12523,46 @@
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I139" s="5" t="n">
-        <v>46171.16535879629</v>
+        <v>46171.78201388889</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>46171.27927083334</v>
+        <v>46171.89481481481</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>46171.37247685185</v>
+        <v>46171.96677083334</v>
       </c>
       <c r="M139" s="5" t="n">
-        <v>46171.61934027778</v>
+        <v>46172.09275462963</v>
       </c>
       <c r="N139" s="6" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="O139" s="6" t="n">
-        <v>5.92</v>
+        <v>3.02</v>
       </c>
       <c r="P139" s="6" t="n">
-        <v>5.92</v>
+        <v>3.02</v>
       </c>
       <c r="Q139" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R139" s="6" t="n">
-        <v>10.9</v>
+        <v>7.46</v>
       </c>
       <c r="S139" s="6" t="n">
-        <v>10.9</v>
+        <v>7.46</v>
       </c>
       <c r="T139" s="6" t="n"/>
       <c r="U139" s="6" t="n">
@@ -12605,56 +12601,56 @@
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I140" s="8" t="n">
-        <v>46171.78201388889</v>
+        <v>46171.33181712963</v>
       </c>
       <c r="J140" s="8" t="n">
-        <v>46171.89481481481</v>
+        <v>46171.60032407408</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>2.71</v>
+        <v>6.44</v>
       </c>
       <c r="L140" s="8" t="n">
-        <v>46171.96677083334</v>
+        <v>46171.67759259259</v>
       </c>
       <c r="M140" s="8" t="n">
-        <v>46172.09275462963</v>
+        <v>46171.70689814815</v>
       </c>
       <c r="N140" s="9" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="O140" s="9" t="n">
-        <v>3.02</v>
+        <v>0.7</v>
       </c>
       <c r="P140" s="9" t="n">
-        <v>3.02</v>
+        <v>0.7</v>
       </c>
       <c r="Q140" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R140" s="9" t="n">
-        <v>7.46</v>
+        <v>9</v>
       </c>
       <c r="S140" s="9" t="n">
-        <v>7.46</v>
+        <v>9</v>
       </c>
       <c r="T140" s="9" t="n"/>
       <c r="U140" s="9" t="n">
@@ -12681,7 +12677,7 @@
         <v>46171</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="C141" s="5" t="n">
         <v>46171</v>
@@ -12693,56 +12689,56 @@
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="I141" s="5" t="n">
-        <v>46171.33181712963</v>
+        <v>46170.99238425926</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>46171.60032407408</v>
+        <v>46171.28165509259</v>
       </c>
       <c r="K141" s="6" t="n">
-        <v>6.44</v>
+        <v>6.94</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>46171.67759259259</v>
+        <v>46171.3696875</v>
       </c>
       <c r="M141" s="5" t="n">
-        <v>46171.70689814815</v>
+        <v>46171.59075231481</v>
       </c>
       <c r="N141" s="6" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="O141" s="6" t="n">
-        <v>0.7</v>
+        <v>5.31</v>
       </c>
       <c r="P141" s="6" t="n">
-        <v>0.7</v>
+        <v>5.31</v>
       </c>
       <c r="Q141" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R141" s="6" t="n">
-        <v>9</v>
+        <v>14.36</v>
       </c>
       <c r="S141" s="6" t="n">
-        <v>9</v>
+        <v>14.36</v>
       </c>
       <c r="T141" s="6" t="n"/>
       <c r="U141" s="6" t="n">
@@ -12769,7 +12765,7 @@
         <v>46171</v>
       </c>
       <c r="B142" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C142" s="8" t="n">
         <v>46171</v>
@@ -12791,46 +12787,46 @@
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="H142" s="9" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="I142" s="8" t="n">
-        <v>46170.99238425926</v>
+        <v>46171.66229166667</v>
       </c>
       <c r="J142" s="8" t="n">
-        <v>46171.28165509259</v>
+        <v>46171.72710648148</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>6.94</v>
+        <v>1.56</v>
       </c>
       <c r="L142" s="8" t="n">
-        <v>46171.3696875</v>
+        <v>46171.82959490741</v>
       </c>
       <c r="M142" s="8" t="n">
-        <v>46171.59075231481</v>
+        <v>46171.94225694444</v>
       </c>
       <c r="N142" s="9" t="n">
-        <v>2.11</v>
+        <v>2.46</v>
       </c>
       <c r="O142" s="9" t="n">
-        <v>5.31</v>
+        <v>2.7</v>
       </c>
       <c r="P142" s="9" t="n">
-        <v>5.31</v>
+        <v>2.7</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R142" s="9" t="n">
-        <v>14.36</v>
+        <v>6.72</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>14.36</v>
+        <v>6.72</v>
       </c>
       <c r="T142" s="9" t="n"/>
       <c r="U142" s="9" t="n">
@@ -12869,56 +12865,56 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="I143" s="5" t="n">
-        <v>46171.66229166667</v>
+        <v>46171.00243055556</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>46171.72710648148</v>
+        <v>46171.46831018518</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>1.56</v>
+        <v>11.18</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>46171.82959490741</v>
+        <v>46171.54582175926</v>
       </c>
       <c r="M143" s="5" t="n">
-        <v>46171.94225694444</v>
+        <v>46171.60834490741</v>
       </c>
       <c r="N143" s="6" t="n">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="O143" s="6" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="P143" s="6" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="Q143" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R143" s="6" t="n">
-        <v>6.72</v>
+        <v>14.54</v>
       </c>
       <c r="S143" s="6" t="n">
-        <v>6.72</v>
+        <v>14.54</v>
       </c>
       <c r="T143" s="6" t="n"/>
       <c r="U143" s="6" t="n">
@@ -12967,46 +12963,46 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="H144" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I144" s="8" t="n">
-        <v>46171.00243055556</v>
+        <v>46171.67638888889</v>
       </c>
       <c r="J144" s="8" t="n">
-        <v>46171.46831018518</v>
+        <v>46171.7416087963</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>11.18</v>
+        <v>1.57</v>
       </c>
       <c r="L144" s="8" t="n">
-        <v>46171.54582175926</v>
+        <v>46171.82641203704</v>
       </c>
       <c r="M144" s="8" t="n">
-        <v>46171.60834490741</v>
+        <v>46171.875625</v>
       </c>
       <c r="N144" s="9" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="O144" s="9" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="P144" s="9" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R144" s="9" t="n">
-        <v>14.54</v>
+        <v>4.78</v>
       </c>
       <c r="S144" s="9" t="n">
-        <v>14.54</v>
+        <v>4.78</v>
       </c>
       <c r="T144" s="9" t="n"/>
       <c r="U144" s="9" t="n">
@@ -13030,7 +13026,7 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B145" s="5" t="n">
         <v>46171</v>
@@ -13040,68 +13036,68 @@
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G145" s="6" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I145" s="5" t="n">
-        <v>46171.67638888889</v>
+        <v>46171.72065972222</v>
       </c>
       <c r="J145" s="5" t="n">
-        <v>46171.7416087963</v>
+        <v>46171.87474537037</v>
       </c>
       <c r="K145" s="6" t="n">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>46171.82641203704</v>
+        <v>46171.94614583333</v>
       </c>
       <c r="M145" s="5" t="n">
-        <v>46171.875625</v>
+        <v>46172.63309027778</v>
       </c>
       <c r="N145" s="6" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="O145" s="6" t="n">
-        <v>1.18</v>
+        <v>16.49</v>
       </c>
       <c r="P145" s="6" t="n">
-        <v>1.18</v>
+        <v>16.49</v>
       </c>
       <c r="Q145" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R145" s="6" t="n">
-        <v>4.78</v>
+        <v>21.9</v>
       </c>
       <c r="S145" s="6" t="n">
-        <v>4.78</v>
+        <v>21.9</v>
       </c>
       <c r="T145" s="6" t="n"/>
       <c r="U145" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V145" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="W145" s="7" t="n">
         <v>0</v>
@@ -13121,68 +13117,68 @@
         <v>46172</v>
       </c>
       <c r="B146" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="C146" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="H146" s="9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I146" s="8" t="n">
-        <v>46171.72065972222</v>
+        <v>46172.32059027778</v>
       </c>
       <c r="J146" s="8" t="n">
-        <v>46171.87474537037</v>
+        <v>46172.47302083333</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="L146" s="8" t="n">
-        <v>46171.94614583333</v>
+        <v>46172.56171296296</v>
       </c>
       <c r="M146" s="8" t="n">
-        <v>46172.63309027778</v>
+        <v>46172.81743055556</v>
       </c>
       <c r="N146" s="9" t="n">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="O146" s="9" t="n">
-        <v>16.49</v>
+        <v>6.14</v>
       </c>
       <c r="P146" s="9" t="n">
-        <v>16.49</v>
+        <v>6.14</v>
       </c>
       <c r="Q146" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R146" s="9" t="n">
-        <v>21.9</v>
+        <v>11.92</v>
       </c>
       <c r="S146" s="9" t="n">
-        <v>21.9</v>
+        <v>11.92</v>
       </c>
       <c r="T146" s="9" t="n"/>
       <c r="U146" s="9" t="n">
@@ -13192,7 +13188,7 @@
         <v>7264</v>
       </c>
       <c r="W146" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X146" s="10" t="n">
         <v>0</v>
@@ -13209,7 +13205,7 @@
         <v>46172</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="C147" s="5" t="n">
         <v>46172</v>
@@ -13221,58 +13217,62 @@
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="I147" s="5" t="n">
-        <v>46172.32059027778</v>
+        <v>46171.82071759259</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>46172.47302083333</v>
+        <v>46171.92391203704</v>
       </c>
       <c r="K147" s="6" t="n">
-        <v>3.66</v>
+        <v>2.48</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>46172.56171296296</v>
+        <v>46172.29966435185</v>
       </c>
       <c r="M147" s="5" t="n">
-        <v>46172.81743055556</v>
+        <v>46172.37111111111</v>
       </c>
       <c r="N147" s="6" t="n">
-        <v>2.13</v>
+        <v>9.02</v>
       </c>
       <c r="O147" s="6" t="n">
-        <v>6.14</v>
+        <v>1.71</v>
       </c>
       <c r="P147" s="6" t="n">
-        <v>6.14</v>
+        <v>1.71</v>
       </c>
       <c r="Q147" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R147" s="6" t="n">
-        <v>11.92</v>
+        <v>13.21</v>
       </c>
       <c r="S147" s="6" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="T147" s="6" t="n"/>
+        <v>13.21</v>
+      </c>
+      <c r="T147" s="6" t="inlineStr">
+        <is>
+          <t>ABNORMAL</t>
+        </is>
+      </c>
       <c r="U147" s="6" t="n">
         <v>1</v>
       </c>
@@ -13280,7 +13280,7 @@
         <v>7264</v>
       </c>
       <c r="W147" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X147" s="7" t="n">
         <v>0</v>
@@ -13297,7 +13297,7 @@
         <v>46172</v>
       </c>
       <c r="B148" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="C148" s="8" t="n">
         <v>46172</v>
@@ -13319,52 +13319,48 @@
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="I148" s="8" t="n">
-        <v>46171.82071759259</v>
+        <v>46172.43083333333</v>
       </c>
       <c r="J148" s="8" t="n">
-        <v>46171.92391203704</v>
+        <v>46172.52552083333</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="L148" s="8" t="n">
-        <v>46172.29966435185</v>
+        <v>46172.61280092593</v>
       </c>
       <c r="M148" s="8" t="n">
-        <v>46172.37111111111</v>
+        <v>46172.86035879629</v>
       </c>
       <c r="N148" s="9" t="n">
-        <v>9.02</v>
+        <v>2.09</v>
       </c>
       <c r="O148" s="9" t="n">
-        <v>1.71</v>
+        <v>5.94</v>
       </c>
       <c r="P148" s="9" t="n">
-        <v>1.71</v>
+        <v>5.94</v>
       </c>
       <c r="Q148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R148" s="9" t="n">
-        <v>13.21</v>
+        <v>10.31</v>
       </c>
       <c r="S148" s="9" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="T148" s="9" t="inlineStr">
-        <is>
-          <t>ABNORMAL</t>
-        </is>
-      </c>
+        <v>10.31</v>
+      </c>
+      <c r="T148" s="9" t="n"/>
       <c r="U148" s="9" t="n">
         <v>1</v>
       </c>
@@ -13401,56 +13397,56 @@
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="I149" s="5" t="n">
-        <v>46172.43083333333</v>
+        <v>46172.03034722222</v>
       </c>
       <c r="J149" s="5" t="n">
-        <v>46172.52552083333</v>
+        <v>46172.28571759259</v>
       </c>
       <c r="K149" s="6" t="n">
-        <v>2.27</v>
+        <v>6.13</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>46172.61280092593</v>
+        <v>46172.36446759259</v>
       </c>
       <c r="M149" s="5" t="n">
-        <v>46172.86035879629</v>
+        <v>46172.49165509259</v>
       </c>
       <c r="N149" s="6" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="O149" s="6" t="n">
-        <v>5.94</v>
+        <v>3.05</v>
       </c>
       <c r="P149" s="6" t="n">
-        <v>5.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q149" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R149" s="6" t="n">
-        <v>10.31</v>
+        <v>11.07</v>
       </c>
       <c r="S149" s="6" t="n">
-        <v>10.31</v>
+        <v>11.07</v>
       </c>
       <c r="T149" s="6" t="n"/>
       <c r="U149" s="6" t="n">
@@ -13460,7 +13456,7 @@
         <v>7264</v>
       </c>
       <c r="W149" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X149" s="7" t="n">
         <v>0</v>
@@ -13477,7 +13473,7 @@
         <v>46172</v>
       </c>
       <c r="B150" s="8" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="C150" s="8" t="n">
         <v>46172</v>
@@ -13489,56 +13485,56 @@
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I150" s="8" t="n">
-        <v>46172.03034722222</v>
+        <v>46171.99543981482</v>
       </c>
       <c r="J150" s="8" t="n">
-        <v>46172.28571759259</v>
+        <v>46172.2858449074</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>6.13</v>
+        <v>6.97</v>
       </c>
       <c r="L150" s="8" t="n">
-        <v>46172.36446759259</v>
+        <v>46172.40947916666</v>
       </c>
       <c r="M150" s="8" t="n">
-        <v>46172.49165509259</v>
+        <v>46172.62247685185</v>
       </c>
       <c r="N150" s="9" t="n">
-        <v>1.89</v>
+        <v>2.97</v>
       </c>
       <c r="O150" s="9" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="P150" s="9" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R150" s="9" t="n">
-        <v>11.07</v>
+        <v>15.05</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>11.07</v>
+        <v>15.05</v>
       </c>
       <c r="T150" s="9" t="n"/>
       <c r="U150" s="9" t="n">
@@ -13562,13 +13558,13 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B151" s="5" t="n">
         <v>46172</v>
       </c>
-      <c r="B151" s="5" t="n">
-        <v>46171</v>
-      </c>
       <c r="C151" s="5" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
@@ -13577,56 +13573,56 @@
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I151" s="5" t="n">
-        <v>46171.99543981482</v>
+        <v>46172.945</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>46172.2858449074</v>
+        <v>46173.25171296296</v>
       </c>
       <c r="K151" s="6" t="n">
-        <v>6.97</v>
+        <v>7.36</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>46172.40947916666</v>
+        <v>46173.33864583333</v>
       </c>
       <c r="M151" s="5" t="n">
-        <v>46172.62247685185</v>
+        <v>46173.38333333333</v>
       </c>
       <c r="N151" s="6" t="n">
-        <v>2.97</v>
+        <v>2.09</v>
       </c>
       <c r="O151" s="6" t="n">
-        <v>5.11</v>
+        <v>1.07</v>
       </c>
       <c r="P151" s="6" t="n">
-        <v>5.11</v>
+        <v>1.07</v>
       </c>
       <c r="Q151" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R151" s="6" t="n">
-        <v>15.05</v>
+        <v>10.52</v>
       </c>
       <c r="S151" s="6" t="n">
-        <v>15.05</v>
+        <v>10.52</v>
       </c>
       <c r="T151" s="6" t="n"/>
       <c r="U151" s="6" t="n">
@@ -13636,7 +13632,7 @@
         <v>7264</v>
       </c>
       <c r="W151" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X151" s="7" t="n">
         <v>0</v>
@@ -13653,7 +13649,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="C152" s="8" t="n">
         <v>46173</v>
@@ -13675,46 +13671,46 @@
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="H152" s="9" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="I152" s="8" t="n">
-        <v>46172.945</v>
+        <v>46173.50255787037</v>
       </c>
       <c r="J152" s="8" t="n">
-        <v>46173.25171296296</v>
+        <v>46173.72892361111</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>7.36</v>
+        <v>5.43</v>
       </c>
       <c r="L152" s="8" t="n">
-        <v>46173.33864583333</v>
+        <v>46173.81170138889</v>
       </c>
       <c r="M152" s="8" t="n">
-        <v>46173.38333333333</v>
+        <v>46173.91047453704</v>
       </c>
       <c r="N152" s="9" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="O152" s="9" t="n">
-        <v>1.07</v>
+        <v>2.37</v>
       </c>
       <c r="P152" s="9" t="n">
-        <v>1.07</v>
+        <v>2.37</v>
       </c>
       <c r="Q152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R152" s="9" t="n">
-        <v>10.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>10.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="T152" s="9" t="n"/>
       <c r="U152" s="9" t="n">
@@ -13741,7 +13737,7 @@
         <v>46173</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="C153" s="5" t="n">
         <v>46173</v>
@@ -13753,56 +13749,56 @@
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="I153" s="5" t="n">
-        <v>46173.50255787037</v>
+        <v>46172.96576388889</v>
       </c>
       <c r="J153" s="5" t="n">
-        <v>46173.72892361111</v>
+        <v>46173.20033564815</v>
       </c>
       <c r="K153" s="6" t="n">
-        <v>5.43</v>
+        <v>5.63</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>46173.81170138889</v>
+        <v>46173.26480324074</v>
       </c>
       <c r="M153" s="5" t="n">
-        <v>46173.91047453704</v>
+        <v>46173.38116898148</v>
       </c>
       <c r="N153" s="6" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="O153" s="6" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="P153" s="6" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="Q153" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R153" s="6" t="n">
-        <v>9.789999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S153" s="6" t="n">
-        <v>9.789999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="T153" s="6" t="n"/>
       <c r="U153" s="6" t="n">
@@ -13812,7 +13808,7 @@
         <v>7264</v>
       </c>
       <c r="W153" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X153" s="7" t="n">
         <v>0</v>
@@ -13841,56 +13837,56 @@
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I154" s="8" t="n">
-        <v>46172.96576388889</v>
+        <v>46172.97828703704</v>
       </c>
       <c r="J154" s="8" t="n">
-        <v>46173.20033564815</v>
+        <v>46173.5018287037</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>5.63</v>
+        <v>12.56</v>
       </c>
       <c r="L154" s="8" t="n">
-        <v>46173.26480324074</v>
+        <v>46173.57653935185</v>
       </c>
       <c r="M154" s="8" t="n">
-        <v>46173.38116898148</v>
+        <v>46173.62144675926</v>
       </c>
       <c r="N154" s="9" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="O154" s="9" t="n">
-        <v>2.79</v>
+        <v>1.08</v>
       </c>
       <c r="P154" s="9" t="n">
-        <v>2.79</v>
+        <v>1.08</v>
       </c>
       <c r="Q154" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R154" s="9" t="n">
-        <v>9.970000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="S154" s="9" t="n">
-        <v>9.970000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="T154" s="9" t="n"/>
       <c r="U154" s="9" t="n">
@@ -13914,7 +13910,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="B155" s="5" t="n">
         <v>46172</v>
@@ -13924,61 +13920,61 @@
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I155" s="5" t="n">
-        <v>46172.97828703704</v>
+        <v>46172.75962962963</v>
       </c>
       <c r="J155" s="5" t="n">
-        <v>46173.5018287037</v>
+        <v>46173.02157407408</v>
       </c>
       <c r="K155" s="6" t="n">
-        <v>12.56</v>
+        <v>6.29</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>46173.57653935185</v>
+        <v>46173.09358796296</v>
       </c>
       <c r="M155" s="5" t="n">
-        <v>46173.62144675926</v>
+        <v>46173.18756944445</v>
       </c>
       <c r="N155" s="6" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="O155" s="6" t="n">
-        <v>1.08</v>
+        <v>2.26</v>
       </c>
       <c r="P155" s="6" t="n">
-        <v>1.08</v>
+        <v>2.26</v>
       </c>
       <c r="Q155" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R155" s="6" t="n">
-        <v>15.44</v>
+        <v>10.27</v>
       </c>
       <c r="S155" s="6" t="n">
-        <v>15.44</v>
+        <v>10.27</v>
       </c>
       <c r="T155" s="6" t="n"/>
       <c r="U155" s="6" t="n">
@@ -13988,7 +13984,7 @@
         <v>7264</v>
       </c>
       <c r="W155" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X155" s="7" t="n">
         <v>0</v>
@@ -14002,10 +13998,10 @@
     </row>
     <row r="156">
       <c r="A156" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B156" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="C156" s="8" t="n">
         <v>46173</v>
@@ -14027,46 +14023,46 @@
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="H156" s="9" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="I156" s="8" t="n">
-        <v>46172.75962962963</v>
+        <v>46173.25349537037</v>
       </c>
       <c r="J156" s="8" t="n">
-        <v>46173.02157407408</v>
+        <v>46173.31078703704</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>6.29</v>
+        <v>1.38</v>
       </c>
       <c r="L156" s="8" t="n">
-        <v>46173.09358796296</v>
+        <v>46173.385625</v>
       </c>
       <c r="M156" s="8" t="n">
-        <v>46173.18756944445</v>
+        <v>46173.41065972222</v>
       </c>
       <c r="N156" s="9" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O156" s="9" t="n">
-        <v>2.26</v>
+        <v>0.6</v>
       </c>
       <c r="P156" s="9" t="n">
-        <v>2.26</v>
+        <v>0.6</v>
       </c>
       <c r="Q156" s="9" t="n">
         <v>0</v>
       </c>
       <c r="R156" s="9" t="n">
-        <v>10.27</v>
+        <v>3.77</v>
       </c>
       <c r="S156" s="9" t="n">
-        <v>10.27</v>
+        <v>3.77</v>
       </c>
       <c r="T156" s="9" t="n"/>
       <c r="U156" s="9" t="n">
@@ -14076,7 +14072,7 @@
         <v>7264</v>
       </c>
       <c r="W156" s="10" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X156" s="10" t="n">
         <v>0</v>
@@ -14088,96 +14084,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="5" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B157" s="5" t="n">
-        <v>46173</v>
-      </c>
-      <c r="C157" s="5" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="F157" s="6" t="inlineStr">
-        <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
-        </is>
-      </c>
-      <c r="G157" s="6" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="H157" s="6" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="I157" s="5" t="n">
-        <v>46173.25349537037</v>
-      </c>
-      <c r="J157" s="5" t="n">
-        <v>46173.31078703704</v>
-      </c>
-      <c r="K157" s="6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="L157" s="5" t="n">
-        <v>46173.385625</v>
-      </c>
-      <c r="M157" s="5" t="n">
-        <v>46173.41065972222</v>
-      </c>
-      <c r="N157" s="6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O157" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P157" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q157" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" s="6" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="S157" s="6" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="T157" s="6" t="n"/>
-      <c r="U157" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V157" s="7" t="n">
-        <v>7264</v>
-      </c>
-      <c r="W157" s="7" t="n">
-        <v>3632</v>
-      </c>
-      <c r="X157" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y157" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z157" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:Z157"/>
+  <autoFilter ref="A4:Z156"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:01</t>
+          <t>2026-08-04 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:33</t>
+          <t>2026-08-04 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:11</t>
+          <t>2026-08-05 14:34</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13895,7 @@
         <v>1720</v>
       </c>
       <c r="X154" s="10" t="n">
-        <v>6880</v>
+        <v>0</v>
       </c>
       <c r="Y154" s="10" t="n">
         <v>0</v>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 14:34</t>
+          <t>2026-08-07 15:55</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13895,7 @@
         <v>1720</v>
       </c>
       <c r="X154" s="10" t="n">
-        <v>0</v>
+        <v>6880</v>
       </c>
       <c r="Y154" s="10" t="n">
         <v>0</v>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 15:55</t>
+          <t>2026-08-09 10:57</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="10" t="n">
-        <v>6688</v>
+        <v>6976</v>
       </c>
       <c r="W44" s="10" t="n">
         <v>1672</v>
@@ -4289,7 +4289,7 @@
         <v>1</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>6688</v>
+        <v>6976</v>
       </c>
       <c r="W45" s="7" t="n">
         <v>1672</v>
@@ -4465,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="V47" s="7" t="n">
-        <v>6688</v>
+        <v>6976</v>
       </c>
       <c r="W47" s="7" t="n">
         <v>1672</v>
@@ -4553,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="10" t="n">
-        <v>6688</v>
+        <v>6976</v>
       </c>
       <c r="W48" s="10" t="n">
         <v>1672</v>
@@ -11949,7 +11949,7 @@
         <v>1</v>
       </c>
       <c r="V132" s="10" t="n">
-        <v>6784</v>
+        <v>6688</v>
       </c>
       <c r="W132" s="10" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="V135" s="7" t="n">
-        <v>6784</v>
+        <v>6688</v>
       </c>
       <c r="W135" s="7" t="n">
         <v>0</v>
@@ -12477,7 +12477,7 @@
         <v>1</v>
       </c>
       <c r="V138" s="10" t="n">
-        <v>6880</v>
+        <v>6784</v>
       </c>
       <c r="W138" s="10" t="n">
         <v>1720</v>
@@ -12829,7 +12829,7 @@
         <v>1</v>
       </c>
       <c r="V142" s="10" t="n">
-        <v>6880</v>
+        <v>6784</v>
       </c>
       <c r="W142" s="10" t="n">
         <v>1720</v>

--- a/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
+++ b/reports/oatside-pg-2026/exports/05_Trip_Detail.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:57</t>
+          <t>2026-08-09 11:52</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
         <v>6976</v>
       </c>
       <c r="W44" s="10" t="n">
-        <v>1672</v>
+        <v>1744</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>6976</v>
       </c>
       <c r="W45" s="7" t="n">
-        <v>1672</v>
+        <v>1744</v>
       </c>
       <c r="X45" s="7" t="n">
         <v>0</v>
@@ -4468,7 +4468,7 @@
         <v>6976</v>
       </c>
       <c r="W47" s="7" t="n">
-        <v>1672</v>
+        <v>1744</v>
       </c>
       <c r="X47" s="7" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>6976</v>
       </c>
       <c r="W48" s="10" t="n">
-        <v>1672</v>
+        <v>1744</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>0</v>
@@ -12480,7 +12480,7 @@
         <v>6784</v>
       </c>
       <c r="W138" s="10" t="n">
-        <v>1720</v>
+        <v>1696</v>
       </c>
       <c r="X138" s="10" t="n">
         <v>0</v>
@@ -12832,7 +12832,7 @@
         <v>6784</v>
       </c>
       <c r="W142" s="10" t="n">
-        <v>1720</v>
+        <v>1696</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>0</v>
